--- a/holdings.xlsx
+++ b/holdings.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06083FE-778C-4B73-AA5A-45E82F0625F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C5E1E6-80A1-4814-B4E3-37B7B0FB11C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="14235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="116">
   <si>
     <t/>
   </si>
@@ -103,6 +103,12 @@
     <t>מניות</t>
   </si>
   <si>
+    <t>אי.טי.ג'י.איי</t>
+  </si>
+  <si>
+    <t>1176114</t>
+  </si>
+  <si>
     <t>אלדן תחבורה</t>
   </si>
   <si>
@@ -239,6 +245,12 @@
   </si>
   <si>
     <t>1242932</t>
+  </si>
+  <si>
+    <t>לוזון קב אג ט</t>
+  </si>
+  <si>
+    <t>4730180</t>
   </si>
   <si>
     <t>מהדרין אגח ב</t>
@@ -750,7 +762,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A5:W75"/>
+  <dimension ref="A1:W77"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.73046875" bestFit="1" customWidth="1"/>
@@ -777,6 +789,77 @@
     <col min="23" max="23" width="24.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V1" t="s">
+        <v>0</v>
+      </c>
+      <c r="W1" t="s">
+        <v>0</v>
+      </c>
+    </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.45">
       <c r="C5" s="1"/>
       <c r="E5" s="1"/>
@@ -1238,48 +1321,48 @@
         <v>0</v>
       </c>
       <c r="F15" s="1">
-        <v>4680</v>
+        <v>1500</v>
       </c>
       <c r="G15" s="1">
-        <v>712.2</v>
+        <v>2000</v>
       </c>
       <c r="H15" t="s">
         <v>2</v>
       </c>
       <c r="I15" s="1">
-        <v>378.95</v>
+        <v>-870.55</v>
       </c>
       <c r="J15" s="1">
-        <v>1.1499999999999999</v>
+        <v>-2.82</v>
       </c>
       <c r="K15" s="1">
-        <v>684.32</v>
+        <v>2000</v>
       </c>
       <c r="L15" s="1">
-        <v>698.43</v>
+        <v>2000</v>
       </c>
       <c r="M15" s="1">
-        <v>1304.79</v>
+        <v>0</v>
       </c>
       <c r="N15" s="1">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="O15" s="1">
-        <v>644.41999999999996</v>
+        <v>0</v>
       </c>
       <c r="P15" s="1">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="1">
-        <v>33330.959999999999</v>
+        <v>30000</v>
       </c>
       <c r="R15" s="1">
-        <v>33330.959999999999</v>
+        <v>30000</v>
       </c>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
       <c r="U15" s="1">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="V15" s="1">
         <v>0</v>
@@ -1305,48 +1388,48 @@
         <v>0</v>
       </c>
       <c r="F16" s="1">
-        <v>7000</v>
+        <v>4680</v>
       </c>
       <c r="G16" s="1">
-        <v>641.4</v>
+        <v>746</v>
       </c>
       <c r="H16" t="s">
         <v>2</v>
       </c>
       <c r="I16" s="1">
-        <v>819.85</v>
+        <v>242.69</v>
       </c>
       <c r="J16" s="1">
-        <v>1.86</v>
+        <v>0.7</v>
       </c>
       <c r="K16" s="1">
-        <v>575.66999999999996</v>
+        <v>684.32</v>
       </c>
       <c r="L16" s="1">
-        <v>635.42999999999995</v>
+        <v>698.43</v>
       </c>
       <c r="M16" s="1">
-        <v>4600.88</v>
+        <v>2886.63</v>
       </c>
       <c r="N16" s="1">
-        <v>11.41</v>
+        <v>9.01</v>
       </c>
       <c r="O16" s="1">
-        <v>418</v>
+        <v>2226.2600000000002</v>
       </c>
       <c r="P16" s="1">
-        <v>0.93</v>
+        <v>6.81</v>
       </c>
       <c r="Q16" s="1">
-        <v>44898</v>
+        <v>34912.800000000003</v>
       </c>
       <c r="R16" s="1">
-        <v>44898</v>
+        <v>34912.800000000003</v>
       </c>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
       <c r="U16" s="1">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="V16" s="1">
         <v>0</v>
@@ -1372,48 +1455,48 @@
         <v>0</v>
       </c>
       <c r="F17" s="1">
-        <v>93000</v>
+        <v>6000</v>
       </c>
       <c r="G17" s="1">
-        <v>99.6</v>
+        <v>674</v>
       </c>
       <c r="H17" t="s">
         <v>2</v>
       </c>
       <c r="I17" s="1">
-        <v>2880.88</v>
+        <v>-289.18</v>
       </c>
       <c r="J17" s="1">
-        <v>3.21</v>
+        <v>-0.71</v>
       </c>
       <c r="K17" s="1">
-        <v>92.69</v>
+        <v>575.66999999999996</v>
       </c>
       <c r="L17" s="1">
-        <v>89.42</v>
+        <v>641.24</v>
       </c>
       <c r="M17" s="1">
-        <v>6423.88</v>
+        <v>5899.61</v>
       </c>
       <c r="N17" s="1">
-        <v>7.45</v>
+        <v>17.079999999999998</v>
       </c>
       <c r="O17" s="1">
-        <v>9470.2000000000007</v>
+        <v>1965.4</v>
       </c>
       <c r="P17" s="1">
-        <v>11.38</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="Q17" s="1">
-        <v>92628</v>
+        <v>40440</v>
       </c>
       <c r="R17" s="1">
-        <v>92628</v>
+        <v>40440</v>
       </c>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
       <c r="U17" s="1">
-        <v>4.6500000000000004</v>
+        <v>2</v>
       </c>
       <c r="V17" s="1">
         <v>0</v>
@@ -1439,48 +1522,48 @@
         <v>0</v>
       </c>
       <c r="F18" s="1">
-        <v>172500</v>
+        <v>93000</v>
       </c>
       <c r="G18" s="1">
-        <v>12.3</v>
+        <v>105.1</v>
       </c>
       <c r="H18" t="s">
         <v>2</v>
       </c>
       <c r="I18" s="1">
-        <v>517.5</v>
+        <v>1025.21</v>
       </c>
       <c r="J18" s="1">
-        <v>2.5</v>
+        <v>1.06</v>
       </c>
       <c r="K18" s="1">
-        <v>18.760000000000002</v>
+        <v>92.69</v>
       </c>
       <c r="L18" s="1">
-        <v>18.78</v>
+        <v>89.42</v>
       </c>
       <c r="M18" s="1">
-        <v>-11136.42</v>
+        <v>11538.88</v>
       </c>
       <c r="N18" s="1">
-        <v>-34.42</v>
+        <v>13.38</v>
       </c>
       <c r="O18" s="1">
-        <v>-11169.67</v>
+        <v>14585.2</v>
       </c>
       <c r="P18" s="1">
-        <v>-34.479999999999997</v>
+        <v>17.53</v>
       </c>
       <c r="Q18" s="1">
-        <v>21217.5</v>
+        <v>97743</v>
       </c>
       <c r="R18" s="1">
-        <v>21217.5</v>
+        <v>97743</v>
       </c>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
       <c r="U18" s="1">
-        <v>1.06</v>
+        <v>4.83</v>
       </c>
       <c r="V18" s="1">
         <v>0</v>
@@ -1506,48 +1589,48 @@
         <v>0</v>
       </c>
       <c r="F19" s="1">
-        <v>143</v>
+        <v>172500</v>
       </c>
       <c r="G19" s="1">
-        <v>9435</v>
+        <v>12.1</v>
       </c>
       <c r="H19" t="s">
         <v>2</v>
       </c>
       <c r="I19" s="1">
-        <v>119.02</v>
+        <v>0</v>
       </c>
       <c r="J19" s="1">
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>29153.85</v>
+        <v>18.760000000000002</v>
       </c>
       <c r="L19" s="1">
-        <v>29236.080000000002</v>
+        <v>18.78</v>
       </c>
       <c r="M19" s="1">
-        <v>-28197.96</v>
+        <v>-11481.42</v>
       </c>
       <c r="N19" s="1">
-        <v>-67.63</v>
+        <v>-35.479999999999997</v>
       </c>
       <c r="O19" s="1">
-        <v>-28315.55</v>
+        <v>-11514.67</v>
       </c>
       <c r="P19" s="1">
-        <v>-67.72</v>
+        <v>-35.549999999999997</v>
       </c>
       <c r="Q19" s="1">
-        <v>13492.05</v>
+        <v>20872.5</v>
       </c>
       <c r="R19" s="1">
-        <v>13492.05</v>
+        <v>20872.5</v>
       </c>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
       <c r="U19" s="1">
-        <v>0.68</v>
+        <v>1.03</v>
       </c>
       <c r="V19" s="1">
         <v>0</v>
@@ -1573,48 +1656,48 @@
         <v>0</v>
       </c>
       <c r="F20" s="1">
-        <v>2200</v>
+        <v>143</v>
       </c>
       <c r="G20" s="1">
-        <v>1018</v>
+        <v>9610</v>
       </c>
       <c r="H20" t="s">
         <v>2</v>
       </c>
       <c r="I20" s="1">
-        <v>-176.06</v>
+        <v>1012.05</v>
       </c>
       <c r="J20" s="1">
-        <v>-0.78</v>
+        <v>7.95</v>
       </c>
       <c r="K20" s="1">
-        <v>1374</v>
+        <v>29153.85</v>
       </c>
       <c r="L20" s="1">
-        <v>1375.24</v>
+        <v>29236.080000000002</v>
       </c>
       <c r="M20" s="1">
-        <v>-7832</v>
+        <v>-27947.71</v>
       </c>
       <c r="N20" s="1">
-        <v>-25.9</v>
+        <v>-67.03</v>
       </c>
       <c r="O20" s="1">
-        <v>-7859.21</v>
+        <v>-28065.3</v>
       </c>
       <c r="P20" s="1">
-        <v>-25.97</v>
+        <v>-67.12</v>
       </c>
       <c r="Q20" s="1">
-        <v>22396</v>
+        <v>13742.3</v>
       </c>
       <c r="R20" s="1">
-        <v>22396</v>
+        <v>13742.3</v>
       </c>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
       <c r="U20" s="1">
-        <v>1.1200000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="V20" s="1">
         <v>0</v>
@@ -1640,48 +1723,48 @@
         <v>0</v>
       </c>
       <c r="F21" s="1">
-        <v>1000</v>
+        <v>2200</v>
       </c>
       <c r="G21" s="1">
-        <v>54.6</v>
+        <v>1117</v>
       </c>
       <c r="H21" t="s">
         <v>2</v>
       </c>
       <c r="I21" s="1">
-        <v>18</v>
+        <v>639.05999999999995</v>
       </c>
       <c r="J21" s="1">
-        <v>3.41</v>
+        <v>2.67</v>
       </c>
       <c r="K21" s="1">
-        <v>55</v>
+        <v>1374</v>
       </c>
       <c r="L21" s="1">
-        <v>55.45</v>
+        <v>1375.24</v>
       </c>
       <c r="M21" s="1">
-        <v>-4</v>
+        <v>-5654</v>
       </c>
       <c r="N21" s="1">
-        <v>-0.72</v>
+        <v>-18.7</v>
       </c>
       <c r="O21" s="1">
-        <v>-8.5</v>
+        <v>-5681.21</v>
       </c>
       <c r="P21" s="1">
-        <v>-1.53</v>
+        <v>-18.77</v>
       </c>
       <c r="Q21" s="1">
-        <v>546</v>
+        <v>24574</v>
       </c>
       <c r="R21" s="1">
-        <v>546</v>
+        <v>24574</v>
       </c>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
       <c r="U21" s="1">
-        <v>0.03</v>
+        <v>1.22</v>
       </c>
       <c r="V21" s="1">
         <v>0</v>
@@ -1707,48 +1790,48 @@
         <v>0</v>
       </c>
       <c r="F22" s="1">
-        <v>15000</v>
+        <v>1000</v>
       </c>
       <c r="G22" s="1">
-        <v>170.6</v>
+        <v>58.9</v>
       </c>
       <c r="H22" t="s">
         <v>2</v>
       </c>
       <c r="I22" s="1">
-        <v>1050.3</v>
+        <v>-1</v>
       </c>
       <c r="J22" s="1">
-        <v>4.28</v>
+        <v>-0.17</v>
       </c>
       <c r="K22" s="1">
-        <v>317.23</v>
+        <v>55</v>
       </c>
       <c r="L22" s="1">
-        <v>318.69</v>
+        <v>55.45</v>
       </c>
       <c r="M22" s="1">
-        <v>-21994.89</v>
+        <v>38.99</v>
       </c>
       <c r="N22" s="1">
-        <v>-46.22</v>
+        <v>7.09</v>
       </c>
       <c r="O22" s="1">
-        <v>-22212.98</v>
+        <v>34.5</v>
       </c>
       <c r="P22" s="1">
-        <v>-46.46</v>
+        <v>6.22</v>
       </c>
       <c r="Q22" s="1">
-        <v>25590</v>
+        <v>589</v>
       </c>
       <c r="R22" s="1">
-        <v>25590</v>
+        <v>589</v>
       </c>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
       <c r="U22" s="1">
-        <v>1.28</v>
+        <v>0.03</v>
       </c>
       <c r="V22" s="1">
         <v>0</v>
@@ -1774,48 +1857,48 @@
         <v>0</v>
       </c>
       <c r="F23" s="1">
-        <v>1350</v>
+        <v>15000</v>
       </c>
       <c r="G23" s="1">
-        <v>2221</v>
+        <v>233.6</v>
       </c>
       <c r="H23" t="s">
         <v>2</v>
       </c>
       <c r="I23" s="1">
-        <v>-229.62</v>
+        <v>1201.27</v>
       </c>
       <c r="J23" s="1">
-        <v>-0.76</v>
+        <v>3.55</v>
       </c>
       <c r="K23" s="1">
-        <v>2610.16</v>
+        <v>317.23</v>
       </c>
       <c r="L23" s="1">
-        <v>2758.41</v>
+        <v>318.69</v>
       </c>
       <c r="M23" s="1">
-        <v>-5253.71</v>
+        <v>-12544.89</v>
       </c>
       <c r="N23" s="1">
-        <v>-14.9</v>
+        <v>-26.36</v>
       </c>
       <c r="O23" s="1">
-        <v>-7254.98</v>
+        <v>-12762.98</v>
       </c>
       <c r="P23" s="1">
-        <v>-19.48</v>
+        <v>-26.69</v>
       </c>
       <c r="Q23" s="1">
-        <v>29983.5</v>
+        <v>35040</v>
       </c>
       <c r="R23" s="1">
-        <v>29983.5</v>
+        <v>35040</v>
       </c>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
       <c r="U23" s="1">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="V23" s="1">
         <v>0</v>
@@ -1841,48 +1924,48 @@
         <v>0</v>
       </c>
       <c r="F24" s="1">
-        <v>700</v>
+        <v>1350</v>
       </c>
       <c r="G24" s="1">
-        <v>4749</v>
+        <v>2250</v>
       </c>
       <c r="H24" t="s">
         <v>2</v>
       </c>
       <c r="I24" s="1">
-        <v>1477.11</v>
+        <v>297.76</v>
       </c>
       <c r="J24" s="1">
-        <v>4.6500000000000004</v>
+        <v>0.99</v>
       </c>
       <c r="K24" s="1">
-        <v>5582.59</v>
+        <v>2610.16</v>
       </c>
       <c r="L24" s="1">
-        <v>5657.95</v>
+        <v>2758.41</v>
       </c>
       <c r="M24" s="1">
-        <v>-5835.1</v>
+        <v>-4862.21</v>
       </c>
       <c r="N24" s="1">
-        <v>-14.93</v>
+        <v>-13.79</v>
       </c>
       <c r="O24" s="1">
-        <v>-6362.62</v>
+        <v>-6863.48</v>
       </c>
       <c r="P24" s="1">
-        <v>-16.059999999999999</v>
+        <v>-18.43</v>
       </c>
       <c r="Q24" s="1">
-        <v>33243</v>
+        <v>30375</v>
       </c>
       <c r="R24" s="1">
-        <v>33243</v>
+        <v>30375</v>
       </c>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
       <c r="U24" s="1">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="V24" s="1">
         <v>0</v>
@@ -1908,48 +1991,48 @@
         <v>0</v>
       </c>
       <c r="F25" s="1">
-        <v>2900</v>
+        <v>700</v>
       </c>
       <c r="G25" s="1">
-        <v>731.1</v>
+        <v>4520</v>
       </c>
       <c r="H25" t="s">
         <v>2</v>
       </c>
       <c r="I25" s="1">
-        <v>-316.32</v>
+        <v>294.64999999999998</v>
       </c>
       <c r="J25" s="1">
-        <v>-1.47</v>
+        <v>0.94</v>
       </c>
       <c r="K25" s="1">
-        <v>998</v>
+        <v>5582.59</v>
       </c>
       <c r="L25" s="1">
-        <v>998.9</v>
+        <v>5657.95</v>
       </c>
       <c r="M25" s="1">
-        <v>-7740.1</v>
+        <v>-7438.1</v>
       </c>
       <c r="N25" s="1">
-        <v>-26.74</v>
+        <v>-19.03</v>
       </c>
       <c r="O25" s="1">
-        <v>-7766.15</v>
+        <v>-7965.62</v>
       </c>
       <c r="P25" s="1">
-        <v>-26.8</v>
+        <v>-20.11</v>
       </c>
       <c r="Q25" s="1">
-        <v>21201.9</v>
+        <v>31640</v>
       </c>
       <c r="R25" s="1">
-        <v>21201.9</v>
+        <v>31640</v>
       </c>
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
       <c r="U25" s="1">
-        <v>1.06</v>
+        <v>1.56</v>
       </c>
       <c r="V25" s="1">
         <v>0</v>
@@ -1975,48 +2058,48 @@
         <v>0</v>
       </c>
       <c r="F26" s="1">
-        <v>252849</v>
+        <v>2900</v>
       </c>
       <c r="G26" s="1">
-        <v>36.200000000000003</v>
+        <v>770</v>
       </c>
       <c r="H26" t="s">
         <v>2</v>
       </c>
       <c r="I26" s="1">
-        <v>0</v>
+        <v>157.43</v>
       </c>
       <c r="J26" s="1">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="K26" s="1">
-        <v>40</v>
+        <v>998</v>
       </c>
       <c r="L26" s="1">
-        <v>40.04</v>
+        <v>998.9</v>
       </c>
       <c r="M26" s="1">
-        <v>-9598.14</v>
+        <v>-6612</v>
       </c>
       <c r="N26" s="1">
-        <v>-9.49</v>
+        <v>-22.84</v>
       </c>
       <c r="O26" s="1">
-        <v>-9695.41</v>
+        <v>-6638.05</v>
       </c>
       <c r="P26" s="1">
-        <v>-9.57</v>
+        <v>-22.91</v>
       </c>
       <c r="Q26" s="1">
-        <v>91531.34</v>
+        <v>22330</v>
       </c>
       <c r="R26" s="1">
-        <v>91531.34</v>
+        <v>22330</v>
       </c>
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
       <c r="U26" s="1">
-        <v>4.59</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="V26" s="1">
         <v>0</v>
@@ -2042,10 +2125,10 @@
         <v>0</v>
       </c>
       <c r="F27" s="1">
-        <v>20000</v>
+        <v>252849</v>
       </c>
       <c r="G27" s="1">
-        <v>74</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="H27" t="s">
         <v>2</v>
@@ -2057,33 +2140,33 @@
         <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>109.9</v>
+        <v>40</v>
       </c>
       <c r="L27" s="1">
-        <v>110</v>
+        <v>40.04</v>
       </c>
       <c r="M27" s="1">
-        <v>-7180</v>
+        <v>-9598.14</v>
       </c>
       <c r="N27" s="1">
-        <v>-32.659999999999997</v>
+        <v>-9.49</v>
       </c>
       <c r="O27" s="1">
-        <v>-7199.78</v>
+        <v>-9695.41</v>
       </c>
       <c r="P27" s="1">
-        <v>-32.72</v>
+        <v>-9.57</v>
       </c>
       <c r="Q27" s="1">
-        <v>14800</v>
+        <v>91531.34</v>
       </c>
       <c r="R27" s="1">
-        <v>14800</v>
+        <v>91531.34</v>
       </c>
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
       <c r="U27" s="1">
-        <v>0.74</v>
+        <v>4.53</v>
       </c>
       <c r="V27" s="1">
         <v>0</v>
@@ -2109,48 +2192,48 @@
         <v>0</v>
       </c>
       <c r="F28" s="1">
-        <v>500</v>
+        <v>20000</v>
       </c>
       <c r="G28" s="1">
-        <v>4534</v>
+        <v>94.8</v>
       </c>
       <c r="H28" t="s">
         <v>2</v>
       </c>
       <c r="I28" s="1">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="J28" s="1">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>4481.99</v>
+        <v>109.9</v>
       </c>
       <c r="L28" s="1">
-        <v>4486.0200000000004</v>
+        <v>110</v>
       </c>
       <c r="M28" s="1">
-        <v>260.06</v>
+        <v>-3020</v>
       </c>
       <c r="N28" s="1">
-        <v>1.1599999999999999</v>
+        <v>-13.73</v>
       </c>
       <c r="O28" s="1">
-        <v>239.91</v>
+        <v>-3039.78</v>
       </c>
       <c r="P28" s="1">
-        <v>1.06</v>
+        <v>-13.81</v>
       </c>
       <c r="Q28" s="1">
-        <v>22670</v>
+        <v>18960</v>
       </c>
       <c r="R28" s="1">
-        <v>22670</v>
+        <v>18960</v>
       </c>
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
       <c r="U28" s="1">
-        <v>1.1399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="V28" s="1">
         <v>0</v>
@@ -2164,10 +2247,10 @@
         <v>0</v>
       </c>
       <c r="B29" t="s">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="C29" t="s">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="D29" t="s">
         <v>0</v>
@@ -2175,55 +2258,51 @@
       <c r="E29" t="s">
         <v>0</v>
       </c>
-      <c r="F29" t="s">
-        <v>0</v>
-      </c>
-      <c r="G29" t="s">
-        <v>0</v>
+      <c r="F29" s="1">
+        <v>500</v>
+      </c>
+      <c r="G29" s="1">
+        <v>4563</v>
       </c>
       <c r="H29" t="s">
-        <v>0</v>
-      </c>
-      <c r="I29" t="s">
-        <v>0</v>
-      </c>
-      <c r="J29" t="s">
-        <v>0</v>
-      </c>
-      <c r="K29" t="s">
-        <v>0</v>
-      </c>
-      <c r="L29" t="s">
-        <v>0</v>
-      </c>
-      <c r="M29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N29" t="s">
-        <v>0</v>
-      </c>
-      <c r="O29" t="s">
-        <v>0</v>
-      </c>
-      <c r="P29" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>0</v>
-      </c>
-      <c r="R29" t="s">
-        <v>0</v>
-      </c>
-      <c r="S29" t="s">
-        <v>0</v>
-      </c>
-      <c r="T29" t="s">
-        <v>0</v>
-      </c>
-      <c r="U29" t="s">
-        <v>0</v>
-      </c>
-      <c r="V29" t="s">
+        <v>2</v>
+      </c>
+      <c r="I29" s="1">
+        <v>99.95</v>
+      </c>
+      <c r="J29" s="1">
+        <v>0.44</v>
+      </c>
+      <c r="K29" s="1">
+        <v>4481.99</v>
+      </c>
+      <c r="L29" s="1">
+        <v>4486.0200000000004</v>
+      </c>
+      <c r="M29" s="1">
+        <v>405.06</v>
+      </c>
+      <c r="N29" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="O29" s="1">
+        <v>384.91</v>
+      </c>
+      <c r="P29" s="1">
+        <v>1.71</v>
+      </c>
+      <c r="Q29" s="1">
+        <v>22815</v>
+      </c>
+      <c r="R29" s="1">
+        <v>22815</v>
+      </c>
+      <c r="S29" s="1"/>
+      <c r="T29" s="1"/>
+      <c r="U29" s="1">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="V29" s="1">
         <v>0</v>
       </c>
       <c r="W29" t="s">
@@ -2235,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="B30" t="s">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="C30" t="s">
         <v>0</v>
@@ -2279,8 +2358,8 @@
       <c r="P30" t="s">
         <v>0</v>
       </c>
-      <c r="Q30" s="1">
-        <v>467528.25</v>
+      <c r="Q30" t="s">
+        <v>0</v>
       </c>
       <c r="R30" t="s">
         <v>0</v>
@@ -2306,7 +2385,7 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="C31" t="s">
         <v>0</v>
@@ -2350,8 +2429,8 @@
       <c r="P31" t="s">
         <v>0</v>
       </c>
-      <c r="Q31" t="s">
-        <v>0</v>
+      <c r="Q31" s="1">
+        <v>515564.94</v>
       </c>
       <c r="R31" t="s">
         <v>0</v>
@@ -2377,7 +2456,7 @@
         <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="C32" t="s">
         <v>0</v>
@@ -2448,10 +2527,10 @@
         <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C33" t="s">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D33" t="s">
         <v>0</v>
@@ -2459,51 +2538,55 @@
       <c r="E33" t="s">
         <v>0</v>
       </c>
-      <c r="F33" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G33" s="1">
-        <v>121.05</v>
+      <c r="F33" t="s">
+        <v>0</v>
+      </c>
+      <c r="G33" t="s">
+        <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>2</v>
-      </c>
-      <c r="I33" s="1">
-        <v>-3.63</v>
-      </c>
-      <c r="J33" s="1">
-        <v>-0.01</v>
-      </c>
-      <c r="K33" s="1">
-        <v>120.64</v>
-      </c>
-      <c r="L33" s="1">
-        <v>120.76</v>
-      </c>
-      <c r="M33" s="1">
-        <v>123.11</v>
-      </c>
-      <c r="N33" s="1">
-        <v>0.34</v>
-      </c>
-      <c r="O33" s="1">
-        <v>86.23</v>
-      </c>
-      <c r="P33" s="1">
-        <v>0.23</v>
-      </c>
-      <c r="Q33" s="1">
-        <v>36315</v>
-      </c>
-      <c r="R33" s="1">
-        <v>36315</v>
-      </c>
-      <c r="S33" s="1"/>
-      <c r="T33" s="1"/>
-      <c r="U33" s="1">
-        <v>1.82</v>
-      </c>
-      <c r="V33" s="1">
+        <v>0</v>
+      </c>
+      <c r="I33" t="s">
+        <v>0</v>
+      </c>
+      <c r="J33" t="s">
+        <v>0</v>
+      </c>
+      <c r="K33" t="s">
+        <v>0</v>
+      </c>
+      <c r="L33" t="s">
+        <v>0</v>
+      </c>
+      <c r="M33" t="s">
+        <v>0</v>
+      </c>
+      <c r="N33" t="s">
+        <v>0</v>
+      </c>
+      <c r="O33" t="s">
+        <v>0</v>
+      </c>
+      <c r="P33" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>0</v>
+      </c>
+      <c r="R33" t="s">
+        <v>0</v>
+      </c>
+      <c r="S33" t="s">
+        <v>0</v>
+      </c>
+      <c r="T33" t="s">
+        <v>0</v>
+      </c>
+      <c r="U33" t="s">
+        <v>0</v>
+      </c>
+      <c r="V33" t="s">
         <v>0</v>
       </c>
       <c r="W33" t="s">
@@ -2527,48 +2610,48 @@
         <v>0</v>
       </c>
       <c r="F34" s="1">
-        <v>75688.77</v>
+        <v>30000</v>
       </c>
       <c r="G34" s="1">
-        <v>89.61</v>
+        <v>121.15</v>
       </c>
       <c r="H34" t="s">
         <v>2</v>
       </c>
       <c r="I34" s="1">
-        <v>20.34</v>
+        <v>0</v>
       </c>
       <c r="J34" s="1">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>74.53</v>
+        <v>120.64</v>
       </c>
       <c r="L34" s="1">
-        <v>81.37</v>
+        <v>120.76</v>
       </c>
       <c r="M34" s="1">
-        <v>11417.8</v>
+        <v>153.11000000000001</v>
       </c>
       <c r="N34" s="1">
-        <v>20.239999999999998</v>
+        <v>0.42</v>
       </c>
       <c r="O34" s="1">
-        <v>6236.79</v>
+        <v>116.23</v>
       </c>
       <c r="P34" s="1">
-        <v>10.119999999999999</v>
+        <v>0.32</v>
       </c>
       <c r="Q34" s="1">
-        <v>67824.710000000006</v>
+        <v>36345</v>
       </c>
       <c r="R34" s="1">
-        <v>67824.710000000006</v>
+        <v>36345</v>
       </c>
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
       <c r="U34" s="1">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="V34" s="1">
         <v>0</v>
@@ -2594,48 +2677,48 @@
         <v>0</v>
       </c>
       <c r="F35" s="1">
-        <v>50000</v>
+        <v>75688.77</v>
       </c>
       <c r="G35" s="1">
-        <v>103.89</v>
+        <v>89.6</v>
       </c>
       <c r="H35" t="s">
         <v>2</v>
       </c>
       <c r="I35" s="1">
-        <v>442.92</v>
+        <v>-54.3</v>
       </c>
       <c r="J35" s="1">
-        <v>0.86</v>
+        <v>-0.08</v>
       </c>
       <c r="K35" s="1">
-        <v>99.28</v>
+        <v>74.53</v>
       </c>
       <c r="L35" s="1">
-        <v>102.54</v>
+        <v>81.37</v>
       </c>
       <c r="M35" s="1">
-        <v>2303.69</v>
+        <v>11410.23</v>
       </c>
       <c r="N35" s="1">
-        <v>4.6399999999999997</v>
+        <v>20.22</v>
       </c>
       <c r="O35" s="1">
-        <v>676.4</v>
+        <v>6229.22</v>
       </c>
       <c r="P35" s="1">
-        <v>1.31</v>
+        <v>10.11</v>
       </c>
       <c r="Q35" s="1">
-        <v>51945</v>
+        <v>67817.14</v>
       </c>
       <c r="R35" s="1">
-        <v>51945</v>
+        <v>67817.14</v>
       </c>
       <c r="S35" s="1"/>
       <c r="T35" s="1"/>
       <c r="U35" s="1">
-        <v>2.61</v>
+        <v>3.35</v>
       </c>
       <c r="V35" s="1">
         <v>0</v>
@@ -2661,48 +2744,48 @@
         <v>0</v>
       </c>
       <c r="F36" s="1">
-        <v>25000</v>
+        <v>50000</v>
       </c>
       <c r="G36" s="1">
-        <v>100</v>
+        <v>103.63</v>
       </c>
       <c r="H36" t="s">
         <v>2</v>
       </c>
       <c r="I36" s="1">
-        <v>129.33000000000001</v>
+        <v>0</v>
       </c>
       <c r="J36" s="1">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
-        <v>97.53</v>
+        <v>99.28</v>
       </c>
       <c r="L36" s="1">
-        <v>100.91</v>
+        <v>102.54</v>
       </c>
       <c r="M36" s="1">
-        <v>618.47</v>
+        <v>2173.69</v>
       </c>
       <c r="N36" s="1">
-        <v>2.5299999999999998</v>
+        <v>4.37</v>
       </c>
       <c r="O36" s="1">
-        <v>-227.97</v>
+        <v>546.4</v>
       </c>
       <c r="P36" s="1">
-        <v>-0.9</v>
+        <v>1.06</v>
       </c>
       <c r="Q36" s="1">
-        <v>25000</v>
+        <v>51815</v>
       </c>
       <c r="R36" s="1">
-        <v>25000</v>
+        <v>51815</v>
       </c>
       <c r="S36" s="1"/>
       <c r="T36" s="1"/>
       <c r="U36" s="1">
-        <v>1.25</v>
+        <v>2.56</v>
       </c>
       <c r="V36" s="1">
         <v>0</v>
@@ -2728,48 +2811,48 @@
         <v>0</v>
       </c>
       <c r="F37" s="1">
-        <v>80257.09</v>
+        <v>25000</v>
       </c>
       <c r="G37" s="1">
-        <v>112.23</v>
+        <v>99.16</v>
       </c>
       <c r="H37" t="s">
         <v>2</v>
       </c>
       <c r="I37" s="1">
-        <v>-18.02</v>
+        <v>-72.099999999999994</v>
       </c>
       <c r="J37" s="1">
-        <v>-0.02</v>
+        <v>-0.28999999999999998</v>
       </c>
       <c r="K37" s="1">
-        <v>94.06</v>
+        <v>97.53</v>
       </c>
       <c r="L37" s="1">
-        <v>99.76</v>
+        <v>100.91</v>
       </c>
       <c r="M37" s="1">
-        <v>14579.74</v>
+        <v>408.47</v>
       </c>
       <c r="N37" s="1">
-        <v>19.309999999999999</v>
+        <v>1.67</v>
       </c>
       <c r="O37" s="1">
-        <v>10011.18</v>
+        <v>-437.97</v>
       </c>
       <c r="P37" s="1">
-        <v>12.5</v>
+        <v>-1.73</v>
       </c>
       <c r="Q37" s="1">
-        <v>90072.53</v>
+        <v>24790</v>
       </c>
       <c r="R37" s="1">
-        <v>90072.53</v>
+        <v>24790</v>
       </c>
       <c r="S37" s="1"/>
       <c r="T37" s="1"/>
       <c r="U37" s="1">
-        <v>4.5199999999999996</v>
+        <v>1.23</v>
       </c>
       <c r="V37" s="1">
         <v>0</v>
@@ -2795,48 +2878,48 @@
         <v>0</v>
       </c>
       <c r="F38" s="1">
-        <v>23000</v>
+        <v>80257.09</v>
       </c>
       <c r="G38" s="1">
-        <v>120.82</v>
+        <v>112.36</v>
       </c>
       <c r="H38" t="s">
         <v>2</v>
       </c>
       <c r="I38" s="1">
-        <v>2.78</v>
+        <v>81.09</v>
       </c>
       <c r="J38" s="1">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="K38" s="1">
-        <v>120.19</v>
+        <v>94.06</v>
       </c>
       <c r="L38" s="1">
-        <v>120.3</v>
+        <v>99.76</v>
       </c>
       <c r="M38" s="1">
-        <v>144.88999999999999</v>
+        <v>14684.07</v>
       </c>
       <c r="N38" s="1">
-        <v>0.52</v>
+        <v>19.45</v>
       </c>
       <c r="O38" s="1">
-        <v>120.02</v>
+        <v>10115.52</v>
       </c>
       <c r="P38" s="1">
-        <v>0.43</v>
+        <v>12.63</v>
       </c>
       <c r="Q38" s="1">
-        <v>27788.6</v>
+        <v>90176.87</v>
       </c>
       <c r="R38" s="1">
-        <v>27788.6</v>
+        <v>90176.87</v>
       </c>
       <c r="S38" s="1"/>
       <c r="T38" s="1"/>
       <c r="U38" s="1">
-        <v>1.39</v>
+        <v>4.46</v>
       </c>
       <c r="V38" s="1">
         <v>0</v>
@@ -2862,48 +2945,48 @@
         <v>0</v>
       </c>
       <c r="F39" s="1">
-        <v>100000</v>
+        <v>23000</v>
       </c>
       <c r="G39" s="1">
-        <v>92.18</v>
+        <v>120.84</v>
       </c>
       <c r="H39" t="s">
         <v>2</v>
       </c>
       <c r="I39" s="1">
-        <v>-9.2200000000000006</v>
+        <v>-11.12</v>
       </c>
       <c r="J39" s="1">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="K39" s="1">
-        <v>74.83</v>
+        <v>120.19</v>
       </c>
       <c r="L39" s="1">
-        <v>82.14</v>
+        <v>120.3</v>
       </c>
       <c r="M39" s="1">
-        <v>17352.490000000002</v>
+        <v>149.49</v>
       </c>
       <c r="N39" s="1">
-        <v>23.19</v>
+        <v>0.54</v>
       </c>
       <c r="O39" s="1">
-        <v>10037.93</v>
+        <v>124.62</v>
       </c>
       <c r="P39" s="1">
-        <v>12.22</v>
+        <v>0.45</v>
       </c>
       <c r="Q39" s="1">
-        <v>92180</v>
+        <v>27793.200000000001</v>
       </c>
       <c r="R39" s="1">
-        <v>92180</v>
+        <v>27793.200000000001</v>
       </c>
       <c r="S39" s="1"/>
       <c r="T39" s="1"/>
       <c r="U39" s="1">
-        <v>4.63</v>
+        <v>1.37</v>
       </c>
       <c r="V39" s="1">
         <v>0</v>
@@ -2929,48 +3012,48 @@
         <v>0</v>
       </c>
       <c r="F40" s="1">
-        <v>45000</v>
+        <v>100000</v>
       </c>
       <c r="G40" s="1">
-        <v>101.59</v>
+        <v>92.34</v>
       </c>
       <c r="H40" t="s">
         <v>2</v>
       </c>
       <c r="I40" s="1">
-        <v>0</v>
+        <v>27.69</v>
       </c>
       <c r="J40" s="1">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="K40" s="1">
-        <v>102.23</v>
+        <v>74.83</v>
       </c>
       <c r="L40" s="1">
-        <v>102.33</v>
+        <v>82.14</v>
       </c>
       <c r="M40" s="1">
-        <v>-289.48</v>
+        <v>17512.490000000002</v>
       </c>
       <c r="N40" s="1">
-        <v>-0.62</v>
+        <v>23.4</v>
       </c>
       <c r="O40" s="1">
-        <v>-330.9</v>
+        <v>10197.93</v>
       </c>
       <c r="P40" s="1">
-        <v>-0.71</v>
+        <v>12.41</v>
       </c>
       <c r="Q40" s="1">
-        <v>45715.5</v>
+        <v>92340</v>
       </c>
       <c r="R40" s="1">
-        <v>45715.5</v>
+        <v>92340</v>
       </c>
       <c r="S40" s="1"/>
       <c r="T40" s="1"/>
       <c r="U40" s="1">
-        <v>2.29</v>
+        <v>4.57</v>
       </c>
       <c r="V40" s="1">
         <v>0</v>
@@ -2996,48 +3079,48 @@
         <v>0</v>
       </c>
       <c r="F41" s="1">
-        <v>25133</v>
+        <v>45000</v>
       </c>
       <c r="G41" s="1">
-        <v>101.1</v>
+        <v>99.91</v>
       </c>
       <c r="H41" t="s">
         <v>2</v>
       </c>
       <c r="I41" s="1">
-        <v>-10.17</v>
+        <v>-112.68</v>
       </c>
       <c r="J41" s="1">
-        <v>-0.04</v>
+        <v>-0.25</v>
       </c>
       <c r="K41" s="1">
-        <v>97.53</v>
+        <v>102.23</v>
       </c>
       <c r="L41" s="1">
-        <v>99.56</v>
+        <v>102.33</v>
       </c>
       <c r="M41" s="1">
-        <v>897.7</v>
+        <v>-1045.48</v>
       </c>
       <c r="N41" s="1">
-        <v>3.66</v>
+        <v>-2.27</v>
       </c>
       <c r="O41" s="1">
-        <v>387.16</v>
+        <v>-1086.9000000000001</v>
       </c>
       <c r="P41" s="1">
-        <v>1.54</v>
+        <v>-2.36</v>
       </c>
       <c r="Q41" s="1">
-        <v>25409.46</v>
+        <v>44959.5</v>
       </c>
       <c r="R41" s="1">
-        <v>25409.46</v>
+        <v>44959.5</v>
       </c>
       <c r="S41" s="1"/>
       <c r="T41" s="1"/>
       <c r="U41" s="1">
-        <v>1.28</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="V41" s="1">
         <v>0</v>
@@ -3063,10 +3146,10 @@
         <v>0</v>
       </c>
       <c r="F42" s="1">
-        <v>40000</v>
+        <v>30000</v>
       </c>
       <c r="G42" s="1">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H42" t="s">
         <v>2</v>
@@ -3078,33 +3161,33 @@
         <v>0</v>
       </c>
       <c r="K42" s="1">
-        <v>84.49</v>
+        <v>99</v>
       </c>
       <c r="L42" s="1">
-        <v>94.72</v>
+        <v>99.09</v>
       </c>
       <c r="M42" s="1">
-        <v>4603.63</v>
+        <v>0</v>
       </c>
       <c r="N42" s="1">
-        <v>13.62</v>
+        <v>0</v>
       </c>
       <c r="O42" s="1">
-        <v>512.16</v>
+        <v>-26.73</v>
       </c>
       <c r="P42" s="1">
-        <v>1.35</v>
+        <v>-0.08</v>
       </c>
       <c r="Q42" s="1">
-        <v>38400</v>
+        <v>29700</v>
       </c>
       <c r="R42" s="1">
-        <v>38400</v>
+        <v>29700</v>
       </c>
       <c r="S42" s="1"/>
       <c r="T42" s="1"/>
       <c r="U42" s="1">
-        <v>1.93</v>
+        <v>1.47</v>
       </c>
       <c r="V42" s="1">
         <v>0</v>
@@ -3130,48 +3213,48 @@
         <v>0</v>
       </c>
       <c r="F43" s="1">
-        <v>41667.919999999998</v>
+        <v>25133</v>
       </c>
       <c r="G43" s="1">
-        <v>109.53</v>
+        <v>100.69</v>
       </c>
       <c r="H43" t="s">
         <v>2</v>
       </c>
       <c r="I43" s="1">
-        <v>4.5599999999999996</v>
+        <v>0</v>
       </c>
       <c r="J43" s="1">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="K43" s="1">
-        <v>107.93</v>
+        <v>97.53</v>
       </c>
       <c r="L43" s="1">
-        <v>108.14</v>
+        <v>99.56</v>
       </c>
       <c r="M43" s="1">
-        <v>668.51</v>
+        <v>794.65</v>
       </c>
       <c r="N43" s="1">
-        <v>1.48</v>
+        <v>3.24</v>
       </c>
       <c r="O43" s="1">
-        <v>580.33000000000004</v>
+        <v>284.12</v>
       </c>
       <c r="P43" s="1">
-        <v>1.28</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="Q43" s="1">
-        <v>45638.87</v>
+        <v>25306.42</v>
       </c>
       <c r="R43" s="1">
-        <v>45638.87</v>
+        <v>25306.42</v>
       </c>
       <c r="S43" s="1"/>
       <c r="T43" s="1"/>
       <c r="U43" s="1">
-        <v>2.29</v>
+        <v>1.25</v>
       </c>
       <c r="V43" s="1">
         <v>0</v>
@@ -3197,48 +3280,48 @@
         <v>0</v>
       </c>
       <c r="F44" s="1">
-        <v>61602</v>
+        <v>40000</v>
       </c>
       <c r="G44" s="1">
-        <v>96.81</v>
+        <v>96</v>
       </c>
       <c r="H44" t="s">
         <v>2</v>
       </c>
       <c r="I44" s="1">
-        <v>5.96</v>
+        <v>0</v>
       </c>
       <c r="J44" s="1">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="K44" s="1">
-        <v>86.1</v>
+        <v>84.49</v>
       </c>
       <c r="L44" s="1">
-        <v>88.3</v>
+        <v>94.72</v>
       </c>
       <c r="M44" s="1">
-        <v>6596.52</v>
+        <v>4603.63</v>
       </c>
       <c r="N44" s="1">
-        <v>12.43</v>
+        <v>13.62</v>
       </c>
       <c r="O44" s="1">
-        <v>5240.13</v>
+        <v>512.16</v>
       </c>
       <c r="P44" s="1">
-        <v>9.6300000000000008</v>
+        <v>1.35</v>
       </c>
       <c r="Q44" s="1">
-        <v>59636.9</v>
+        <v>38400</v>
       </c>
       <c r="R44" s="1">
-        <v>59636.9</v>
+        <v>38400</v>
       </c>
       <c r="S44" s="1"/>
       <c r="T44" s="1"/>
       <c r="U44" s="1">
-        <v>2.99</v>
+        <v>1.9</v>
       </c>
       <c r="V44" s="1">
         <v>0</v>
@@ -3264,48 +3347,48 @@
         <v>0</v>
       </c>
       <c r="F45" s="1">
-        <v>57435.9</v>
+        <v>41667.919999999998</v>
       </c>
       <c r="G45" s="1">
-        <v>119.18</v>
+        <v>109.78</v>
       </c>
       <c r="H45" t="s">
         <v>2</v>
       </c>
       <c r="I45" s="1">
-        <v>-6.85</v>
+        <v>54.83</v>
       </c>
       <c r="J45" s="1">
-        <v>-0.01</v>
+        <v>0.12</v>
       </c>
       <c r="K45" s="1">
-        <v>106.92</v>
+        <v>107.93</v>
       </c>
       <c r="L45" s="1">
-        <v>110.63</v>
+        <v>108.14</v>
       </c>
       <c r="M45" s="1">
-        <v>7041.35</v>
+        <v>772.68</v>
       </c>
       <c r="N45" s="1">
-        <v>11.46</v>
+        <v>1.71</v>
       </c>
       <c r="O45" s="1">
-        <v>4908.42</v>
+        <v>684.5</v>
       </c>
       <c r="P45" s="1">
-        <v>7.72</v>
+        <v>1.51</v>
       </c>
       <c r="Q45" s="1">
-        <v>68452.11</v>
+        <v>45743.040000000001</v>
       </c>
       <c r="R45" s="1">
-        <v>68452.11</v>
+        <v>45743.040000000001</v>
       </c>
       <c r="S45" s="1"/>
       <c r="T45" s="1"/>
       <c r="U45" s="1">
-        <v>3.43</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="V45" s="1">
         <v>0</v>
@@ -3331,48 +3414,48 @@
         <v>0</v>
       </c>
       <c r="F46" s="1">
-        <v>45000</v>
+        <v>61602</v>
       </c>
       <c r="G46" s="1">
-        <v>104.15</v>
+        <v>96.58</v>
       </c>
       <c r="H46" t="s">
         <v>2</v>
       </c>
       <c r="I46" s="1">
-        <v>0</v>
+        <v>71.31</v>
       </c>
       <c r="J46" s="1">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="K46" s="1">
-        <v>101.08</v>
+        <v>86.1</v>
       </c>
       <c r="L46" s="1">
-        <v>106.6</v>
+        <v>88.3</v>
       </c>
       <c r="M46" s="1">
-        <v>1382.48</v>
+        <v>6454.84</v>
       </c>
       <c r="N46" s="1">
-        <v>3.03</v>
+        <v>12.16</v>
       </c>
       <c r="O46" s="1">
-        <v>-1100.6199999999999</v>
+        <v>5098.4399999999996</v>
       </c>
       <c r="P46" s="1">
-        <v>-2.29</v>
+        <v>9.3699999999999992</v>
       </c>
       <c r="Q46" s="1">
-        <v>46867.5</v>
+        <v>59495.21</v>
       </c>
       <c r="R46" s="1">
-        <v>46867.5</v>
+        <v>59495.21</v>
       </c>
       <c r="S46" s="1"/>
       <c r="T46" s="1"/>
       <c r="U46" s="1">
-        <v>2.35</v>
+        <v>2.94</v>
       </c>
       <c r="V46" s="1">
         <v>0</v>
@@ -3398,48 +3481,48 @@
         <v>0</v>
       </c>
       <c r="F47" s="1">
-        <v>40000</v>
+        <v>57435.9</v>
       </c>
       <c r="G47" s="1">
-        <v>118.74</v>
+        <v>119.3</v>
       </c>
       <c r="H47" t="s">
         <v>2</v>
       </c>
       <c r="I47" s="1">
-        <v>-14.25</v>
+        <v>54.77</v>
       </c>
       <c r="J47" s="1">
-        <v>-0.03</v>
+        <v>0.08</v>
       </c>
       <c r="K47" s="1">
-        <v>109.11</v>
+        <v>106.92</v>
       </c>
       <c r="L47" s="1">
-        <v>111.45</v>
+        <v>110.63</v>
       </c>
       <c r="M47" s="1">
-        <v>3853.39</v>
+        <v>7110.27</v>
       </c>
       <c r="N47" s="1">
-        <v>8.82</v>
+        <v>11.57</v>
       </c>
       <c r="O47" s="1">
-        <v>2917.07</v>
+        <v>4977.34</v>
       </c>
       <c r="P47" s="1">
-        <v>6.54</v>
+        <v>7.83</v>
       </c>
       <c r="Q47" s="1">
-        <v>47496</v>
+        <v>68521.03</v>
       </c>
       <c r="R47" s="1">
-        <v>47496</v>
+        <v>68521.03</v>
       </c>
       <c r="S47" s="1"/>
       <c r="T47" s="1"/>
       <c r="U47" s="1">
-        <v>2.38</v>
+        <v>3.39</v>
       </c>
       <c r="V47" s="1">
         <v>0</v>
@@ -3465,48 +3548,48 @@
         <v>0</v>
       </c>
       <c r="F48" s="1">
-        <v>24000</v>
+        <v>45000</v>
       </c>
       <c r="G48" s="1">
-        <v>121.38</v>
+        <v>104.1</v>
       </c>
       <c r="H48" t="s">
         <v>2</v>
       </c>
       <c r="I48" s="1">
-        <v>11.65</v>
+        <v>28.09</v>
       </c>
       <c r="J48" s="1">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="K48" s="1">
-        <v>121</v>
+        <v>101.08</v>
       </c>
       <c r="L48" s="1">
-        <v>121.13</v>
+        <v>106.6</v>
       </c>
       <c r="M48" s="1">
-        <v>91.19</v>
+        <v>1359.98</v>
       </c>
       <c r="N48" s="1">
-        <v>0.31</v>
+        <v>2.98</v>
       </c>
       <c r="O48" s="1">
-        <v>60.61</v>
+        <v>-1123.1199999999999</v>
       </c>
       <c r="P48" s="1">
-        <v>0.2</v>
+        <v>-2.34</v>
       </c>
       <c r="Q48" s="1">
-        <v>29131.200000000001</v>
+        <v>46845</v>
       </c>
       <c r="R48" s="1">
-        <v>29131.200000000001</v>
+        <v>46845</v>
       </c>
       <c r="S48" s="1"/>
       <c r="T48" s="1"/>
       <c r="U48" s="1">
-        <v>1.46</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="V48" s="1">
         <v>0</v>
@@ -3535,45 +3618,45 @@
         <v>40000</v>
       </c>
       <c r="G49" s="1">
-        <v>142.5</v>
+        <v>118.8</v>
       </c>
       <c r="H49" t="s">
         <v>2</v>
       </c>
       <c r="I49" s="1">
-        <v>2480.63</v>
+        <v>0</v>
       </c>
       <c r="J49" s="1">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="K49" s="1">
-        <v>121.85</v>
+        <v>109.11</v>
       </c>
       <c r="L49" s="1">
-        <v>124.61</v>
+        <v>111.45</v>
       </c>
       <c r="M49" s="1">
-        <v>8259.99</v>
+        <v>3877.39</v>
       </c>
       <c r="N49" s="1">
-        <v>16.940000000000001</v>
+        <v>8.8800000000000008</v>
       </c>
       <c r="O49" s="1">
-        <v>7155.17</v>
+        <v>2941.07</v>
       </c>
       <c r="P49" s="1">
-        <v>14.35</v>
+        <v>6.59</v>
       </c>
       <c r="Q49" s="1">
-        <v>57000</v>
+        <v>47520</v>
       </c>
       <c r="R49" s="1">
-        <v>57000</v>
+        <v>47520</v>
       </c>
       <c r="S49" s="1"/>
       <c r="T49" s="1"/>
       <c r="U49" s="1">
-        <v>2.86</v>
+        <v>2.35</v>
       </c>
       <c r="V49" s="1">
         <v>0</v>
@@ -3587,10 +3670,10 @@
         <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="C50" t="s">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="D50" t="s">
         <v>0</v>
@@ -3598,55 +3681,51 @@
       <c r="E50" t="s">
         <v>0</v>
       </c>
-      <c r="F50" t="s">
-        <v>0</v>
-      </c>
-      <c r="G50" t="s">
-        <v>0</v>
+      <c r="F50" s="1">
+        <v>24000</v>
+      </c>
+      <c r="G50" s="1">
+        <v>121.52</v>
       </c>
       <c r="H50" t="s">
-        <v>0</v>
-      </c>
-      <c r="I50" t="s">
-        <v>0</v>
-      </c>
-      <c r="J50" t="s">
-        <v>0</v>
-      </c>
-      <c r="K50" t="s">
-        <v>0</v>
-      </c>
-      <c r="L50" t="s">
-        <v>0</v>
-      </c>
-      <c r="M50" t="s">
-        <v>0</v>
-      </c>
-      <c r="N50" t="s">
-        <v>0</v>
-      </c>
-      <c r="O50" t="s">
-        <v>0</v>
-      </c>
-      <c r="P50" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>0</v>
-      </c>
-      <c r="R50" t="s">
-        <v>0</v>
-      </c>
-      <c r="S50" t="s">
-        <v>0</v>
-      </c>
-      <c r="T50" t="s">
-        <v>0</v>
-      </c>
-      <c r="U50" t="s">
-        <v>0</v>
-      </c>
-      <c r="V50" t="s">
+        <v>2</v>
+      </c>
+      <c r="I50" s="1">
+        <v>0</v>
+      </c>
+      <c r="J50" s="1">
+        <v>0</v>
+      </c>
+      <c r="K50" s="1">
+        <v>121</v>
+      </c>
+      <c r="L50" s="1">
+        <v>121.13</v>
+      </c>
+      <c r="M50" s="1">
+        <v>124.79</v>
+      </c>
+      <c r="N50" s="1">
+        <v>0.42</v>
+      </c>
+      <c r="O50" s="1">
+        <v>94.21</v>
+      </c>
+      <c r="P50" s="1">
+        <v>0.32</v>
+      </c>
+      <c r="Q50" s="1">
+        <v>29164.799999999999</v>
+      </c>
+      <c r="R50" s="1">
+        <v>29164.799999999999</v>
+      </c>
+      <c r="S50" s="1"/>
+      <c r="T50" s="1"/>
+      <c r="U50" s="1">
+        <v>1.44</v>
+      </c>
+      <c r="V50" s="1">
         <v>0</v>
       </c>
       <c r="W50" t="s">
@@ -3658,10 +3737,10 @@
         <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C51" t="s">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="D51" t="s">
         <v>0</v>
@@ -3669,55 +3748,51 @@
       <c r="E51" t="s">
         <v>0</v>
       </c>
-      <c r="F51" t="s">
-        <v>0</v>
-      </c>
-      <c r="G51" t="s">
-        <v>0</v>
+      <c r="F51" s="1">
+        <v>20000</v>
+      </c>
+      <c r="G51" s="1">
+        <v>142.80000000000001</v>
       </c>
       <c r="H51" t="s">
-        <v>0</v>
-      </c>
-      <c r="I51" t="s">
-        <v>0</v>
-      </c>
-      <c r="J51" t="s">
-        <v>0</v>
-      </c>
-      <c r="K51" t="s">
-        <v>0</v>
-      </c>
-      <c r="L51" t="s">
-        <v>0</v>
-      </c>
-      <c r="M51" t="s">
-        <v>0</v>
-      </c>
-      <c r="N51" t="s">
-        <v>0</v>
-      </c>
-      <c r="O51" t="s">
-        <v>0</v>
-      </c>
-      <c r="P51" t="s">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="I51" s="1">
+        <v>0</v>
+      </c>
+      <c r="J51" s="1">
+        <v>0</v>
+      </c>
+      <c r="K51" s="1">
+        <v>121.85</v>
+      </c>
+      <c r="L51" s="1">
+        <v>124.11</v>
+      </c>
+      <c r="M51" s="1">
+        <v>4189.97</v>
+      </c>
+      <c r="N51" s="1">
+        <v>17.190000000000001</v>
+      </c>
+      <c r="O51" s="1">
+        <v>3737.68</v>
+      </c>
+      <c r="P51" s="1">
+        <v>15.05</v>
       </c>
       <c r="Q51" s="1">
-        <v>854873.38</v>
-      </c>
-      <c r="R51" t="s">
-        <v>0</v>
-      </c>
-      <c r="S51" t="s">
-        <v>0</v>
-      </c>
-      <c r="T51" t="s">
-        <v>0</v>
-      </c>
-      <c r="U51" t="s">
-        <v>0</v>
-      </c>
-      <c r="V51" t="s">
+        <v>28560</v>
+      </c>
+      <c r="R51" s="1">
+        <v>28560</v>
+      </c>
+      <c r="S51" s="1"/>
+      <c r="T51" s="1"/>
+      <c r="U51" s="1">
+        <v>1.41</v>
+      </c>
+      <c r="V51" s="1">
         <v>0</v>
       </c>
       <c r="W51" t="s">
@@ -3800,7 +3875,7 @@
         <v>0</v>
       </c>
       <c r="B53" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C53" t="s">
         <v>0</v>
@@ -3844,8 +3919,8 @@
       <c r="P53" t="s">
         <v>0</v>
       </c>
-      <c r="Q53" t="s">
-        <v>0</v>
+      <c r="Q53" s="1">
+        <v>855292.21</v>
       </c>
       <c r="R53" t="s">
         <v>0</v>
@@ -3871,10 +3946,10 @@
         <v>0</v>
       </c>
       <c r="B54" t="s">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="C54" t="s">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="D54" t="s">
         <v>0</v>
@@ -3882,51 +3957,55 @@
       <c r="E54" t="s">
         <v>0</v>
       </c>
-      <c r="F54" s="1">
-        <v>45000</v>
-      </c>
-      <c r="G54" s="1">
-        <v>127.2</v>
+      <c r="F54" t="s">
+        <v>0</v>
+      </c>
+      <c r="G54" t="s">
+        <v>0</v>
       </c>
       <c r="H54" t="s">
-        <v>3</v>
-      </c>
-      <c r="I54" s="1">
-        <v>39.729999999999997</v>
-      </c>
-      <c r="J54" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="K54" s="1">
-        <v>120.19</v>
-      </c>
-      <c r="L54" s="1">
-        <v>125.11</v>
-      </c>
-      <c r="M54" s="1">
-        <v>9324.24</v>
-      </c>
-      <c r="N54" s="1">
-        <v>5.83</v>
-      </c>
-      <c r="O54" s="1">
-        <v>2775.57</v>
-      </c>
-      <c r="P54" s="1">
-        <v>1.66</v>
-      </c>
-      <c r="Q54" s="1">
-        <v>169086.96</v>
-      </c>
-      <c r="R54" s="1">
-        <v>57240</v>
-      </c>
-      <c r="S54" s="1"/>
-      <c r="T54" s="1"/>
-      <c r="U54" s="1">
-        <v>8.48</v>
-      </c>
-      <c r="V54" s="1">
+        <v>0</v>
+      </c>
+      <c r="I54" t="s">
+        <v>0</v>
+      </c>
+      <c r="J54" t="s">
+        <v>0</v>
+      </c>
+      <c r="K54" t="s">
+        <v>0</v>
+      </c>
+      <c r="L54" t="s">
+        <v>0</v>
+      </c>
+      <c r="M54" t="s">
+        <v>0</v>
+      </c>
+      <c r="N54" t="s">
+        <v>0</v>
+      </c>
+      <c r="O54" t="s">
+        <v>0</v>
+      </c>
+      <c r="P54" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>0</v>
+      </c>
+      <c r="R54" t="s">
+        <v>0</v>
+      </c>
+      <c r="S54" t="s">
+        <v>0</v>
+      </c>
+      <c r="T54" t="s">
+        <v>0</v>
+      </c>
+      <c r="U54" t="s">
+        <v>0</v>
+      </c>
+      <c r="V54" t="s">
         <v>0</v>
       </c>
       <c r="W54" t="s">
@@ -3938,10 +4017,10 @@
         <v>0</v>
       </c>
       <c r="B55" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C55" t="s">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="D55" t="s">
         <v>0</v>
@@ -3949,51 +4028,55 @@
       <c r="E55" t="s">
         <v>0</v>
       </c>
-      <c r="F55" s="1">
-        <v>189000</v>
-      </c>
-      <c r="G55" s="1">
-        <v>106.04</v>
+      <c r="F55" t="s">
+        <v>0</v>
+      </c>
+      <c r="G55" t="s">
+        <v>0</v>
       </c>
       <c r="H55" t="s">
-        <v>2</v>
-      </c>
-      <c r="I55" s="1">
-        <v>18.84</v>
-      </c>
-      <c r="J55" s="1">
-        <v>0.01</v>
-      </c>
-      <c r="K55" s="1">
-        <v>105.16</v>
-      </c>
-      <c r="L55" s="1">
-        <v>105.53</v>
-      </c>
-      <c r="M55" s="1">
-        <v>1655.07</v>
-      </c>
-      <c r="N55" s="1">
-        <v>0.83</v>
-      </c>
-      <c r="O55" s="1">
-        <v>963.9</v>
-      </c>
-      <c r="P55" s="1">
-        <v>0.48</v>
-      </c>
-      <c r="Q55" s="1">
-        <v>200415.6</v>
-      </c>
-      <c r="R55" s="1">
-        <v>200415.6</v>
-      </c>
-      <c r="S55" s="1"/>
-      <c r="T55" s="1"/>
-      <c r="U55" s="1">
-        <v>10.06</v>
-      </c>
-      <c r="V55" s="1">
+        <v>0</v>
+      </c>
+      <c r="I55" t="s">
+        <v>0</v>
+      </c>
+      <c r="J55" t="s">
+        <v>0</v>
+      </c>
+      <c r="K55" t="s">
+        <v>0</v>
+      </c>
+      <c r="L55" t="s">
+        <v>0</v>
+      </c>
+      <c r="M55" t="s">
+        <v>0</v>
+      </c>
+      <c r="N55" t="s">
+        <v>0</v>
+      </c>
+      <c r="O55" t="s">
+        <v>0</v>
+      </c>
+      <c r="P55" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>0</v>
+      </c>
+      <c r="R55" t="s">
+        <v>0</v>
+      </c>
+      <c r="S55" t="s">
+        <v>0</v>
+      </c>
+      <c r="T55" t="s">
+        <v>0</v>
+      </c>
+      <c r="U55" t="s">
+        <v>0</v>
+      </c>
+      <c r="V55" t="s">
         <v>0</v>
       </c>
       <c r="W55" t="s">
@@ -4005,10 +4088,10 @@
         <v>0</v>
       </c>
       <c r="B56" t="s">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="C56" t="s">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="D56" t="s">
         <v>0</v>
@@ -4016,55 +4099,51 @@
       <c r="E56" t="s">
         <v>0</v>
       </c>
-      <c r="F56" t="s">
-        <v>0</v>
-      </c>
-      <c r="G56" t="s">
-        <v>0</v>
+      <c r="F56" s="1">
+        <v>45000</v>
+      </c>
+      <c r="G56" s="1">
+        <v>127.28</v>
       </c>
       <c r="H56" t="s">
-        <v>0</v>
-      </c>
-      <c r="I56" t="s">
-        <v>0</v>
-      </c>
-      <c r="J56" t="s">
-        <v>0</v>
-      </c>
-      <c r="K56" t="s">
-        <v>0</v>
-      </c>
-      <c r="L56" t="s">
-        <v>0</v>
-      </c>
-      <c r="M56" t="s">
-        <v>0</v>
-      </c>
-      <c r="N56" t="s">
-        <v>0</v>
-      </c>
-      <c r="O56" t="s">
-        <v>0</v>
-      </c>
-      <c r="P56" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="s">
-        <v>0</v>
-      </c>
-      <c r="R56" t="s">
-        <v>0</v>
-      </c>
-      <c r="S56" t="s">
-        <v>0</v>
-      </c>
-      <c r="T56" t="s">
-        <v>0</v>
-      </c>
-      <c r="U56" t="s">
-        <v>0</v>
-      </c>
-      <c r="V56" t="s">
+        <v>3</v>
+      </c>
+      <c r="I56" s="1">
+        <v>26.89</v>
+      </c>
+      <c r="J56" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="K56" s="1">
+        <v>120.19</v>
+      </c>
+      <c r="L56" s="1">
+        <v>125.11</v>
+      </c>
+      <c r="M56" s="1">
+        <v>9548.7000000000007</v>
+      </c>
+      <c r="N56" s="1">
+        <v>5.9</v>
+      </c>
+      <c r="O56" s="1">
+        <v>2918.01</v>
+      </c>
+      <c r="P56" s="1">
+        <v>1.73</v>
+      </c>
+      <c r="Q56" s="1">
+        <v>171312.52</v>
+      </c>
+      <c r="R56" s="1">
+        <v>57276</v>
+      </c>
+      <c r="S56" s="1"/>
+      <c r="T56" s="1"/>
+      <c r="U56" s="1">
+        <v>8.4700000000000006</v>
+      </c>
+      <c r="V56" s="1">
         <v>0</v>
       </c>
       <c r="W56" t="s">
@@ -4076,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="B57" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C57" t="s">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D57" t="s">
         <v>0</v>
@@ -4087,55 +4166,51 @@
       <c r="E57" t="s">
         <v>0</v>
       </c>
-      <c r="F57" t="s">
-        <v>0</v>
-      </c>
-      <c r="G57" t="s">
-        <v>0</v>
+      <c r="F57" s="1">
+        <v>169000</v>
+      </c>
+      <c r="G57" s="1">
+        <v>106.1</v>
       </c>
       <c r="H57" t="s">
-        <v>0</v>
-      </c>
-      <c r="I57" t="s">
-        <v>0</v>
-      </c>
-      <c r="J57" t="s">
-        <v>0</v>
-      </c>
-      <c r="K57" t="s">
-        <v>0</v>
-      </c>
-      <c r="L57" t="s">
-        <v>0</v>
-      </c>
-      <c r="M57" t="s">
-        <v>0</v>
-      </c>
-      <c r="N57" t="s">
-        <v>0</v>
-      </c>
-      <c r="O57" t="s">
-        <v>0</v>
-      </c>
-      <c r="P57" t="s">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="I57" s="1">
+        <v>16.850000000000001</v>
+      </c>
+      <c r="J57" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="K57" s="1">
+        <v>105.16</v>
+      </c>
+      <c r="L57" s="1">
+        <v>105.53</v>
+      </c>
+      <c r="M57" s="1">
+        <v>1581.33</v>
+      </c>
+      <c r="N57" s="1">
+        <v>0.88</v>
+      </c>
+      <c r="O57" s="1">
+        <v>963.3</v>
+      </c>
+      <c r="P57" s="1">
+        <v>0.54</v>
       </c>
       <c r="Q57" s="1">
-        <v>369502.56</v>
-      </c>
-      <c r="R57" t="s">
-        <v>0</v>
-      </c>
-      <c r="S57" t="s">
-        <v>0</v>
-      </c>
-      <c r="T57" t="s">
-        <v>0</v>
-      </c>
-      <c r="U57" t="s">
-        <v>0</v>
-      </c>
-      <c r="V57" t="s">
+        <v>179309</v>
+      </c>
+      <c r="R57" s="1">
+        <v>179309</v>
+      </c>
+      <c r="S57" s="1"/>
+      <c r="T57" s="1"/>
+      <c r="U57" s="1">
+        <v>8.8699999999999992</v>
+      </c>
+      <c r="V57" s="1">
         <v>0</v>
       </c>
       <c r="W57" t="s">
@@ -4218,7 +4293,7 @@
         <v>0</v>
       </c>
       <c r="B59" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C59" t="s">
         <v>0</v>
@@ -4262,8 +4337,8 @@
       <c r="P59" t="s">
         <v>0</v>
       </c>
-      <c r="Q59" t="s">
-        <v>0</v>
+      <c r="Q59" s="1">
+        <v>350621.52</v>
       </c>
       <c r="R59" t="s">
         <v>0</v>
@@ -4289,10 +4364,10 @@
         <v>0</v>
       </c>
       <c r="B60" t="s">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="C60" t="s">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D60" t="s">
         <v>0</v>
@@ -4300,51 +4375,55 @@
       <c r="E60" t="s">
         <v>0</v>
       </c>
-      <c r="F60" s="1">
-        <v>703</v>
-      </c>
-      <c r="G60" s="1">
-        <v>39600</v>
+      <c r="F60" t="s">
+        <v>0</v>
+      </c>
+      <c r="G60" t="s">
+        <v>0</v>
       </c>
       <c r="H60" t="s">
-        <v>2</v>
-      </c>
-      <c r="I60" s="1">
-        <v>-1624.07</v>
-      </c>
-      <c r="J60" s="1">
-        <v>-0.57999999999999996</v>
-      </c>
-      <c r="K60" s="1">
-        <v>34092.879999999997</v>
-      </c>
-      <c r="L60" s="1">
-        <v>34168.11</v>
-      </c>
-      <c r="M60" s="1">
-        <v>38715.050000000003</v>
-      </c>
-      <c r="N60" s="1">
-        <v>16.149999999999999</v>
-      </c>
-      <c r="O60" s="1">
-        <v>38186.21</v>
-      </c>
-      <c r="P60" s="1">
-        <v>15.89</v>
-      </c>
-      <c r="Q60" s="1">
-        <v>278388</v>
-      </c>
-      <c r="R60" s="1">
-        <v>278388</v>
-      </c>
-      <c r="S60" s="1"/>
-      <c r="T60" s="1"/>
-      <c r="U60" s="1">
-        <v>13.97</v>
-      </c>
-      <c r="V60" s="1">
+        <v>0</v>
+      </c>
+      <c r="I60" t="s">
+        <v>0</v>
+      </c>
+      <c r="J60" t="s">
+        <v>0</v>
+      </c>
+      <c r="K60" t="s">
+        <v>0</v>
+      </c>
+      <c r="L60" t="s">
+        <v>0</v>
+      </c>
+      <c r="M60" t="s">
+        <v>0</v>
+      </c>
+      <c r="N60" t="s">
+        <v>0</v>
+      </c>
+      <c r="O60" t="s">
+        <v>0</v>
+      </c>
+      <c r="P60" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>0</v>
+      </c>
+      <c r="R60" t="s">
+        <v>0</v>
+      </c>
+      <c r="S60" t="s">
+        <v>0</v>
+      </c>
+      <c r="T60" t="s">
+        <v>0</v>
+      </c>
+      <c r="U60" t="s">
+        <v>0</v>
+      </c>
+      <c r="V60" t="s">
         <v>0</v>
       </c>
       <c r="W60" t="s">
@@ -4356,10 +4435,10 @@
         <v>0</v>
       </c>
       <c r="B61" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C61" t="s">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="D61" t="s">
         <v>0</v>
@@ -4367,51 +4446,55 @@
       <c r="E61" t="s">
         <v>0</v>
       </c>
-      <c r="F61" s="1">
-        <v>1000</v>
-      </c>
-      <c r="G61" s="1">
-        <v>1766</v>
+      <c r="F61" t="s">
+        <v>0</v>
+      </c>
+      <c r="G61" t="s">
+        <v>0</v>
       </c>
       <c r="H61" t="s">
-        <v>2</v>
-      </c>
-      <c r="I61" s="1">
-        <v>59.84</v>
-      </c>
-      <c r="J61" s="1">
-        <v>0.34</v>
-      </c>
-      <c r="K61" s="1">
-        <v>2278</v>
-      </c>
-      <c r="L61" s="1">
-        <v>2280.0500000000002</v>
-      </c>
-      <c r="M61" s="1">
-        <v>-5120</v>
-      </c>
-      <c r="N61" s="1">
-        <v>-22.47</v>
-      </c>
-      <c r="O61" s="1">
-        <v>-5140.5</v>
-      </c>
-      <c r="P61" s="1">
-        <v>-22.54</v>
-      </c>
-      <c r="Q61" s="1">
-        <v>17660</v>
-      </c>
-      <c r="R61" s="1">
-        <v>17660</v>
-      </c>
-      <c r="S61" s="1"/>
-      <c r="T61" s="1"/>
-      <c r="U61" s="1">
-        <v>0.89</v>
-      </c>
-      <c r="V61" s="1">
+        <v>0</v>
+      </c>
+      <c r="I61" t="s">
+        <v>0</v>
+      </c>
+      <c r="J61" t="s">
+        <v>0</v>
+      </c>
+      <c r="K61" t="s">
+        <v>0</v>
+      </c>
+      <c r="L61" t="s">
+        <v>0</v>
+      </c>
+      <c r="M61" t="s">
+        <v>0</v>
+      </c>
+      <c r="N61" t="s">
+        <v>0</v>
+      </c>
+      <c r="O61" t="s">
+        <v>0</v>
+      </c>
+      <c r="P61" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>0</v>
+      </c>
+      <c r="R61" t="s">
+        <v>0</v>
+      </c>
+      <c r="S61" t="s">
+        <v>0</v>
+      </c>
+      <c r="T61" t="s">
+        <v>0</v>
+      </c>
+      <c r="U61" t="s">
+        <v>0</v>
+      </c>
+      <c r="V61" t="s">
         <v>0</v>
       </c>
       <c r="W61" t="s">
@@ -4423,10 +4506,10 @@
         <v>0</v>
       </c>
       <c r="B62" t="s">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="C62" t="s">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="D62" t="s">
         <v>0</v>
@@ -4434,55 +4517,51 @@
       <c r="E62" t="s">
         <v>0</v>
       </c>
-      <c r="F62" t="s">
-        <v>0</v>
-      </c>
-      <c r="G62" t="s">
-        <v>0</v>
+      <c r="F62" s="1">
+        <v>703</v>
+      </c>
+      <c r="G62" s="1">
+        <v>39530</v>
       </c>
       <c r="H62" t="s">
-        <v>0</v>
-      </c>
-      <c r="I62" t="s">
-        <v>0</v>
-      </c>
-      <c r="J62" t="s">
-        <v>0</v>
-      </c>
-      <c r="K62" t="s">
-        <v>0</v>
-      </c>
-      <c r="L62" t="s">
-        <v>0</v>
-      </c>
-      <c r="M62" t="s">
-        <v>0</v>
-      </c>
-      <c r="N62" t="s">
-        <v>0</v>
-      </c>
-      <c r="O62" t="s">
-        <v>0</v>
-      </c>
-      <c r="P62" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="s">
-        <v>0</v>
-      </c>
-      <c r="R62" t="s">
-        <v>0</v>
-      </c>
-      <c r="S62" t="s">
-        <v>0</v>
-      </c>
-      <c r="T62" t="s">
-        <v>0</v>
-      </c>
-      <c r="U62" t="s">
-        <v>0</v>
-      </c>
-      <c r="V62" t="s">
+        <v>2</v>
+      </c>
+      <c r="I62" s="1">
+        <v>1465.08</v>
+      </c>
+      <c r="J62" s="1">
+        <v>0.53</v>
+      </c>
+      <c r="K62" s="1">
+        <v>34092.879999999997</v>
+      </c>
+      <c r="L62" s="1">
+        <v>34168.11</v>
+      </c>
+      <c r="M62" s="1">
+        <v>38222.949999999997</v>
+      </c>
+      <c r="N62" s="1">
+        <v>15.94</v>
+      </c>
+      <c r="O62" s="1">
+        <v>37694.11</v>
+      </c>
+      <c r="P62" s="1">
+        <v>15.69</v>
+      </c>
+      <c r="Q62" s="1">
+        <v>277895.90000000002</v>
+      </c>
+      <c r="R62" s="1">
+        <v>277895.90000000002</v>
+      </c>
+      <c r="S62" s="1"/>
+      <c r="T62" s="1"/>
+      <c r="U62" s="1">
+        <v>13.74</v>
+      </c>
+      <c r="V62" s="1">
         <v>0</v>
       </c>
       <c r="W62" t="s">
@@ -4494,10 +4573,10 @@
         <v>0</v>
       </c>
       <c r="B63" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C63" t="s">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="D63" t="s">
         <v>0</v>
@@ -4505,55 +4584,51 @@
       <c r="E63" t="s">
         <v>0</v>
       </c>
-      <c r="F63" t="s">
-        <v>0</v>
-      </c>
-      <c r="G63" t="s">
-        <v>0</v>
+      <c r="F63" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G63" s="1">
+        <v>1812</v>
       </c>
       <c r="H63" t="s">
-        <v>0</v>
-      </c>
-      <c r="I63" t="s">
-        <v>0</v>
-      </c>
-      <c r="J63" t="s">
-        <v>0</v>
-      </c>
-      <c r="K63" t="s">
-        <v>0</v>
-      </c>
-      <c r="L63" t="s">
-        <v>0</v>
-      </c>
-      <c r="M63" t="s">
-        <v>0</v>
-      </c>
-      <c r="N63" t="s">
-        <v>0</v>
-      </c>
-      <c r="O63" t="s">
-        <v>0</v>
-      </c>
-      <c r="P63" t="s">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="I63" s="1">
+        <v>490.11</v>
+      </c>
+      <c r="J63" s="1">
+        <v>2.78</v>
+      </c>
+      <c r="K63" s="1">
+        <v>2278</v>
+      </c>
+      <c r="L63" s="1">
+        <v>2280.0500000000002</v>
+      </c>
+      <c r="M63" s="1">
+        <v>-4660</v>
+      </c>
+      <c r="N63" s="1">
+        <v>-20.45</v>
+      </c>
+      <c r="O63" s="1">
+        <v>-4680.5</v>
+      </c>
+      <c r="P63" s="1">
+        <v>-20.52</v>
       </c>
       <c r="Q63" s="1">
-        <v>296048</v>
-      </c>
-      <c r="R63" t="s">
-        <v>0</v>
-      </c>
-      <c r="S63" t="s">
-        <v>0</v>
-      </c>
-      <c r="T63" t="s">
-        <v>0</v>
-      </c>
-      <c r="U63" t="s">
-        <v>0</v>
-      </c>
-      <c r="V63" t="s">
+        <v>18120</v>
+      </c>
+      <c r="R63" s="1">
+        <v>18120</v>
+      </c>
+      <c r="S63" s="1"/>
+      <c r="T63" s="1"/>
+      <c r="U63" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="V63" s="1">
         <v>0</v>
       </c>
       <c r="W63" t="s">
@@ -4636,7 +4711,7 @@
         <v>0</v>
       </c>
       <c r="B65" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C65" t="s">
         <v>0</v>
@@ -4680,8 +4755,8 @@
       <c r="P65" t="s">
         <v>0</v>
       </c>
-      <c r="Q65" t="s">
-        <v>0</v>
+      <c r="Q65" s="1">
+        <v>296015.90000000002</v>
       </c>
       <c r="R65" t="s">
         <v>0</v>
@@ -4707,10 +4782,10 @@
         <v>0</v>
       </c>
       <c r="B66" t="s">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="C66" t="s">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D66" t="s">
         <v>0</v>
@@ -4718,51 +4793,55 @@
       <c r="E66" t="s">
         <v>0</v>
       </c>
-      <c r="F66" s="1">
-        <v>7148</v>
-      </c>
-      <c r="G66" s="1">
-        <v>56.5</v>
+      <c r="F66" t="s">
+        <v>0</v>
+      </c>
+      <c r="G66" t="s">
+        <v>0</v>
       </c>
       <c r="H66" t="s">
-        <v>2</v>
-      </c>
-      <c r="I66" s="1">
-        <v>0</v>
-      </c>
-      <c r="J66" s="1">
-        <v>0</v>
-      </c>
-      <c r="K66" s="1">
-        <v>56.1</v>
-      </c>
-      <c r="L66" s="1">
-        <v>56.15</v>
-      </c>
-      <c r="M66" s="1">
-        <v>28.59</v>
-      </c>
-      <c r="N66" s="1">
-        <v>0.71</v>
-      </c>
-      <c r="O66" s="1">
-        <v>24.99</v>
-      </c>
-      <c r="P66" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="Q66" s="1">
-        <v>4038.62</v>
-      </c>
-      <c r="R66" s="1">
-        <v>4038.62</v>
-      </c>
-      <c r="S66" s="1"/>
-      <c r="T66" s="1"/>
-      <c r="U66" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="V66" s="1">
+        <v>0</v>
+      </c>
+      <c r="I66" t="s">
+        <v>0</v>
+      </c>
+      <c r="J66" t="s">
+        <v>0</v>
+      </c>
+      <c r="K66" t="s">
+        <v>0</v>
+      </c>
+      <c r="L66" t="s">
+        <v>0</v>
+      </c>
+      <c r="M66" t="s">
+        <v>0</v>
+      </c>
+      <c r="N66" t="s">
+        <v>0</v>
+      </c>
+      <c r="O66" t="s">
+        <v>0</v>
+      </c>
+      <c r="P66" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>0</v>
+      </c>
+      <c r="R66" t="s">
+        <v>0</v>
+      </c>
+      <c r="S66" t="s">
+        <v>0</v>
+      </c>
+      <c r="T66" t="s">
+        <v>0</v>
+      </c>
+      <c r="U66" t="s">
+        <v>0</v>
+      </c>
+      <c r="V66" t="s">
         <v>0</v>
       </c>
       <c r="W66" t="s">
@@ -4774,7 +4853,7 @@
         <v>0</v>
       </c>
       <c r="B67" t="s">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="C67" t="s">
         <v>0</v>
@@ -4845,10 +4924,10 @@
         <v>0</v>
       </c>
       <c r="B68" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C68" t="s">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D68" t="s">
         <v>0</v>
@@ -4856,55 +4935,51 @@
       <c r="E68" t="s">
         <v>0</v>
       </c>
-      <c r="F68" t="s">
-        <v>0</v>
-      </c>
-      <c r="G68" t="s">
-        <v>0</v>
+      <c r="F68" s="1">
+        <v>7148</v>
+      </c>
+      <c r="G68" s="1">
+        <v>56.5</v>
       </c>
       <c r="H68" t="s">
-        <v>0</v>
-      </c>
-      <c r="I68" t="s">
-        <v>0</v>
-      </c>
-      <c r="J68" t="s">
-        <v>0</v>
-      </c>
-      <c r="K68" t="s">
-        <v>0</v>
-      </c>
-      <c r="L68" t="s">
-        <v>0</v>
-      </c>
-      <c r="M68" t="s">
-        <v>0</v>
-      </c>
-      <c r="N68" t="s">
-        <v>0</v>
-      </c>
-      <c r="O68" t="s">
-        <v>0</v>
-      </c>
-      <c r="P68" t="s">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="I68" s="1">
+        <v>0</v>
+      </c>
+      <c r="J68" s="1">
+        <v>0</v>
+      </c>
+      <c r="K68" s="1">
+        <v>56.1</v>
+      </c>
+      <c r="L68" s="1">
+        <v>56.15</v>
+      </c>
+      <c r="M68" s="1">
+        <v>28.59</v>
+      </c>
+      <c r="N68" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="O68" s="1">
+        <v>24.99</v>
+      </c>
+      <c r="P68" s="1">
+        <v>0.62</v>
       </c>
       <c r="Q68" s="1">
         <v>4038.62</v>
       </c>
-      <c r="R68" t="s">
-        <v>0</v>
-      </c>
-      <c r="S68" t="s">
-        <v>0</v>
-      </c>
-      <c r="T68" t="s">
-        <v>0</v>
-      </c>
-      <c r="U68" t="s">
-        <v>0</v>
-      </c>
-      <c r="V68" t="s">
+      <c r="R68" s="1">
+        <v>4038.62</v>
+      </c>
+      <c r="S68" s="1"/>
+      <c r="T68" s="1"/>
+      <c r="U68" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="V68" s="1">
         <v>0</v>
       </c>
       <c r="W68" t="s">
@@ -4987,7 +5062,7 @@
         <v>0</v>
       </c>
       <c r="B70" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C70" t="s">
         <v>0</v>
@@ -5031,8 +5106,8 @@
       <c r="P70" t="s">
         <v>0</v>
       </c>
-      <c r="Q70" t="s">
-        <v>0</v>
+      <c r="Q70" s="1">
+        <v>4038.62</v>
       </c>
       <c r="R70" t="s">
         <v>0</v>
@@ -5129,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="B72" t="s">
-        <v>26</v>
+        <v>112</v>
       </c>
       <c r="C72" t="s">
         <v>0</v>
@@ -5200,62 +5275,66 @@
         <v>0</v>
       </c>
       <c r="B73" t="s">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="C73" t="s">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D73" t="s">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="E73" t="s">
         <v>0</v>
       </c>
-      <c r="F73" s="1">
-        <v>700</v>
-      </c>
-      <c r="G73" s="1">
-        <v>0.4</v>
+      <c r="F73" t="s">
+        <v>0</v>
+      </c>
+      <c r="G73" t="s">
+        <v>0</v>
       </c>
       <c r="H73" t="s">
-        <v>3</v>
-      </c>
-      <c r="I73" s="1">
-        <v>3.72</v>
-      </c>
-      <c r="J73" s="1">
-        <v>0.46</v>
-      </c>
-      <c r="K73" s="1">
-        <v>0.59</v>
-      </c>
-      <c r="L73" s="1">
-        <v>0.59</v>
-      </c>
-      <c r="M73" s="1">
-        <v>-400.11</v>
-      </c>
-      <c r="N73" s="1">
-        <v>-32.79</v>
-      </c>
-      <c r="O73" s="1">
-        <v>-408.38</v>
-      </c>
-      <c r="P73" s="1">
-        <v>-33.24</v>
-      </c>
-      <c r="Q73" s="1">
-        <v>819.88</v>
-      </c>
-      <c r="R73" s="1">
-        <v>277.55</v>
-      </c>
-      <c r="S73" s="1"/>
-      <c r="T73" s="1"/>
-      <c r="U73" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="V73" s="1">
+        <v>0</v>
+      </c>
+      <c r="I73" t="s">
+        <v>0</v>
+      </c>
+      <c r="J73" t="s">
+        <v>0</v>
+      </c>
+      <c r="K73" t="s">
+        <v>0</v>
+      </c>
+      <c r="L73" t="s">
+        <v>0</v>
+      </c>
+      <c r="M73" t="s">
+        <v>0</v>
+      </c>
+      <c r="N73" t="s">
+        <v>0</v>
+      </c>
+      <c r="O73" t="s">
+        <v>0</v>
+      </c>
+      <c r="P73" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>0</v>
+      </c>
+      <c r="R73" t="s">
+        <v>0</v>
+      </c>
+      <c r="S73" t="s">
+        <v>0</v>
+      </c>
+      <c r="T73" t="s">
+        <v>0</v>
+      </c>
+      <c r="U73" t="s">
+        <v>0</v>
+      </c>
+      <c r="V73" t="s">
         <v>0</v>
       </c>
       <c r="W73" t="s">
@@ -5267,7 +5346,7 @@
         <v>0</v>
       </c>
       <c r="B74" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C74" t="s">
         <v>0</v>
@@ -5338,69 +5417,207 @@
         <v>0</v>
       </c>
       <c r="B75" t="s">
-        <v>55</v>
+        <v>113</v>
       </c>
       <c r="C75" t="s">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="D75" t="s">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="E75" t="s">
         <v>0</v>
       </c>
-      <c r="F75" t="s">
-        <v>0</v>
-      </c>
-      <c r="G75" t="s">
-        <v>0</v>
+      <c r="F75" s="1">
+        <v>700</v>
+      </c>
+      <c r="G75" s="1">
+        <v>0.33</v>
       </c>
       <c r="H75" t="s">
-        <v>0</v>
-      </c>
-      <c r="I75" t="s">
-        <v>0</v>
-      </c>
-      <c r="J75" t="s">
-        <v>0</v>
-      </c>
-      <c r="K75" t="s">
-        <v>0</v>
-      </c>
-      <c r="L75" t="s">
-        <v>0</v>
-      </c>
-      <c r="M75" t="s">
-        <v>0</v>
-      </c>
-      <c r="N75" t="s">
-        <v>0</v>
-      </c>
-      <c r="O75" t="s">
-        <v>0</v>
-      </c>
-      <c r="P75" t="s">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="I75" s="1">
+        <v>-26.59</v>
+      </c>
+      <c r="J75" s="1">
+        <v>-3.67</v>
+      </c>
+      <c r="K75" s="1">
+        <v>0.59</v>
+      </c>
+      <c r="L75" s="1">
+        <v>0.59</v>
+      </c>
+      <c r="M75" s="1">
+        <v>-537.87</v>
+      </c>
+      <c r="N75" s="1">
+        <v>-43.54</v>
+      </c>
+      <c r="O75" s="1">
+        <v>-546.24</v>
+      </c>
+      <c r="P75" s="1">
+        <v>-43.92</v>
       </c>
       <c r="Q75" s="1">
-        <v>819.88</v>
-      </c>
-      <c r="R75" t="s">
-        <v>0</v>
-      </c>
-      <c r="S75" t="s">
-        <v>0</v>
-      </c>
-      <c r="T75" t="s">
-        <v>0</v>
-      </c>
-      <c r="U75" t="s">
-        <v>0</v>
-      </c>
-      <c r="V75" t="s">
+        <v>697.41</v>
+      </c>
+      <c r="R75" s="1">
+        <v>233.17</v>
+      </c>
+      <c r="S75" s="1"/>
+      <c r="T75" s="1"/>
+      <c r="U75" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="V75" s="1">
         <v>0</v>
       </c>
       <c r="W75" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A76" t="s">
+        <v>0</v>
+      </c>
+      <c r="B76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C76" t="s">
+        <v>0</v>
+      </c>
+      <c r="D76" t="s">
+        <v>0</v>
+      </c>
+      <c r="E76" t="s">
+        <v>0</v>
+      </c>
+      <c r="F76" t="s">
+        <v>0</v>
+      </c>
+      <c r="G76" t="s">
+        <v>0</v>
+      </c>
+      <c r="H76" t="s">
+        <v>0</v>
+      </c>
+      <c r="I76" t="s">
+        <v>0</v>
+      </c>
+      <c r="J76" t="s">
+        <v>0</v>
+      </c>
+      <c r="K76" t="s">
+        <v>0</v>
+      </c>
+      <c r="L76" t="s">
+        <v>0</v>
+      </c>
+      <c r="M76" t="s">
+        <v>0</v>
+      </c>
+      <c r="N76" t="s">
+        <v>0</v>
+      </c>
+      <c r="O76" t="s">
+        <v>0</v>
+      </c>
+      <c r="P76" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>0</v>
+      </c>
+      <c r="R76" t="s">
+        <v>0</v>
+      </c>
+      <c r="S76" t="s">
+        <v>0</v>
+      </c>
+      <c r="T76" t="s">
+        <v>0</v>
+      </c>
+      <c r="U76" t="s">
+        <v>0</v>
+      </c>
+      <c r="V76" t="s">
+        <v>0</v>
+      </c>
+      <c r="W76" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A77" t="s">
+        <v>0</v>
+      </c>
+      <c r="B77" t="s">
+        <v>57</v>
+      </c>
+      <c r="C77" t="s">
+        <v>0</v>
+      </c>
+      <c r="D77" t="s">
+        <v>0</v>
+      </c>
+      <c r="E77" t="s">
+        <v>0</v>
+      </c>
+      <c r="F77" t="s">
+        <v>0</v>
+      </c>
+      <c r="G77" t="s">
+        <v>0</v>
+      </c>
+      <c r="H77" t="s">
+        <v>0</v>
+      </c>
+      <c r="I77" t="s">
+        <v>0</v>
+      </c>
+      <c r="J77" t="s">
+        <v>0</v>
+      </c>
+      <c r="K77" t="s">
+        <v>0</v>
+      </c>
+      <c r="L77" t="s">
+        <v>0</v>
+      </c>
+      <c r="M77" t="s">
+        <v>0</v>
+      </c>
+      <c r="N77" t="s">
+        <v>0</v>
+      </c>
+      <c r="O77" t="s">
+        <v>0</v>
+      </c>
+      <c r="P77" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="1">
+        <v>697.41</v>
+      </c>
+      <c r="R77" t="s">
+        <v>0</v>
+      </c>
+      <c r="S77" t="s">
+        <v>0</v>
+      </c>
+      <c r="T77" t="s">
+        <v>0</v>
+      </c>
+      <c r="U77" t="s">
+        <v>0</v>
+      </c>
+      <c r="V77" t="s">
+        <v>0</v>
+      </c>
+      <c r="W77" t="s">
         <v>0</v>
       </c>
     </row>

--- a/holdings.xlsx
+++ b/holdings.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chen\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chen\tase-ytm-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C5E1E6-80A1-4814-B4E3-37B7B0FB11C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0E60EF9-D232-4CCF-B060-7621CCD410BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="14235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="116">
   <si>
     <t/>
   </si>
@@ -151,6 +151,12 @@
     <t>1174093</t>
   </si>
   <si>
+    <t>ליברה</t>
+  </si>
+  <si>
+    <t>1176981</t>
+  </si>
+  <si>
     <t>מיטרוניקס</t>
   </si>
   <si>
@@ -335,12 +341,6 @@
   </si>
   <si>
     <t>1146356</t>
-  </si>
-  <si>
-    <t>תכ.תאבנייה</t>
-  </si>
-  <si>
-    <t>1176536</t>
   </si>
   <si>
     <t>:סה"כ מחקי מדד</t>
@@ -762,7 +762,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W77"/>
+  <dimension ref="A5:W77"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.73046875" bestFit="1" customWidth="1"/>
@@ -789,77 +789,6 @@
     <col min="23" max="23" width="24.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" t="s">
-        <v>0</v>
-      </c>
-      <c r="I1" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K1" t="s">
-        <v>0</v>
-      </c>
-      <c r="L1" t="s">
-        <v>0</v>
-      </c>
-      <c r="M1" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" t="s">
-        <v>0</v>
-      </c>
-      <c r="O1" t="s">
-        <v>0</v>
-      </c>
-      <c r="P1" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>0</v>
-      </c>
-      <c r="R1" t="s">
-        <v>0</v>
-      </c>
-      <c r="S1" t="s">
-        <v>0</v>
-      </c>
-      <c r="T1" t="s">
-        <v>0</v>
-      </c>
-      <c r="U1" t="s">
-        <v>0</v>
-      </c>
-      <c r="V1" t="s">
-        <v>0</v>
-      </c>
-      <c r="W1" t="s">
-        <v>0</v>
-      </c>
-    </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.45">
       <c r="C5" s="1"/>
       <c r="E5" s="1"/>
@@ -1330,16 +1259,16 @@
         <v>2</v>
       </c>
       <c r="I15" s="1">
-        <v>-870.55</v>
+        <v>-269.39999999999998</v>
       </c>
       <c r="J15" s="1">
-        <v>-2.82</v>
+        <v>-0.89</v>
       </c>
       <c r="K15" s="1">
         <v>2000</v>
       </c>
       <c r="L15" s="1">
-        <v>2000</v>
+        <v>2001.82</v>
       </c>
       <c r="M15" s="1">
         <v>0</v>
@@ -1348,10 +1277,10 @@
         <v>0</v>
       </c>
       <c r="O15" s="1">
-        <v>0</v>
+        <v>-27.29</v>
       </c>
       <c r="P15" s="1">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="Q15" s="1">
         <v>30000</v>
@@ -1391,16 +1320,16 @@
         <v>4680</v>
       </c>
       <c r="G16" s="1">
-        <v>746</v>
+        <v>729.6</v>
       </c>
       <c r="H16" t="s">
         <v>2</v>
       </c>
       <c r="I16" s="1">
-        <v>242.69</v>
+        <v>-379.78</v>
       </c>
       <c r="J16" s="1">
-        <v>0.7</v>
+        <v>-1.1000000000000001</v>
       </c>
       <c r="K16" s="1">
         <v>684.32</v>
@@ -1409,27 +1338,27 @@
         <v>698.43</v>
       </c>
       <c r="M16" s="1">
-        <v>2886.63</v>
+        <v>2119.11</v>
       </c>
       <c r="N16" s="1">
-        <v>9.01</v>
+        <v>6.61</v>
       </c>
       <c r="O16" s="1">
-        <v>2226.2600000000002</v>
+        <v>1458.74</v>
       </c>
       <c r="P16" s="1">
-        <v>6.81</v>
+        <v>4.46</v>
       </c>
       <c r="Q16" s="1">
-        <v>34912.800000000003</v>
+        <v>34145.279999999999</v>
       </c>
       <c r="R16" s="1">
-        <v>34912.800000000003</v>
+        <v>34145.279999999999</v>
       </c>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
       <c r="U16" s="1">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="V16" s="1">
         <v>0</v>
@@ -1458,16 +1387,16 @@
         <v>6000</v>
       </c>
       <c r="G17" s="1">
-        <v>674</v>
+        <v>647.79999999999995</v>
       </c>
       <c r="H17" t="s">
         <v>2</v>
       </c>
       <c r="I17" s="1">
-        <v>-289.18</v>
+        <v>487.43</v>
       </c>
       <c r="J17" s="1">
-        <v>-0.71</v>
+        <v>1.27</v>
       </c>
       <c r="K17" s="1">
         <v>575.66999999999996</v>
@@ -1476,27 +1405,27 @@
         <v>641.24</v>
       </c>
       <c r="M17" s="1">
-        <v>5899.61</v>
+        <v>4327.6099999999997</v>
       </c>
       <c r="N17" s="1">
-        <v>17.079999999999998</v>
+        <v>12.52</v>
       </c>
       <c r="O17" s="1">
-        <v>1965.4</v>
+        <v>393.4</v>
       </c>
       <c r="P17" s="1">
-        <v>5.0999999999999996</v>
+        <v>1.02</v>
       </c>
       <c r="Q17" s="1">
-        <v>40440</v>
+        <v>38868</v>
       </c>
       <c r="R17" s="1">
-        <v>40440</v>
+        <v>38868</v>
       </c>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
       <c r="U17" s="1">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="V17" s="1">
         <v>0</v>
@@ -1525,16 +1454,16 @@
         <v>93000</v>
       </c>
       <c r="G18" s="1">
-        <v>105.1</v>
+        <v>104.1</v>
       </c>
       <c r="H18" t="s">
         <v>2</v>
       </c>
       <c r="I18" s="1">
-        <v>1025.21</v>
+        <v>0</v>
       </c>
       <c r="J18" s="1">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
         <v>92.69</v>
@@ -1543,27 +1472,27 @@
         <v>89.42</v>
       </c>
       <c r="M18" s="1">
-        <v>11538.88</v>
+        <v>10608.88</v>
       </c>
       <c r="N18" s="1">
-        <v>13.38</v>
+        <v>12.3</v>
       </c>
       <c r="O18" s="1">
-        <v>14585.2</v>
+        <v>13655.2</v>
       </c>
       <c r="P18" s="1">
-        <v>17.53</v>
+        <v>16.420000000000002</v>
       </c>
       <c r="Q18" s="1">
-        <v>97743</v>
+        <v>96813</v>
       </c>
       <c r="R18" s="1">
-        <v>97743</v>
+        <v>96813</v>
       </c>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
       <c r="U18" s="1">
-        <v>4.83</v>
+        <v>4.79</v>
       </c>
       <c r="V18" s="1">
         <v>0</v>
@@ -1592,16 +1521,16 @@
         <v>172500</v>
       </c>
       <c r="G19" s="1">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="H19" t="s">
         <v>2</v>
       </c>
       <c r="I19" s="1">
-        <v>0</v>
+        <v>171.56</v>
       </c>
       <c r="J19" s="1">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="K19" s="1">
         <v>18.760000000000002</v>
@@ -1610,27 +1539,27 @@
         <v>18.78</v>
       </c>
       <c r="M19" s="1">
-        <v>-11481.42</v>
+        <v>-11998.92</v>
       </c>
       <c r="N19" s="1">
-        <v>-35.479999999999997</v>
+        <v>-37.08</v>
       </c>
       <c r="O19" s="1">
-        <v>-11514.67</v>
+        <v>-12032.17</v>
       </c>
       <c r="P19" s="1">
-        <v>-35.549999999999997</v>
+        <v>-37.15</v>
       </c>
       <c r="Q19" s="1">
-        <v>20872.5</v>
+        <v>20355</v>
       </c>
       <c r="R19" s="1">
-        <v>20872.5</v>
+        <v>20355</v>
       </c>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
       <c r="U19" s="1">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="V19" s="1">
         <v>0</v>
@@ -1656,48 +1585,48 @@
         <v>0</v>
       </c>
       <c r="F20" s="1">
-        <v>143</v>
+        <v>293</v>
       </c>
       <c r="G20" s="1">
-        <v>9610</v>
+        <v>10700</v>
       </c>
       <c r="H20" t="s">
         <v>2</v>
       </c>
       <c r="I20" s="1">
-        <v>1012.05</v>
+        <v>877.63</v>
       </c>
       <c r="J20" s="1">
-        <v>7.95</v>
+        <v>2.88</v>
       </c>
       <c r="K20" s="1">
-        <v>29153.85</v>
+        <v>19220.14</v>
       </c>
       <c r="L20" s="1">
-        <v>29236.080000000002</v>
+        <v>19264.77</v>
       </c>
       <c r="M20" s="1">
-        <v>-27947.71</v>
+        <v>-24964.01</v>
       </c>
       <c r="N20" s="1">
-        <v>-67.03</v>
+        <v>-44.32</v>
       </c>
       <c r="O20" s="1">
-        <v>-28065.3</v>
+        <v>-25094.76</v>
       </c>
       <c r="P20" s="1">
-        <v>-67.12</v>
+        <v>-44.45</v>
       </c>
       <c r="Q20" s="1">
-        <v>13742.3</v>
+        <v>31351</v>
       </c>
       <c r="R20" s="1">
-        <v>13742.3</v>
+        <v>31351</v>
       </c>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
       <c r="U20" s="1">
-        <v>0.68</v>
+        <v>1.55</v>
       </c>
       <c r="V20" s="1">
         <v>0</v>
@@ -1726,16 +1655,16 @@
         <v>2200</v>
       </c>
       <c r="G21" s="1">
-        <v>1117</v>
+        <v>1127</v>
       </c>
       <c r="H21" t="s">
         <v>2</v>
       </c>
       <c r="I21" s="1">
-        <v>639.05999999999995</v>
+        <v>155.22</v>
       </c>
       <c r="J21" s="1">
-        <v>2.67</v>
+        <v>0.63</v>
       </c>
       <c r="K21" s="1">
         <v>1374</v>
@@ -1744,27 +1673,27 @@
         <v>1375.24</v>
       </c>
       <c r="M21" s="1">
-        <v>-5654</v>
+        <v>-5434</v>
       </c>
       <c r="N21" s="1">
-        <v>-18.7</v>
+        <v>-17.97</v>
       </c>
       <c r="O21" s="1">
-        <v>-5681.21</v>
+        <v>-5461.21</v>
       </c>
       <c r="P21" s="1">
-        <v>-18.77</v>
+        <v>-18.05</v>
       </c>
       <c r="Q21" s="1">
-        <v>24574</v>
+        <v>24794</v>
       </c>
       <c r="R21" s="1">
-        <v>24574</v>
+        <v>24794</v>
       </c>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
       <c r="U21" s="1">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="V21" s="1">
         <v>0</v>
@@ -1793,16 +1722,16 @@
         <v>1000</v>
       </c>
       <c r="G22" s="1">
-        <v>58.9</v>
+        <v>58.7</v>
       </c>
       <c r="H22" t="s">
         <v>2</v>
       </c>
       <c r="I22" s="1">
-        <v>-1</v>
+        <v>28.01</v>
       </c>
       <c r="J22" s="1">
-        <v>-0.17</v>
+        <v>5.01</v>
       </c>
       <c r="K22" s="1">
         <v>55</v>
@@ -1811,22 +1740,22 @@
         <v>55.45</v>
       </c>
       <c r="M22" s="1">
-        <v>38.99</v>
+        <v>36.99</v>
       </c>
       <c r="N22" s="1">
-        <v>7.09</v>
+        <v>6.72</v>
       </c>
       <c r="O22" s="1">
-        <v>34.5</v>
+        <v>32.5</v>
       </c>
       <c r="P22" s="1">
-        <v>6.22</v>
+        <v>5.86</v>
       </c>
       <c r="Q22" s="1">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="R22" s="1">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
@@ -1857,48 +1786,48 @@
         <v>0</v>
       </c>
       <c r="F23" s="1">
-        <v>15000</v>
+        <v>1000</v>
       </c>
       <c r="G23" s="1">
-        <v>233.6</v>
+        <v>2777</v>
       </c>
       <c r="H23" t="s">
         <v>2</v>
       </c>
       <c r="I23" s="1">
-        <v>1201.27</v>
+        <v>171.11</v>
       </c>
       <c r="J23" s="1">
-        <v>3.55</v>
+        <v>0.62</v>
       </c>
       <c r="K23" s="1">
-        <v>317.23</v>
+        <v>2472</v>
       </c>
       <c r="L23" s="1">
-        <v>318.69</v>
+        <v>2474.23</v>
       </c>
       <c r="M23" s="1">
-        <v>-12544.89</v>
+        <v>3049.99</v>
       </c>
       <c r="N23" s="1">
-        <v>-26.36</v>
+        <v>12.33</v>
       </c>
       <c r="O23" s="1">
-        <v>-12762.98</v>
+        <v>3027.75</v>
       </c>
       <c r="P23" s="1">
-        <v>-26.69</v>
+        <v>12.23</v>
       </c>
       <c r="Q23" s="1">
-        <v>35040</v>
+        <v>27770</v>
       </c>
       <c r="R23" s="1">
-        <v>35040</v>
+        <v>27770</v>
       </c>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
       <c r="U23" s="1">
-        <v>1.73</v>
+        <v>1.37</v>
       </c>
       <c r="V23" s="1">
         <v>0</v>
@@ -1924,48 +1853,48 @@
         <v>0</v>
       </c>
       <c r="F24" s="1">
-        <v>1350</v>
+        <v>15000</v>
       </c>
       <c r="G24" s="1">
-        <v>2250</v>
+        <v>253.7</v>
       </c>
       <c r="H24" t="s">
         <v>2</v>
       </c>
       <c r="I24" s="1">
-        <v>297.76</v>
+        <v>1484.75</v>
       </c>
       <c r="J24" s="1">
-        <v>0.99</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="K24" s="1">
-        <v>2610.16</v>
+        <v>317.23</v>
       </c>
       <c r="L24" s="1">
-        <v>2758.41</v>
+        <v>318.69</v>
       </c>
       <c r="M24" s="1">
-        <v>-4862.21</v>
+        <v>-9529.89</v>
       </c>
       <c r="N24" s="1">
-        <v>-13.79</v>
+        <v>-20.02</v>
       </c>
       <c r="O24" s="1">
-        <v>-6863.48</v>
+        <v>-9747.98</v>
       </c>
       <c r="P24" s="1">
-        <v>-18.43</v>
+        <v>-20.39</v>
       </c>
       <c r="Q24" s="1">
-        <v>30375</v>
+        <v>38055</v>
       </c>
       <c r="R24" s="1">
-        <v>30375</v>
+        <v>38055</v>
       </c>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
       <c r="U24" s="1">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="V24" s="1">
         <v>0</v>
@@ -1991,48 +1920,52 @@
         <v>0</v>
       </c>
       <c r="F25" s="1">
-        <v>700</v>
+        <v>1350</v>
       </c>
       <c r="G25" s="1">
-        <v>4520</v>
+        <v>2213</v>
       </c>
       <c r="H25" t="s">
         <v>2</v>
       </c>
       <c r="I25" s="1">
-        <v>294.64999999999998</v>
+        <v>14.93</v>
       </c>
       <c r="J25" s="1">
-        <v>0.94</v>
+        <v>0.05</v>
       </c>
       <c r="K25" s="1">
-        <v>5582.59</v>
+        <v>2610.16</v>
       </c>
       <c r="L25" s="1">
-        <v>5657.95</v>
+        <v>2758.41</v>
       </c>
       <c r="M25" s="1">
-        <v>-7438.1</v>
+        <v>-5361.71</v>
       </c>
       <c r="N25" s="1">
-        <v>-19.03</v>
+        <v>-15.21</v>
       </c>
       <c r="O25" s="1">
-        <v>-7965.62</v>
+        <v>-7362.98</v>
       </c>
       <c r="P25" s="1">
-        <v>-20.11</v>
+        <v>-19.77</v>
       </c>
       <c r="Q25" s="1">
-        <v>31640</v>
+        <v>29875.5</v>
       </c>
       <c r="R25" s="1">
-        <v>31640</v>
-      </c>
-      <c r="S25" s="1"/>
-      <c r="T25" s="1"/>
+        <v>29875.5</v>
+      </c>
+      <c r="S25" s="1">
+        <v>463.18</v>
+      </c>
+      <c r="T25" s="1">
+        <v>463.18</v>
+      </c>
       <c r="U25" s="1">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="V25" s="1">
         <v>0</v>
@@ -2058,48 +1991,52 @@
         <v>0</v>
       </c>
       <c r="F26" s="1">
-        <v>2900</v>
+        <v>700</v>
       </c>
       <c r="G26" s="1">
-        <v>770</v>
+        <v>4300</v>
       </c>
       <c r="H26" t="s">
         <v>2</v>
       </c>
       <c r="I26" s="1">
-        <v>157.43</v>
+        <v>188.44</v>
       </c>
       <c r="J26" s="1">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="K26" s="1">
-        <v>998</v>
+        <v>5582.59</v>
       </c>
       <c r="L26" s="1">
-        <v>998.9</v>
+        <v>5657.95</v>
       </c>
       <c r="M26" s="1">
-        <v>-6612</v>
+        <v>-8978.1</v>
       </c>
       <c r="N26" s="1">
-        <v>-22.84</v>
+        <v>-22.97</v>
       </c>
       <c r="O26" s="1">
-        <v>-6638.05</v>
+        <v>-9505.6200000000008</v>
       </c>
       <c r="P26" s="1">
-        <v>-22.91</v>
+        <v>-24</v>
       </c>
       <c r="Q26" s="1">
-        <v>22330</v>
+        <v>30100</v>
       </c>
       <c r="R26" s="1">
-        <v>22330</v>
-      </c>
-      <c r="S26" s="1"/>
-      <c r="T26" s="1"/>
+        <v>30100</v>
+      </c>
+      <c r="S26" s="1">
+        <v>242.42</v>
+      </c>
+      <c r="T26" s="1">
+        <v>242.42</v>
+      </c>
       <c r="U26" s="1">
-        <v>1.1000000000000001</v>
+        <v>1.49</v>
       </c>
       <c r="V26" s="1">
         <v>0</v>
@@ -2125,48 +2062,48 @@
         <v>0</v>
       </c>
       <c r="F27" s="1">
-        <v>252849</v>
+        <v>2900</v>
       </c>
       <c r="G27" s="1">
-        <v>36.200000000000003</v>
+        <v>748</v>
       </c>
       <c r="H27" t="s">
         <v>2</v>
       </c>
       <c r="I27" s="1">
-        <v>0</v>
+        <v>28.16</v>
       </c>
       <c r="J27" s="1">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="K27" s="1">
-        <v>40</v>
+        <v>998</v>
       </c>
       <c r="L27" s="1">
-        <v>40.04</v>
+        <v>998.9</v>
       </c>
       <c r="M27" s="1">
-        <v>-9598.14</v>
+        <v>-7250</v>
       </c>
       <c r="N27" s="1">
-        <v>-9.49</v>
+        <v>-25.05</v>
       </c>
       <c r="O27" s="1">
-        <v>-9695.41</v>
+        <v>-7276.05</v>
       </c>
       <c r="P27" s="1">
-        <v>-9.57</v>
+        <v>-25.11</v>
       </c>
       <c r="Q27" s="1">
-        <v>91531.34</v>
+        <v>21692</v>
       </c>
       <c r="R27" s="1">
-        <v>91531.34</v>
+        <v>21692</v>
       </c>
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
       <c r="U27" s="1">
-        <v>4.53</v>
+        <v>1.07</v>
       </c>
       <c r="V27" s="1">
         <v>0</v>
@@ -2192,10 +2129,10 @@
         <v>0</v>
       </c>
       <c r="F28" s="1">
-        <v>20000</v>
+        <v>252849</v>
       </c>
       <c r="G28" s="1">
-        <v>94.8</v>
+        <v>36</v>
       </c>
       <c r="H28" t="s">
         <v>2</v>
@@ -2204,36 +2141,36 @@
         <v>0</v>
       </c>
       <c r="J28" s="1">
-        <v>0</v>
+        <v>-0.55000000000000004</v>
       </c>
       <c r="K28" s="1">
-        <v>109.9</v>
+        <v>40</v>
       </c>
       <c r="L28" s="1">
-        <v>110</v>
+        <v>40.04</v>
       </c>
       <c r="M28" s="1">
-        <v>-3020</v>
+        <v>-10103.84</v>
       </c>
       <c r="N28" s="1">
-        <v>-13.73</v>
+        <v>-9.99</v>
       </c>
       <c r="O28" s="1">
-        <v>-3039.78</v>
+        <v>-10201.11</v>
       </c>
       <c r="P28" s="1">
-        <v>-13.81</v>
+        <v>-10.07</v>
       </c>
       <c r="Q28" s="1">
-        <v>18960</v>
+        <v>91025.64</v>
       </c>
       <c r="R28" s="1">
-        <v>18960</v>
+        <v>91025.64</v>
       </c>
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
       <c r="U28" s="1">
-        <v>0.94</v>
+        <v>4.5</v>
       </c>
       <c r="V28" s="1">
         <v>0</v>
@@ -2259,48 +2196,48 @@
         <v>0</v>
       </c>
       <c r="F29" s="1">
-        <v>500</v>
+        <v>20000</v>
       </c>
       <c r="G29" s="1">
-        <v>4563</v>
+        <v>94.8</v>
       </c>
       <c r="H29" t="s">
         <v>2</v>
       </c>
       <c r="I29" s="1">
-        <v>99.95</v>
+        <v>0</v>
       </c>
       <c r="J29" s="1">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>4481.99</v>
+        <v>109.9</v>
       </c>
       <c r="L29" s="1">
-        <v>4486.0200000000004</v>
+        <v>110</v>
       </c>
       <c r="M29" s="1">
-        <v>405.06</v>
+        <v>-3020</v>
       </c>
       <c r="N29" s="1">
-        <v>1.8</v>
+        <v>-13.73</v>
       </c>
       <c r="O29" s="1">
-        <v>384.91</v>
+        <v>-3039.78</v>
       </c>
       <c r="P29" s="1">
-        <v>1.71</v>
+        <v>-13.81</v>
       </c>
       <c r="Q29" s="1">
-        <v>22815</v>
+        <v>18960</v>
       </c>
       <c r="R29" s="1">
-        <v>22815</v>
+        <v>18960</v>
       </c>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
       <c r="U29" s="1">
-        <v>1.1299999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="V29" s="1">
         <v>0</v>
@@ -2314,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="B30" t="s">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="C30" t="s">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="D30" t="s">
         <v>0</v>
@@ -2325,55 +2262,51 @@
       <c r="E30" t="s">
         <v>0</v>
       </c>
-      <c r="F30" t="s">
-        <v>0</v>
-      </c>
-      <c r="G30" t="s">
-        <v>0</v>
+      <c r="F30" s="1">
+        <v>500</v>
+      </c>
+      <c r="G30" s="1">
+        <v>4553</v>
       </c>
       <c r="H30" t="s">
-        <v>0</v>
-      </c>
-      <c r="I30" t="s">
-        <v>0</v>
-      </c>
-      <c r="J30" t="s">
-        <v>0</v>
-      </c>
-      <c r="K30" t="s">
-        <v>0</v>
-      </c>
-      <c r="L30" t="s">
-        <v>0</v>
-      </c>
-      <c r="M30" t="s">
-        <v>0</v>
-      </c>
-      <c r="N30" t="s">
-        <v>0</v>
-      </c>
-      <c r="O30" t="s">
-        <v>0</v>
-      </c>
-      <c r="P30" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>0</v>
-      </c>
-      <c r="R30" t="s">
-        <v>0</v>
-      </c>
-      <c r="S30" t="s">
-        <v>0</v>
-      </c>
-      <c r="T30" t="s">
-        <v>0</v>
-      </c>
-      <c r="U30" t="s">
-        <v>0</v>
-      </c>
-      <c r="V30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I30" s="1">
+        <v>301.02</v>
+      </c>
+      <c r="J30" s="1">
+        <v>1.34</v>
+      </c>
+      <c r="K30" s="1">
+        <v>4481.99</v>
+      </c>
+      <c r="L30" s="1">
+        <v>4486.0200000000004</v>
+      </c>
+      <c r="M30" s="1">
+        <v>355.06</v>
+      </c>
+      <c r="N30" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="O30" s="1">
+        <v>334.91</v>
+      </c>
+      <c r="P30" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>22765</v>
+      </c>
+      <c r="R30" s="1">
+        <v>22765</v>
+      </c>
+      <c r="S30" s="1"/>
+      <c r="T30" s="1"/>
+      <c r="U30" s="1">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="V30" s="1">
         <v>0</v>
       </c>
       <c r="W30" t="s">
@@ -2385,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="C31" t="s">
         <v>0</v>
@@ -2429,8 +2362,8 @@
       <c r="P31" t="s">
         <v>0</v>
       </c>
-      <c r="Q31" s="1">
-        <v>515564.94</v>
+      <c r="Q31" t="s">
+        <v>0</v>
       </c>
       <c r="R31" t="s">
         <v>0</v>
@@ -2456,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="C32" t="s">
         <v>0</v>
@@ -2500,8 +2433,8 @@
       <c r="P32" t="s">
         <v>0</v>
       </c>
-      <c r="Q32" t="s">
-        <v>0</v>
+      <c r="Q32" s="1">
+        <v>557156.42000000004</v>
       </c>
       <c r="R32" t="s">
         <v>0</v>
@@ -2527,7 +2460,7 @@
         <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="C33" t="s">
         <v>0</v>
@@ -2598,10 +2531,10 @@
         <v>0</v>
       </c>
       <c r="B34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C34" t="s">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D34" t="s">
         <v>0</v>
@@ -2609,51 +2542,55 @@
       <c r="E34" t="s">
         <v>0</v>
       </c>
-      <c r="F34" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G34" s="1">
-        <v>121.15</v>
+      <c r="F34" t="s">
+        <v>0</v>
+      </c>
+      <c r="G34" t="s">
+        <v>0</v>
       </c>
       <c r="H34" t="s">
-        <v>2</v>
-      </c>
-      <c r="I34" s="1">
-        <v>0</v>
-      </c>
-      <c r="J34" s="1">
-        <v>0</v>
-      </c>
-      <c r="K34" s="1">
-        <v>120.64</v>
-      </c>
-      <c r="L34" s="1">
-        <v>120.76</v>
-      </c>
-      <c r="M34" s="1">
-        <v>153.11000000000001</v>
-      </c>
-      <c r="N34" s="1">
-        <v>0.42</v>
-      </c>
-      <c r="O34" s="1">
-        <v>116.23</v>
-      </c>
-      <c r="P34" s="1">
-        <v>0.32</v>
-      </c>
-      <c r="Q34" s="1">
-        <v>36345</v>
-      </c>
-      <c r="R34" s="1">
-        <v>36345</v>
-      </c>
-      <c r="S34" s="1"/>
-      <c r="T34" s="1"/>
-      <c r="U34" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="V34" s="1">
+        <v>0</v>
+      </c>
+      <c r="I34" t="s">
+        <v>0</v>
+      </c>
+      <c r="J34" t="s">
+        <v>0</v>
+      </c>
+      <c r="K34" t="s">
+        <v>0</v>
+      </c>
+      <c r="L34" t="s">
+        <v>0</v>
+      </c>
+      <c r="M34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N34" t="s">
+        <v>0</v>
+      </c>
+      <c r="O34" t="s">
+        <v>0</v>
+      </c>
+      <c r="P34" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>0</v>
+      </c>
+      <c r="R34" t="s">
+        <v>0</v>
+      </c>
+      <c r="S34" t="s">
+        <v>0</v>
+      </c>
+      <c r="T34" t="s">
+        <v>0</v>
+      </c>
+      <c r="U34" t="s">
+        <v>0</v>
+      </c>
+      <c r="V34" t="s">
         <v>0</v>
       </c>
       <c r="W34" t="s">
@@ -2677,48 +2614,48 @@
         <v>0</v>
       </c>
       <c r="F35" s="1">
-        <v>75688.77</v>
+        <v>30000</v>
       </c>
       <c r="G35" s="1">
-        <v>89.6</v>
+        <v>120.8</v>
       </c>
       <c r="H35" t="s">
         <v>2</v>
       </c>
       <c r="I35" s="1">
-        <v>-54.3</v>
+        <v>-178.45</v>
       </c>
       <c r="J35" s="1">
-        <v>-0.08</v>
+        <v>-0.49</v>
       </c>
       <c r="K35" s="1">
-        <v>74.53</v>
+        <v>120.64</v>
       </c>
       <c r="L35" s="1">
-        <v>81.37</v>
+        <v>120.76</v>
       </c>
       <c r="M35" s="1">
-        <v>11410.23</v>
+        <v>48.11</v>
       </c>
       <c r="N35" s="1">
-        <v>20.22</v>
+        <v>0.13</v>
       </c>
       <c r="O35" s="1">
-        <v>6229.22</v>
+        <v>11.23</v>
       </c>
       <c r="P35" s="1">
-        <v>10.11</v>
+        <v>0.03</v>
       </c>
       <c r="Q35" s="1">
-        <v>67817.14</v>
+        <v>36240</v>
       </c>
       <c r="R35" s="1">
-        <v>67817.14</v>
+        <v>36240</v>
       </c>
       <c r="S35" s="1"/>
       <c r="T35" s="1"/>
       <c r="U35" s="1">
-        <v>3.35</v>
+        <v>1.79</v>
       </c>
       <c r="V35" s="1">
         <v>0</v>
@@ -2744,48 +2681,48 @@
         <v>0</v>
       </c>
       <c r="F36" s="1">
-        <v>50000</v>
+        <v>75688.77</v>
       </c>
       <c r="G36" s="1">
-        <v>103.63</v>
+        <v>89.72</v>
       </c>
       <c r="H36" t="s">
         <v>2</v>
       </c>
       <c r="I36" s="1">
-        <v>0</v>
+        <v>-6.79</v>
       </c>
       <c r="J36" s="1">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="K36" s="1">
-        <v>99.28</v>
+        <v>74.53</v>
       </c>
       <c r="L36" s="1">
-        <v>102.54</v>
+        <v>81.37</v>
       </c>
       <c r="M36" s="1">
-        <v>2173.69</v>
+        <v>11501.05</v>
       </c>
       <c r="N36" s="1">
-        <v>4.37</v>
+        <v>20.38</v>
       </c>
       <c r="O36" s="1">
-        <v>546.4</v>
+        <v>6320.04</v>
       </c>
       <c r="P36" s="1">
-        <v>1.06</v>
+        <v>10.26</v>
       </c>
       <c r="Q36" s="1">
-        <v>51815</v>
+        <v>67907.960000000006</v>
       </c>
       <c r="R36" s="1">
-        <v>51815</v>
+        <v>67907.960000000006</v>
       </c>
       <c r="S36" s="1"/>
       <c r="T36" s="1"/>
       <c r="U36" s="1">
-        <v>2.56</v>
+        <v>3.36</v>
       </c>
       <c r="V36" s="1">
         <v>0</v>
@@ -2811,48 +2748,48 @@
         <v>0</v>
       </c>
       <c r="F37" s="1">
-        <v>25000</v>
+        <v>50000</v>
       </c>
       <c r="G37" s="1">
-        <v>99.16</v>
+        <v>103</v>
       </c>
       <c r="H37" t="s">
         <v>2</v>
       </c>
       <c r="I37" s="1">
-        <v>-72.099999999999994</v>
+        <v>0</v>
       </c>
       <c r="J37" s="1">
-        <v>-0.28999999999999998</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1">
-        <v>97.53</v>
+        <v>99.28</v>
       </c>
       <c r="L37" s="1">
-        <v>100.91</v>
+        <v>102.54</v>
       </c>
       <c r="M37" s="1">
-        <v>408.47</v>
+        <v>1858.69</v>
       </c>
       <c r="N37" s="1">
-        <v>1.67</v>
+        <v>3.74</v>
       </c>
       <c r="O37" s="1">
-        <v>-437.97</v>
+        <v>231.4</v>
       </c>
       <c r="P37" s="1">
-        <v>-1.73</v>
+        <v>0.45</v>
       </c>
       <c r="Q37" s="1">
-        <v>24790</v>
+        <v>51500</v>
       </c>
       <c r="R37" s="1">
-        <v>24790</v>
+        <v>51500</v>
       </c>
       <c r="S37" s="1"/>
       <c r="T37" s="1"/>
       <c r="U37" s="1">
-        <v>1.23</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="V37" s="1">
         <v>0</v>
@@ -2878,48 +2815,48 @@
         <v>0</v>
       </c>
       <c r="F38" s="1">
-        <v>80257.09</v>
+        <v>25000</v>
       </c>
       <c r="G38" s="1">
-        <v>112.36</v>
+        <v>99.24</v>
       </c>
       <c r="H38" t="s">
         <v>2</v>
       </c>
       <c r="I38" s="1">
-        <v>81.09</v>
+        <v>0</v>
       </c>
       <c r="J38" s="1">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="K38" s="1">
-        <v>94.06</v>
+        <v>97.53</v>
       </c>
       <c r="L38" s="1">
-        <v>99.76</v>
+        <v>100.91</v>
       </c>
       <c r="M38" s="1">
-        <v>14684.07</v>
+        <v>428.47</v>
       </c>
       <c r="N38" s="1">
-        <v>19.45</v>
+        <v>1.75</v>
       </c>
       <c r="O38" s="1">
-        <v>10115.52</v>
+        <v>-417.97</v>
       </c>
       <c r="P38" s="1">
-        <v>12.63</v>
+        <v>-1.65</v>
       </c>
       <c r="Q38" s="1">
-        <v>90176.87</v>
+        <v>24810</v>
       </c>
       <c r="R38" s="1">
-        <v>90176.87</v>
+        <v>24810</v>
       </c>
       <c r="S38" s="1"/>
       <c r="T38" s="1"/>
       <c r="U38" s="1">
-        <v>4.46</v>
+        <v>1.23</v>
       </c>
       <c r="V38" s="1">
         <v>0</v>
@@ -2945,48 +2882,48 @@
         <v>0</v>
       </c>
       <c r="F39" s="1">
-        <v>23000</v>
+        <v>80257.09</v>
       </c>
       <c r="G39" s="1">
-        <v>120.84</v>
+        <v>112.34</v>
       </c>
       <c r="H39" t="s">
         <v>2</v>
       </c>
       <c r="I39" s="1">
-        <v>-11.12</v>
+        <v>90.07</v>
       </c>
       <c r="J39" s="1">
-        <v>-0.04</v>
+        <v>0.1</v>
       </c>
       <c r="K39" s="1">
-        <v>120.19</v>
+        <v>94.06</v>
       </c>
       <c r="L39" s="1">
-        <v>120.3</v>
+        <v>99.76</v>
       </c>
       <c r="M39" s="1">
-        <v>149.49</v>
+        <v>14668.02</v>
       </c>
       <c r="N39" s="1">
-        <v>0.54</v>
+        <v>19.420000000000002</v>
       </c>
       <c r="O39" s="1">
-        <v>124.62</v>
+        <v>10099.459999999999</v>
       </c>
       <c r="P39" s="1">
-        <v>0.45</v>
+        <v>12.61</v>
       </c>
       <c r="Q39" s="1">
-        <v>27793.200000000001</v>
+        <v>90160.81</v>
       </c>
       <c r="R39" s="1">
-        <v>27793.200000000001</v>
+        <v>90160.81</v>
       </c>
       <c r="S39" s="1"/>
       <c r="T39" s="1"/>
       <c r="U39" s="1">
-        <v>1.37</v>
+        <v>4.46</v>
       </c>
       <c r="V39" s="1">
         <v>0</v>
@@ -3012,48 +2949,48 @@
         <v>0</v>
       </c>
       <c r="F40" s="1">
-        <v>100000</v>
+        <v>23000</v>
       </c>
       <c r="G40" s="1">
-        <v>92.34</v>
+        <v>120.93</v>
       </c>
       <c r="H40" t="s">
         <v>2</v>
       </c>
       <c r="I40" s="1">
-        <v>27.69</v>
+        <v>0</v>
       </c>
       <c r="J40" s="1">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="K40" s="1">
-        <v>74.83</v>
+        <v>120.19</v>
       </c>
       <c r="L40" s="1">
-        <v>82.14</v>
+        <v>120.3</v>
       </c>
       <c r="M40" s="1">
-        <v>17512.490000000002</v>
+        <v>170.19</v>
       </c>
       <c r="N40" s="1">
-        <v>23.4</v>
+        <v>0.61</v>
       </c>
       <c r="O40" s="1">
-        <v>10197.93</v>
+        <v>145.32</v>
       </c>
       <c r="P40" s="1">
-        <v>12.41</v>
+        <v>0.52</v>
       </c>
       <c r="Q40" s="1">
-        <v>92340</v>
+        <v>27813.9</v>
       </c>
       <c r="R40" s="1">
-        <v>92340</v>
+        <v>27813.9</v>
       </c>
       <c r="S40" s="1"/>
       <c r="T40" s="1"/>
       <c r="U40" s="1">
-        <v>4.57</v>
+        <v>1.38</v>
       </c>
       <c r="V40" s="1">
         <v>0</v>
@@ -3079,48 +3016,48 @@
         <v>0</v>
       </c>
       <c r="F41" s="1">
-        <v>45000</v>
+        <v>100000</v>
       </c>
       <c r="G41" s="1">
-        <v>99.91</v>
+        <v>92.33</v>
       </c>
       <c r="H41" t="s">
         <v>2</v>
       </c>
       <c r="I41" s="1">
-        <v>-112.68</v>
+        <v>27.69</v>
       </c>
       <c r="J41" s="1">
-        <v>-0.25</v>
+        <v>0.03</v>
       </c>
       <c r="K41" s="1">
-        <v>102.23</v>
+        <v>74.83</v>
       </c>
       <c r="L41" s="1">
-        <v>102.33</v>
+        <v>82.14</v>
       </c>
       <c r="M41" s="1">
-        <v>-1045.48</v>
+        <v>17502.490000000002</v>
       </c>
       <c r="N41" s="1">
-        <v>-2.27</v>
+        <v>23.39</v>
       </c>
       <c r="O41" s="1">
-        <v>-1086.9000000000001</v>
+        <v>10187.93</v>
       </c>
       <c r="P41" s="1">
-        <v>-2.36</v>
+        <v>12.4</v>
       </c>
       <c r="Q41" s="1">
-        <v>44959.5</v>
+        <v>92330</v>
       </c>
       <c r="R41" s="1">
-        <v>44959.5</v>
+        <v>92330</v>
       </c>
       <c r="S41" s="1"/>
       <c r="T41" s="1"/>
       <c r="U41" s="1">
-        <v>2.2200000000000002</v>
+        <v>4.57</v>
       </c>
       <c r="V41" s="1">
         <v>0</v>
@@ -3146,48 +3083,48 @@
         <v>0</v>
       </c>
       <c r="F42" s="1">
-        <v>30000</v>
+        <v>45000</v>
       </c>
       <c r="G42" s="1">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H42" t="s">
         <v>2</v>
       </c>
       <c r="I42" s="1">
-        <v>0</v>
+        <v>1293.5899999999999</v>
       </c>
       <c r="J42" s="1">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="K42" s="1">
-        <v>99</v>
+        <v>102.23</v>
       </c>
       <c r="L42" s="1">
-        <v>99.09</v>
+        <v>102.33</v>
       </c>
       <c r="M42" s="1">
-        <v>0</v>
+        <v>-104.98</v>
       </c>
       <c r="N42" s="1">
-        <v>0</v>
+        <v>-0.22</v>
       </c>
       <c r="O42" s="1">
-        <v>-26.73</v>
+        <v>-146.4</v>
       </c>
       <c r="P42" s="1">
-        <v>-0.08</v>
+        <v>-0.31</v>
       </c>
       <c r="Q42" s="1">
-        <v>29700</v>
+        <v>45900</v>
       </c>
       <c r="R42" s="1">
-        <v>29700</v>
+        <v>45900</v>
       </c>
       <c r="S42" s="1"/>
       <c r="T42" s="1"/>
       <c r="U42" s="1">
-        <v>1.47</v>
+        <v>2.27</v>
       </c>
       <c r="V42" s="1">
         <v>0</v>
@@ -3213,10 +3150,10 @@
         <v>0</v>
       </c>
       <c r="F43" s="1">
-        <v>25133</v>
+        <v>30000</v>
       </c>
       <c r="G43" s="1">
-        <v>100.69</v>
+        <v>99</v>
       </c>
       <c r="H43" t="s">
         <v>2</v>
@@ -3228,33 +3165,33 @@
         <v>0</v>
       </c>
       <c r="K43" s="1">
-        <v>97.53</v>
+        <v>99</v>
       </c>
       <c r="L43" s="1">
-        <v>99.56</v>
+        <v>99.09</v>
       </c>
       <c r="M43" s="1">
-        <v>794.65</v>
+        <v>0</v>
       </c>
       <c r="N43" s="1">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O43" s="1">
-        <v>284.12</v>
+        <v>-26.73</v>
       </c>
       <c r="P43" s="1">
-        <v>1.1299999999999999</v>
+        <v>-0.08</v>
       </c>
       <c r="Q43" s="1">
-        <v>25306.42</v>
+        <v>29700</v>
       </c>
       <c r="R43" s="1">
-        <v>25306.42</v>
+        <v>29700</v>
       </c>
       <c r="S43" s="1"/>
       <c r="T43" s="1"/>
       <c r="U43" s="1">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="V43" s="1">
         <v>0</v>
@@ -3280,10 +3217,10 @@
         <v>0</v>
       </c>
       <c r="F44" s="1">
-        <v>40000</v>
+        <v>25133</v>
       </c>
       <c r="G44" s="1">
-        <v>96</v>
+        <v>100.61</v>
       </c>
       <c r="H44" t="s">
         <v>2</v>
@@ -3295,33 +3232,33 @@
         <v>0</v>
       </c>
       <c r="K44" s="1">
-        <v>84.49</v>
+        <v>97.53</v>
       </c>
       <c r="L44" s="1">
-        <v>94.72</v>
+        <v>99.56</v>
       </c>
       <c r="M44" s="1">
-        <v>4603.63</v>
+        <v>774.54</v>
       </c>
       <c r="N44" s="1">
-        <v>13.62</v>
+        <v>3.15</v>
       </c>
       <c r="O44" s="1">
-        <v>512.16</v>
+        <v>264.01</v>
       </c>
       <c r="P44" s="1">
-        <v>1.35</v>
+        <v>1.05</v>
       </c>
       <c r="Q44" s="1">
-        <v>38400</v>
+        <v>25286.31</v>
       </c>
       <c r="R44" s="1">
-        <v>38400</v>
+        <v>25286.31</v>
       </c>
       <c r="S44" s="1"/>
       <c r="T44" s="1"/>
       <c r="U44" s="1">
-        <v>1.9</v>
+        <v>1.25</v>
       </c>
       <c r="V44" s="1">
         <v>0</v>
@@ -3347,48 +3284,48 @@
         <v>0</v>
       </c>
       <c r="F45" s="1">
-        <v>41667.919999999998</v>
+        <v>40000</v>
       </c>
       <c r="G45" s="1">
-        <v>109.78</v>
+        <v>95.4</v>
       </c>
       <c r="H45" t="s">
         <v>2</v>
       </c>
       <c r="I45" s="1">
-        <v>54.83</v>
+        <v>0</v>
       </c>
       <c r="J45" s="1">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="K45" s="1">
-        <v>107.93</v>
+        <v>84.49</v>
       </c>
       <c r="L45" s="1">
-        <v>108.14</v>
+        <v>94.72</v>
       </c>
       <c r="M45" s="1">
-        <v>772.68</v>
+        <v>4363.63</v>
       </c>
       <c r="N45" s="1">
-        <v>1.71</v>
+        <v>12.91</v>
       </c>
       <c r="O45" s="1">
-        <v>684.5</v>
+        <v>272.16000000000003</v>
       </c>
       <c r="P45" s="1">
-        <v>1.51</v>
+        <v>0.71</v>
       </c>
       <c r="Q45" s="1">
-        <v>45743.040000000001</v>
+        <v>38160</v>
       </c>
       <c r="R45" s="1">
-        <v>45743.040000000001</v>
+        <v>38160</v>
       </c>
       <c r="S45" s="1"/>
       <c r="T45" s="1"/>
       <c r="U45" s="1">
-        <v>2.2599999999999998</v>
+        <v>1.89</v>
       </c>
       <c r="V45" s="1">
         <v>0</v>
@@ -3414,48 +3351,48 @@
         <v>0</v>
       </c>
       <c r="F46" s="1">
-        <v>61602</v>
+        <v>41667.919999999998</v>
       </c>
       <c r="G46" s="1">
-        <v>96.58</v>
+        <v>109.77</v>
       </c>
       <c r="H46" t="s">
         <v>2</v>
       </c>
       <c r="I46" s="1">
-        <v>71.31</v>
+        <v>-9.15</v>
       </c>
       <c r="J46" s="1">
-        <v>0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="K46" s="1">
-        <v>86.1</v>
+        <v>107.93</v>
       </c>
       <c r="L46" s="1">
-        <v>88.3</v>
+        <v>108.14</v>
       </c>
       <c r="M46" s="1">
-        <v>6454.84</v>
+        <v>768.52</v>
       </c>
       <c r="N46" s="1">
-        <v>12.16</v>
+        <v>1.7</v>
       </c>
       <c r="O46" s="1">
-        <v>5098.4399999999996</v>
+        <v>680.34</v>
       </c>
       <c r="P46" s="1">
-        <v>9.3699999999999992</v>
+        <v>1.5</v>
       </c>
       <c r="Q46" s="1">
-        <v>59495.21</v>
+        <v>45738.879999999997</v>
       </c>
       <c r="R46" s="1">
-        <v>59495.21</v>
+        <v>45738.879999999997</v>
       </c>
       <c r="S46" s="1"/>
       <c r="T46" s="1"/>
       <c r="U46" s="1">
-        <v>2.94</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="V46" s="1">
         <v>0</v>
@@ -3481,48 +3418,48 @@
         <v>0</v>
       </c>
       <c r="F47" s="1">
-        <v>57435.9</v>
+        <v>61602</v>
       </c>
       <c r="G47" s="1">
-        <v>119.3</v>
+        <v>96.54</v>
       </c>
       <c r="H47" t="s">
         <v>2</v>
       </c>
       <c r="I47" s="1">
-        <v>54.77</v>
+        <v>0</v>
       </c>
       <c r="J47" s="1">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="K47" s="1">
-        <v>106.92</v>
+        <v>86.1</v>
       </c>
       <c r="L47" s="1">
-        <v>110.63</v>
+        <v>88.3</v>
       </c>
       <c r="M47" s="1">
-        <v>7110.27</v>
+        <v>6430.2</v>
       </c>
       <c r="N47" s="1">
-        <v>11.57</v>
+        <v>12.12</v>
       </c>
       <c r="O47" s="1">
-        <v>4977.34</v>
+        <v>5073.8</v>
       </c>
       <c r="P47" s="1">
-        <v>7.83</v>
+        <v>9.32</v>
       </c>
       <c r="Q47" s="1">
-        <v>68521.03</v>
+        <v>59470.57</v>
       </c>
       <c r="R47" s="1">
-        <v>68521.03</v>
+        <v>59470.57</v>
       </c>
       <c r="S47" s="1"/>
       <c r="T47" s="1"/>
       <c r="U47" s="1">
-        <v>3.39</v>
+        <v>2.94</v>
       </c>
       <c r="V47" s="1">
         <v>0</v>
@@ -3548,48 +3485,48 @@
         <v>0</v>
       </c>
       <c r="F48" s="1">
-        <v>45000</v>
+        <v>57435.9</v>
       </c>
       <c r="G48" s="1">
-        <v>104.1</v>
+        <v>119.33</v>
       </c>
       <c r="H48" t="s">
         <v>2</v>
       </c>
       <c r="I48" s="1">
-        <v>28.09</v>
+        <v>20.56</v>
       </c>
       <c r="J48" s="1">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="K48" s="1">
-        <v>101.08</v>
+        <v>106.92</v>
       </c>
       <c r="L48" s="1">
-        <v>106.6</v>
+        <v>110.63</v>
       </c>
       <c r="M48" s="1">
-        <v>1359.98</v>
+        <v>7127.5</v>
       </c>
       <c r="N48" s="1">
-        <v>2.98</v>
+        <v>11.6</v>
       </c>
       <c r="O48" s="1">
-        <v>-1123.1199999999999</v>
+        <v>4994.57</v>
       </c>
       <c r="P48" s="1">
-        <v>-2.34</v>
+        <v>7.86</v>
       </c>
       <c r="Q48" s="1">
-        <v>46845</v>
+        <v>68538.259999999995</v>
       </c>
       <c r="R48" s="1">
-        <v>46845</v>
+        <v>68538.259999999995</v>
       </c>
       <c r="S48" s="1"/>
       <c r="T48" s="1"/>
       <c r="U48" s="1">
-        <v>2.3199999999999998</v>
+        <v>3.39</v>
       </c>
       <c r="V48" s="1">
         <v>0</v>
@@ -3615,48 +3552,48 @@
         <v>0</v>
       </c>
       <c r="F49" s="1">
-        <v>40000</v>
+        <v>45000</v>
       </c>
       <c r="G49" s="1">
-        <v>118.8</v>
+        <v>104.2</v>
       </c>
       <c r="H49" t="s">
         <v>2</v>
       </c>
       <c r="I49" s="1">
-        <v>0</v>
+        <v>-23.46</v>
       </c>
       <c r="J49" s="1">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="K49" s="1">
-        <v>109.11</v>
+        <v>101.08</v>
       </c>
       <c r="L49" s="1">
-        <v>111.45</v>
+        <v>106.6</v>
       </c>
       <c r="M49" s="1">
-        <v>3877.39</v>
+        <v>1404.98</v>
       </c>
       <c r="N49" s="1">
-        <v>8.8800000000000008</v>
+        <v>3.08</v>
       </c>
       <c r="O49" s="1">
-        <v>2941.07</v>
+        <v>-1078.1199999999999</v>
       </c>
       <c r="P49" s="1">
-        <v>6.59</v>
+        <v>-2.2400000000000002</v>
       </c>
       <c r="Q49" s="1">
-        <v>47520</v>
+        <v>46890</v>
       </c>
       <c r="R49" s="1">
-        <v>47520</v>
+        <v>46890</v>
       </c>
       <c r="S49" s="1"/>
       <c r="T49" s="1"/>
       <c r="U49" s="1">
-        <v>2.35</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="V49" s="1">
         <v>0</v>
@@ -3682,10 +3619,10 @@
         <v>0</v>
       </c>
       <c r="F50" s="1">
-        <v>24000</v>
+        <v>40000</v>
       </c>
       <c r="G50" s="1">
-        <v>121.52</v>
+        <v>118.95</v>
       </c>
       <c r="H50" t="s">
         <v>2</v>
@@ -3697,33 +3634,33 @@
         <v>0</v>
       </c>
       <c r="K50" s="1">
-        <v>121</v>
+        <v>109.11</v>
       </c>
       <c r="L50" s="1">
-        <v>121.13</v>
+        <v>111.45</v>
       </c>
       <c r="M50" s="1">
-        <v>124.79</v>
+        <v>3937.39</v>
       </c>
       <c r="N50" s="1">
-        <v>0.42</v>
+        <v>9.02</v>
       </c>
       <c r="O50" s="1">
-        <v>94.21</v>
+        <v>3001.07</v>
       </c>
       <c r="P50" s="1">
-        <v>0.32</v>
+        <v>6.73</v>
       </c>
       <c r="Q50" s="1">
-        <v>29164.799999999999</v>
+        <v>47580</v>
       </c>
       <c r="R50" s="1">
-        <v>29164.799999999999</v>
+        <v>47580</v>
       </c>
       <c r="S50" s="1"/>
       <c r="T50" s="1"/>
       <c r="U50" s="1">
-        <v>1.44</v>
+        <v>2.35</v>
       </c>
       <c r="V50" s="1">
         <v>0</v>
@@ -3749,10 +3686,10 @@
         <v>0</v>
       </c>
       <c r="F51" s="1">
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="G51" s="1">
-        <v>142.80000000000001</v>
+        <v>121.39</v>
       </c>
       <c r="H51" t="s">
         <v>2</v>
@@ -3764,33 +3701,33 @@
         <v>0</v>
       </c>
       <c r="K51" s="1">
-        <v>121.85</v>
+        <v>121</v>
       </c>
       <c r="L51" s="1">
-        <v>124.11</v>
+        <v>121.13</v>
       </c>
       <c r="M51" s="1">
-        <v>4189.97</v>
+        <v>93.59</v>
       </c>
       <c r="N51" s="1">
-        <v>17.190000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="O51" s="1">
-        <v>3737.68</v>
+        <v>63.01</v>
       </c>
       <c r="P51" s="1">
-        <v>15.05</v>
+        <v>0.21</v>
       </c>
       <c r="Q51" s="1">
-        <v>28560</v>
+        <v>29133.599999999999</v>
       </c>
       <c r="R51" s="1">
-        <v>28560</v>
+        <v>29133.599999999999</v>
       </c>
       <c r="S51" s="1"/>
       <c r="T51" s="1"/>
       <c r="U51" s="1">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="V51" s="1">
         <v>0</v>
@@ -3804,10 +3741,10 @@
         <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C52" t="s">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="D52" t="s">
         <v>0</v>
@@ -3815,55 +3752,51 @@
       <c r="E52" t="s">
         <v>0</v>
       </c>
-      <c r="F52" t="s">
-        <v>0</v>
-      </c>
-      <c r="G52" t="s">
-        <v>0</v>
+      <c r="F52" s="1">
+        <v>20000</v>
+      </c>
+      <c r="G52" s="1">
+        <v>144.69999999999999</v>
       </c>
       <c r="H52" t="s">
-        <v>0</v>
-      </c>
-      <c r="I52" t="s">
-        <v>0</v>
-      </c>
-      <c r="J52" t="s">
-        <v>0</v>
-      </c>
-      <c r="K52" t="s">
-        <v>0</v>
-      </c>
-      <c r="L52" t="s">
-        <v>0</v>
-      </c>
-      <c r="M52" t="s">
-        <v>0</v>
-      </c>
-      <c r="N52" t="s">
-        <v>0</v>
-      </c>
-      <c r="O52" t="s">
-        <v>0</v>
-      </c>
-      <c r="P52" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>0</v>
-      </c>
-      <c r="R52" t="s">
-        <v>0</v>
-      </c>
-      <c r="S52" t="s">
-        <v>0</v>
-      </c>
-      <c r="T52" t="s">
-        <v>0</v>
-      </c>
-      <c r="U52" t="s">
-        <v>0</v>
-      </c>
-      <c r="V52" t="s">
+        <v>2</v>
+      </c>
+      <c r="I52" s="1">
+        <v>-218.69</v>
+      </c>
+      <c r="J52" s="1">
+        <v>-0.75</v>
+      </c>
+      <c r="K52" s="1">
+        <v>121.85</v>
+      </c>
+      <c r="L52" s="1">
+        <v>124.11</v>
+      </c>
+      <c r="M52" s="1">
+        <v>4569.97</v>
+      </c>
+      <c r="N52" s="1">
+        <v>18.75</v>
+      </c>
+      <c r="O52" s="1">
+        <v>4117.68</v>
+      </c>
+      <c r="P52" s="1">
+        <v>16.579999999999998</v>
+      </c>
+      <c r="Q52" s="1">
+        <v>28940</v>
+      </c>
+      <c r="R52" s="1">
+        <v>28940</v>
+      </c>
+      <c r="S52" s="1"/>
+      <c r="T52" s="1"/>
+      <c r="U52" s="1">
+        <v>1.43</v>
+      </c>
+      <c r="V52" s="1">
         <v>0</v>
       </c>
       <c r="W52" t="s">
@@ -3875,7 +3808,7 @@
         <v>0</v>
       </c>
       <c r="B53" t="s">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="C53" t="s">
         <v>0</v>
@@ -3919,8 +3852,8 @@
       <c r="P53" t="s">
         <v>0</v>
       </c>
-      <c r="Q53" s="1">
-        <v>855292.21</v>
+      <c r="Q53" t="s">
+        <v>0</v>
       </c>
       <c r="R53" t="s">
         <v>0</v>
@@ -3946,7 +3879,7 @@
         <v>0</v>
       </c>
       <c r="B54" t="s">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="C54" t="s">
         <v>0</v>
@@ -3990,8 +3923,8 @@
       <c r="P54" t="s">
         <v>0</v>
       </c>
-      <c r="Q54" t="s">
-        <v>0</v>
+      <c r="Q54" s="1">
+        <v>856100.29</v>
       </c>
       <c r="R54" t="s">
         <v>0</v>
@@ -4017,7 +3950,7 @@
         <v>0</v>
       </c>
       <c r="B55" t="s">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="C55" t="s">
         <v>0</v>
@@ -4088,10 +4021,10 @@
         <v>0</v>
       </c>
       <c r="B56" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C56" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="D56" t="s">
         <v>0</v>
@@ -4099,51 +4032,55 @@
       <c r="E56" t="s">
         <v>0</v>
       </c>
-      <c r="F56" s="1">
-        <v>45000</v>
-      </c>
-      <c r="G56" s="1">
-        <v>127.28</v>
+      <c r="F56" t="s">
+        <v>0</v>
+      </c>
+      <c r="G56" t="s">
+        <v>0</v>
       </c>
       <c r="H56" t="s">
-        <v>3</v>
-      </c>
-      <c r="I56" s="1">
-        <v>26.89</v>
-      </c>
-      <c r="J56" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="K56" s="1">
-        <v>120.19</v>
-      </c>
-      <c r="L56" s="1">
-        <v>125.11</v>
-      </c>
-      <c r="M56" s="1">
-        <v>9548.7000000000007</v>
-      </c>
-      <c r="N56" s="1">
-        <v>5.9</v>
-      </c>
-      <c r="O56" s="1">
-        <v>2918.01</v>
-      </c>
-      <c r="P56" s="1">
-        <v>1.73</v>
-      </c>
-      <c r="Q56" s="1">
-        <v>171312.52</v>
-      </c>
-      <c r="R56" s="1">
-        <v>57276</v>
-      </c>
-      <c r="S56" s="1"/>
-      <c r="T56" s="1"/>
-      <c r="U56" s="1">
-        <v>8.4700000000000006</v>
-      </c>
-      <c r="V56" s="1">
+        <v>0</v>
+      </c>
+      <c r="I56" t="s">
+        <v>0</v>
+      </c>
+      <c r="J56" t="s">
+        <v>0</v>
+      </c>
+      <c r="K56" t="s">
+        <v>0</v>
+      </c>
+      <c r="L56" t="s">
+        <v>0</v>
+      </c>
+      <c r="M56" t="s">
+        <v>0</v>
+      </c>
+      <c r="N56" t="s">
+        <v>0</v>
+      </c>
+      <c r="O56" t="s">
+        <v>0</v>
+      </c>
+      <c r="P56" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>0</v>
+      </c>
+      <c r="R56" t="s">
+        <v>0</v>
+      </c>
+      <c r="S56" t="s">
+        <v>0</v>
+      </c>
+      <c r="T56" t="s">
+        <v>0</v>
+      </c>
+      <c r="U56" t="s">
+        <v>0</v>
+      </c>
+      <c r="V56" t="s">
         <v>0</v>
       </c>
       <c r="W56" t="s">
@@ -4167,48 +4104,48 @@
         <v>0</v>
       </c>
       <c r="F57" s="1">
-        <v>169000</v>
+        <v>45000</v>
       </c>
       <c r="G57" s="1">
-        <v>106.1</v>
+        <v>127.37</v>
       </c>
       <c r="H57" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I57" s="1">
-        <v>16.850000000000001</v>
+        <v>40.020000000000003</v>
       </c>
       <c r="J57" s="1">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K57" s="1">
-        <v>105.16</v>
+        <v>120.19</v>
       </c>
       <c r="L57" s="1">
-        <v>105.53</v>
+        <v>125.11</v>
       </c>
       <c r="M57" s="1">
-        <v>1581.33</v>
+        <v>9608.41</v>
       </c>
       <c r="N57" s="1">
-        <v>0.88</v>
+        <v>5.97</v>
       </c>
       <c r="O57" s="1">
-        <v>963.3</v>
+        <v>3019.84</v>
       </c>
       <c r="P57" s="1">
-        <v>0.54</v>
+        <v>1.8</v>
       </c>
       <c r="Q57" s="1">
-        <v>179309</v>
+        <v>170344.64</v>
       </c>
       <c r="R57" s="1">
-        <v>179309</v>
+        <v>57316.5</v>
       </c>
       <c r="S57" s="1"/>
       <c r="T57" s="1"/>
       <c r="U57" s="1">
-        <v>8.8699999999999992</v>
+        <v>8.43</v>
       </c>
       <c r="V57" s="1">
         <v>0</v>
@@ -4222,10 +4159,10 @@
         <v>0</v>
       </c>
       <c r="B58" t="s">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C58" t="s">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="D58" t="s">
         <v>0</v>
@@ -4233,55 +4170,51 @@
       <c r="E58" t="s">
         <v>0</v>
       </c>
-      <c r="F58" t="s">
-        <v>0</v>
-      </c>
-      <c r="G58" t="s">
-        <v>0</v>
+      <c r="F58" s="1">
+        <v>144000</v>
+      </c>
+      <c r="G58" s="1">
+        <v>106.15</v>
       </c>
       <c r="H58" t="s">
-        <v>0</v>
-      </c>
-      <c r="I58" t="s">
-        <v>0</v>
-      </c>
-      <c r="J58" t="s">
-        <v>0</v>
-      </c>
-      <c r="K58" t="s">
-        <v>0</v>
-      </c>
-      <c r="L58" t="s">
-        <v>0</v>
-      </c>
-      <c r="M58" t="s">
-        <v>0</v>
-      </c>
-      <c r="N58" t="s">
-        <v>0</v>
-      </c>
-      <c r="O58" t="s">
-        <v>0</v>
-      </c>
-      <c r="P58" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="s">
-        <v>0</v>
-      </c>
-      <c r="R58" t="s">
-        <v>0</v>
-      </c>
-      <c r="S58" t="s">
-        <v>0</v>
-      </c>
-      <c r="T58" t="s">
-        <v>0</v>
-      </c>
-      <c r="U58" t="s">
-        <v>0</v>
-      </c>
-      <c r="V58" t="s">
+        <v>2</v>
+      </c>
+      <c r="I58" s="1">
+        <v>0</v>
+      </c>
+      <c r="J58" s="1">
+        <v>0</v>
+      </c>
+      <c r="K58" s="1">
+        <v>105.16</v>
+      </c>
+      <c r="L58" s="1">
+        <v>105.53</v>
+      </c>
+      <c r="M58" s="1">
+        <v>1419.4</v>
+      </c>
+      <c r="N58" s="1">
+        <v>0.93</v>
+      </c>
+      <c r="O58" s="1">
+        <v>892.8</v>
+      </c>
+      <c r="P58" s="1">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="Q58" s="1">
+        <v>152856</v>
+      </c>
+      <c r="R58" s="1">
+        <v>152856</v>
+      </c>
+      <c r="S58" s="1"/>
+      <c r="T58" s="1"/>
+      <c r="U58" s="1">
+        <v>7.56</v>
+      </c>
+      <c r="V58" s="1">
         <v>0</v>
       </c>
       <c r="W58" t="s">
@@ -4293,7 +4226,7 @@
         <v>0</v>
       </c>
       <c r="B59" t="s">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C59" t="s">
         <v>0</v>
@@ -4337,8 +4270,8 @@
       <c r="P59" t="s">
         <v>0</v>
       </c>
-      <c r="Q59" s="1">
-        <v>350621.52</v>
+      <c r="Q59" t="s">
+        <v>0</v>
       </c>
       <c r="R59" t="s">
         <v>0</v>
@@ -4364,7 +4297,7 @@
         <v>0</v>
       </c>
       <c r="B60" t="s">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="C60" t="s">
         <v>0</v>
@@ -4408,8 +4341,8 @@
       <c r="P60" t="s">
         <v>0</v>
       </c>
-      <c r="Q60" t="s">
-        <v>0</v>
+      <c r="Q60" s="1">
+        <v>323200.64000000001</v>
       </c>
       <c r="R60" t="s">
         <v>0</v>
@@ -4435,7 +4368,7 @@
         <v>0</v>
       </c>
       <c r="B61" t="s">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="C61" t="s">
         <v>0</v>
@@ -4506,10 +4439,10 @@
         <v>0</v>
       </c>
       <c r="B62" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C62" t="s">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D62" t="s">
         <v>0</v>
@@ -4517,51 +4450,55 @@
       <c r="E62" t="s">
         <v>0</v>
       </c>
-      <c r="F62" s="1">
-        <v>703</v>
-      </c>
-      <c r="G62" s="1">
-        <v>39530</v>
+      <c r="F62" t="s">
+        <v>0</v>
+      </c>
+      <c r="G62" t="s">
+        <v>0</v>
       </c>
       <c r="H62" t="s">
-        <v>2</v>
-      </c>
-      <c r="I62" s="1">
-        <v>1465.08</v>
-      </c>
-      <c r="J62" s="1">
-        <v>0.53</v>
-      </c>
-      <c r="K62" s="1">
-        <v>34092.879999999997</v>
-      </c>
-      <c r="L62" s="1">
-        <v>34168.11</v>
-      </c>
-      <c r="M62" s="1">
-        <v>38222.949999999997</v>
-      </c>
-      <c r="N62" s="1">
-        <v>15.94</v>
-      </c>
-      <c r="O62" s="1">
-        <v>37694.11</v>
-      </c>
-      <c r="P62" s="1">
-        <v>15.69</v>
-      </c>
-      <c r="Q62" s="1">
-        <v>277895.90000000002</v>
-      </c>
-      <c r="R62" s="1">
-        <v>277895.90000000002</v>
-      </c>
-      <c r="S62" s="1"/>
-      <c r="T62" s="1"/>
-      <c r="U62" s="1">
-        <v>13.74</v>
-      </c>
-      <c r="V62" s="1">
+        <v>0</v>
+      </c>
+      <c r="I62" t="s">
+        <v>0</v>
+      </c>
+      <c r="J62" t="s">
+        <v>0</v>
+      </c>
+      <c r="K62" t="s">
+        <v>0</v>
+      </c>
+      <c r="L62" t="s">
+        <v>0</v>
+      </c>
+      <c r="M62" t="s">
+        <v>0</v>
+      </c>
+      <c r="N62" t="s">
+        <v>0</v>
+      </c>
+      <c r="O62" t="s">
+        <v>0</v>
+      </c>
+      <c r="P62" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>0</v>
+      </c>
+      <c r="R62" t="s">
+        <v>0</v>
+      </c>
+      <c r="S62" t="s">
+        <v>0</v>
+      </c>
+      <c r="T62" t="s">
+        <v>0</v>
+      </c>
+      <c r="U62" t="s">
+        <v>0</v>
+      </c>
+      <c r="V62" t="s">
         <v>0</v>
       </c>
       <c r="W62" t="s">
@@ -4585,48 +4522,48 @@
         <v>0</v>
       </c>
       <c r="F63" s="1">
-        <v>1000</v>
+        <v>703</v>
       </c>
       <c r="G63" s="1">
-        <v>1812</v>
+        <v>39820</v>
       </c>
       <c r="H63" t="s">
         <v>2</v>
       </c>
       <c r="I63" s="1">
-        <v>490.11</v>
+        <v>3100.54</v>
       </c>
       <c r="J63" s="1">
-        <v>2.78</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="K63" s="1">
-        <v>2278</v>
+        <v>34092.879999999997</v>
       </c>
       <c r="L63" s="1">
-        <v>2280.0500000000002</v>
+        <v>34168.11</v>
       </c>
       <c r="M63" s="1">
-        <v>-4660</v>
+        <v>40261.65</v>
       </c>
       <c r="N63" s="1">
-        <v>-20.45</v>
+        <v>16.79</v>
       </c>
       <c r="O63" s="1">
-        <v>-4680.5</v>
+        <v>39732.81</v>
       </c>
       <c r="P63" s="1">
-        <v>-20.52</v>
+        <v>16.54</v>
       </c>
       <c r="Q63" s="1">
-        <v>18120</v>
+        <v>279934.59999999998</v>
       </c>
       <c r="R63" s="1">
-        <v>18120</v>
+        <v>279934.59999999998</v>
       </c>
       <c r="S63" s="1"/>
       <c r="T63" s="1"/>
       <c r="U63" s="1">
-        <v>0.9</v>
+        <v>13.85</v>
       </c>
       <c r="V63" s="1">
         <v>0</v>
@@ -4756,7 +4693,7 @@
         <v>0</v>
       </c>
       <c r="Q65" s="1">
-        <v>296015.90000000002</v>
+        <v>279934.59999999998</v>
       </c>
       <c r="R65" t="s">
         <v>0</v>
@@ -5438,10 +5375,10 @@
         <v>3</v>
       </c>
       <c r="I75" s="1">
-        <v>-26.59</v>
+        <v>-17.059999999999999</v>
       </c>
       <c r="J75" s="1">
-        <v>-3.67</v>
+        <v>-2.41</v>
       </c>
       <c r="K75" s="1">
         <v>0.59</v>
@@ -5450,22 +5387,22 @@
         <v>0.59</v>
       </c>
       <c r="M75" s="1">
-        <v>-537.87</v>
+        <v>-537.98</v>
       </c>
       <c r="N75" s="1">
-        <v>-43.54</v>
+        <v>-43.83</v>
       </c>
       <c r="O75" s="1">
-        <v>-546.24</v>
+        <v>-546.29999999999995</v>
       </c>
       <c r="P75" s="1">
-        <v>-43.92</v>
+        <v>-44.2</v>
       </c>
       <c r="Q75" s="1">
-        <v>697.41</v>
+        <v>689.44</v>
       </c>
       <c r="R75" s="1">
-        <v>233.17</v>
+        <v>231.98</v>
       </c>
       <c r="S75" s="1"/>
       <c r="T75" s="1"/>
@@ -5555,7 +5492,7 @@
         <v>0</v>
       </c>
       <c r="B77" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C77" t="s">
         <v>0</v>
@@ -5600,7 +5537,7 @@
         <v>0</v>
       </c>
       <c r="Q77" s="1">
-        <v>697.41</v>
+        <v>689.44</v>
       </c>
       <c r="R77" t="s">
         <v>0</v>

--- a/holdings.xlsx
+++ b/holdings.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chen\tase-ytm-dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0E60EF9-D232-4CCF-B060-7621CCD410BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{184E01F8-0665-4996-B877-D3D3AF2263E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="14235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="112">
   <si>
     <t/>
   </si>
@@ -103,18 +103,18 @@
     <t>מניות</t>
   </si>
   <si>
+    <t>אטראו שוקי הון</t>
+  </si>
+  <si>
+    <t>1096106</t>
+  </si>
+  <si>
     <t>אי.טי.ג'י.איי</t>
   </si>
   <si>
     <t>1176114</t>
   </si>
   <si>
-    <t>אלדן תחבורה</t>
-  </si>
-  <si>
-    <t>1134881</t>
-  </si>
-  <si>
     <t>אלטשולר שחם פנ</t>
   </si>
   <si>
@@ -307,12 +307,6 @@
     <t>7300171</t>
   </si>
   <si>
-    <t>רב בריח אג א</t>
-  </si>
-  <si>
-    <t>1209824</t>
-  </si>
-  <si>
     <t>:סה"כ אג״ח</t>
   </si>
   <si>
@@ -331,6 +325,12 @@
     <t>5140413</t>
   </si>
   <si>
+    <t>מור כספית ניהול</t>
+  </si>
+  <si>
+    <t>5139324</t>
+  </si>
+  <si>
     <t>:סה"כ קרנות נאמנות</t>
   </si>
   <si>
@@ -344,18 +344,6 @@
   </si>
   <si>
     <t>:סה"כ מחקי מדד</t>
-  </si>
-  <si>
-    <t>נגזרים</t>
-  </si>
-  <si>
-    <t>1 שובל הנדסה אפ</t>
-  </si>
-  <si>
-    <t>1215961</t>
-  </si>
-  <si>
-    <t>:סה"כ נגזרים</t>
   </si>
   <si>
     <t>ניע זרים</t>
@@ -762,7 +750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A5:W77"/>
+  <dimension ref="A5:W72"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.73046875" bestFit="1" customWidth="1"/>
@@ -1250,48 +1238,48 @@
         <v>0</v>
       </c>
       <c r="F15" s="1">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="G15" s="1">
-        <v>2000</v>
+        <v>6772</v>
       </c>
       <c r="H15" t="s">
         <v>2</v>
       </c>
       <c r="I15" s="1">
-        <v>-269.39999999999998</v>
+        <v>124.82</v>
       </c>
       <c r="J15" s="1">
-        <v>-0.89</v>
+        <v>0.37</v>
       </c>
       <c r="K15" s="1">
-        <v>2000</v>
+        <v>6688</v>
       </c>
       <c r="L15" s="1">
-        <v>2001.82</v>
+        <v>6694.02</v>
       </c>
       <c r="M15" s="1">
-        <v>0</v>
+        <v>419.99</v>
       </c>
       <c r="N15" s="1">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O15" s="1">
-        <v>-27.29</v>
+        <v>389.9</v>
       </c>
       <c r="P15" s="1">
-        <v>-0.09</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="Q15" s="1">
-        <v>30000</v>
+        <v>33860</v>
       </c>
       <c r="R15" s="1">
-        <v>30000</v>
+        <v>33860</v>
       </c>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
       <c r="U15" s="1">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="V15" s="1">
         <v>0</v>
@@ -1317,48 +1305,52 @@
         <v>0</v>
       </c>
       <c r="F16" s="1">
-        <v>4680</v>
+        <v>1500</v>
       </c>
       <c r="G16" s="1">
-        <v>729.6</v>
+        <v>2029</v>
       </c>
       <c r="H16" t="s">
         <v>2</v>
       </c>
       <c r="I16" s="1">
-        <v>-379.78</v>
+        <v>405.4</v>
       </c>
       <c r="J16" s="1">
-        <v>-1.1000000000000001</v>
+        <v>1.35</v>
       </c>
       <c r="K16" s="1">
-        <v>684.32</v>
+        <v>2000</v>
       </c>
       <c r="L16" s="1">
-        <v>698.43</v>
+        <v>2001.82</v>
       </c>
       <c r="M16" s="1">
-        <v>2119.11</v>
+        <v>435</v>
       </c>
       <c r="N16" s="1">
-        <v>6.61</v>
+        <v>1.45</v>
       </c>
       <c r="O16" s="1">
-        <v>1458.74</v>
+        <v>407.71</v>
       </c>
       <c r="P16" s="1">
-        <v>4.46</v>
+        <v>1.35</v>
       </c>
       <c r="Q16" s="1">
-        <v>34145.279999999999</v>
+        <v>30435</v>
       </c>
       <c r="R16" s="1">
-        <v>34145.279999999999</v>
-      </c>
-      <c r="S16" s="1"/>
-      <c r="T16" s="1"/>
+        <v>30435</v>
+      </c>
+      <c r="S16" s="1">
+        <v>676.18</v>
+      </c>
+      <c r="T16" s="1">
+        <v>676.18</v>
+      </c>
       <c r="U16" s="1">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="V16" s="1">
         <v>0</v>
@@ -1387,16 +1379,16 @@
         <v>6000</v>
       </c>
       <c r="G17" s="1">
-        <v>647.79999999999995</v>
+        <v>716.8</v>
       </c>
       <c r="H17" t="s">
         <v>2</v>
       </c>
       <c r="I17" s="1">
-        <v>487.43</v>
+        <v>648.11</v>
       </c>
       <c r="J17" s="1">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="K17" s="1">
         <v>575.66999999999996</v>
@@ -1405,27 +1397,27 @@
         <v>641.24</v>
       </c>
       <c r="M17" s="1">
-        <v>4327.6099999999997</v>
+        <v>8467.61</v>
       </c>
       <c r="N17" s="1">
-        <v>12.52</v>
+        <v>24.51</v>
       </c>
       <c r="O17" s="1">
-        <v>393.4</v>
+        <v>4533.3999999999996</v>
       </c>
       <c r="P17" s="1">
-        <v>1.02</v>
+        <v>11.78</v>
       </c>
       <c r="Q17" s="1">
-        <v>38868</v>
+        <v>43008</v>
       </c>
       <c r="R17" s="1">
-        <v>38868</v>
+        <v>43008</v>
       </c>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
       <c r="U17" s="1">
-        <v>1.92</v>
+        <v>2.13</v>
       </c>
       <c r="V17" s="1">
         <v>0</v>
@@ -1454,16 +1446,16 @@
         <v>93000</v>
       </c>
       <c r="G18" s="1">
-        <v>104.1</v>
+        <v>101.6</v>
       </c>
       <c r="H18" t="s">
         <v>2</v>
       </c>
       <c r="I18" s="1">
-        <v>0</v>
+        <v>-189.35</v>
       </c>
       <c r="J18" s="1">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="K18" s="1">
         <v>92.69</v>
@@ -1472,27 +1464,27 @@
         <v>89.42</v>
       </c>
       <c r="M18" s="1">
-        <v>10608.88</v>
+        <v>8283.8799999999992</v>
       </c>
       <c r="N18" s="1">
-        <v>12.3</v>
+        <v>9.6</v>
       </c>
       <c r="O18" s="1">
-        <v>13655.2</v>
+        <v>11330.2</v>
       </c>
       <c r="P18" s="1">
-        <v>16.420000000000002</v>
+        <v>13.62</v>
       </c>
       <c r="Q18" s="1">
-        <v>96813</v>
+        <v>94488</v>
       </c>
       <c r="R18" s="1">
-        <v>96813</v>
+        <v>94488</v>
       </c>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
       <c r="U18" s="1">
-        <v>4.79</v>
+        <v>4.67</v>
       </c>
       <c r="V18" s="1">
         <v>0</v>
@@ -1521,16 +1513,16 @@
         <v>172500</v>
       </c>
       <c r="G19" s="1">
-        <v>11.8</v>
+        <v>15.3</v>
       </c>
       <c r="H19" t="s">
         <v>2</v>
       </c>
       <c r="I19" s="1">
-        <v>171.56</v>
+        <v>343.84</v>
       </c>
       <c r="J19" s="1">
-        <v>0.85</v>
+        <v>1.32</v>
       </c>
       <c r="K19" s="1">
         <v>18.760000000000002</v>
@@ -1539,27 +1531,27 @@
         <v>18.78</v>
       </c>
       <c r="M19" s="1">
-        <v>-11998.92</v>
+        <v>-5961.42</v>
       </c>
       <c r="N19" s="1">
-        <v>-37.08</v>
+        <v>-18.420000000000002</v>
       </c>
       <c r="O19" s="1">
-        <v>-12032.17</v>
+        <v>-5994.67</v>
       </c>
       <c r="P19" s="1">
-        <v>-37.15</v>
+        <v>-18.5</v>
       </c>
       <c r="Q19" s="1">
-        <v>20355</v>
+        <v>26392.5</v>
       </c>
       <c r="R19" s="1">
-        <v>20355</v>
+        <v>26392.5</v>
       </c>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
       <c r="U19" s="1">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="V19" s="1">
         <v>0</v>
@@ -1588,16 +1580,16 @@
         <v>293</v>
       </c>
       <c r="G20" s="1">
-        <v>10700</v>
+        <v>9874</v>
       </c>
       <c r="H20" t="s">
         <v>2</v>
       </c>
       <c r="I20" s="1">
-        <v>877.63</v>
+        <v>-256.85000000000002</v>
       </c>
       <c r="J20" s="1">
-        <v>2.88</v>
+        <v>-0.88</v>
       </c>
       <c r="K20" s="1">
         <v>19220.14</v>
@@ -1606,27 +1598,27 @@
         <v>19264.77</v>
       </c>
       <c r="M20" s="1">
-        <v>-24964.01</v>
+        <v>-27384.19</v>
       </c>
       <c r="N20" s="1">
-        <v>-44.32</v>
+        <v>-48.62</v>
       </c>
       <c r="O20" s="1">
-        <v>-25094.76</v>
+        <v>-27514.94</v>
       </c>
       <c r="P20" s="1">
-        <v>-44.45</v>
+        <v>-48.74</v>
       </c>
       <c r="Q20" s="1">
-        <v>31351</v>
+        <v>28930.82</v>
       </c>
       <c r="R20" s="1">
-        <v>31351</v>
+        <v>28930.82</v>
       </c>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
       <c r="U20" s="1">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="V20" s="1">
         <v>0</v>
@@ -1655,16 +1647,16 @@
         <v>2200</v>
       </c>
       <c r="G21" s="1">
-        <v>1127</v>
+        <v>1190</v>
       </c>
       <c r="H21" t="s">
         <v>2</v>
       </c>
       <c r="I21" s="1">
-        <v>155.22</v>
+        <v>-20.96</v>
       </c>
       <c r="J21" s="1">
-        <v>0.63</v>
+        <v>-0.08</v>
       </c>
       <c r="K21" s="1">
         <v>1374</v>
@@ -1673,27 +1665,27 @@
         <v>1375.24</v>
       </c>
       <c r="M21" s="1">
-        <v>-5434</v>
+        <v>-4048</v>
       </c>
       <c r="N21" s="1">
-        <v>-17.97</v>
+        <v>-13.39</v>
       </c>
       <c r="O21" s="1">
-        <v>-5461.21</v>
+        <v>-4075.21</v>
       </c>
       <c r="P21" s="1">
-        <v>-18.05</v>
+        <v>-13.46</v>
       </c>
       <c r="Q21" s="1">
-        <v>24794</v>
+        <v>26180</v>
       </c>
       <c r="R21" s="1">
-        <v>24794</v>
+        <v>26180</v>
       </c>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
       <c r="U21" s="1">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="V21" s="1">
         <v>0</v>
@@ -1722,16 +1714,16 @@
         <v>1000</v>
       </c>
       <c r="G22" s="1">
-        <v>58.7</v>
+        <v>57.7</v>
       </c>
       <c r="H22" t="s">
         <v>2</v>
       </c>
       <c r="I22" s="1">
-        <v>28.01</v>
+        <v>44.02</v>
       </c>
       <c r="J22" s="1">
-        <v>5.01</v>
+        <v>8.26</v>
       </c>
       <c r="K22" s="1">
         <v>55</v>
@@ -1740,22 +1732,22 @@
         <v>55.45</v>
       </c>
       <c r="M22" s="1">
-        <v>36.99</v>
+        <v>26.99</v>
       </c>
       <c r="N22" s="1">
-        <v>6.72</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="O22" s="1">
-        <v>32.5</v>
+        <v>22.5</v>
       </c>
       <c r="P22" s="1">
-        <v>5.86</v>
+        <v>4.05</v>
       </c>
       <c r="Q22" s="1">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="R22" s="1">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
@@ -1789,16 +1781,16 @@
         <v>1000</v>
       </c>
       <c r="G23" s="1">
-        <v>2777</v>
+        <v>3119</v>
       </c>
       <c r="H23" t="s">
         <v>2</v>
       </c>
       <c r="I23" s="1">
-        <v>171.11</v>
+        <v>-191.43</v>
       </c>
       <c r="J23" s="1">
-        <v>0.62</v>
+        <v>-0.61</v>
       </c>
       <c r="K23" s="1">
         <v>2472</v>
@@ -1807,27 +1799,27 @@
         <v>2474.23</v>
       </c>
       <c r="M23" s="1">
-        <v>3049.99</v>
+        <v>6469.99</v>
       </c>
       <c r="N23" s="1">
-        <v>12.33</v>
+        <v>26.17</v>
       </c>
       <c r="O23" s="1">
-        <v>3027.75</v>
+        <v>6447.75</v>
       </c>
       <c r="P23" s="1">
-        <v>12.23</v>
+        <v>26.05</v>
       </c>
       <c r="Q23" s="1">
-        <v>27770</v>
+        <v>31190</v>
       </c>
       <c r="R23" s="1">
-        <v>27770</v>
+        <v>31190</v>
       </c>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
       <c r="U23" s="1">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="V23" s="1">
         <v>0</v>
@@ -1856,16 +1848,16 @@
         <v>15000</v>
       </c>
       <c r="G24" s="1">
-        <v>253.7</v>
+        <v>267.3</v>
       </c>
       <c r="H24" t="s">
         <v>2</v>
       </c>
       <c r="I24" s="1">
-        <v>1484.75</v>
+        <v>2039.76</v>
       </c>
       <c r="J24" s="1">
-        <v>4.0599999999999996</v>
+        <v>5.36</v>
       </c>
       <c r="K24" s="1">
         <v>317.23</v>
@@ -1874,27 +1866,27 @@
         <v>318.69</v>
       </c>
       <c r="M24" s="1">
-        <v>-9529.89</v>
+        <v>-7489.89</v>
       </c>
       <c r="N24" s="1">
-        <v>-20.02</v>
+        <v>-15.74</v>
       </c>
       <c r="O24" s="1">
-        <v>-9747.98</v>
+        <v>-7707.98</v>
       </c>
       <c r="P24" s="1">
-        <v>-20.39</v>
+        <v>-16.12</v>
       </c>
       <c r="Q24" s="1">
-        <v>38055</v>
+        <v>40095</v>
       </c>
       <c r="R24" s="1">
-        <v>38055</v>
+        <v>40095</v>
       </c>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
       <c r="U24" s="1">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="V24" s="1">
         <v>0</v>
@@ -1923,49 +1915,45 @@
         <v>1350</v>
       </c>
       <c r="G25" s="1">
-        <v>2213</v>
+        <v>2440</v>
       </c>
       <c r="H25" t="s">
         <v>2</v>
       </c>
       <c r="I25" s="1">
-        <v>14.93</v>
+        <v>-215.51</v>
       </c>
       <c r="J25" s="1">
-        <v>0.05</v>
+        <v>-0.65</v>
       </c>
       <c r="K25" s="1">
-        <v>2610.16</v>
+        <v>2575.86</v>
       </c>
       <c r="L25" s="1">
         <v>2758.41</v>
       </c>
       <c r="M25" s="1">
-        <v>-5361.71</v>
+        <v>-1834.03</v>
       </c>
       <c r="N25" s="1">
-        <v>-15.21</v>
+        <v>-5.27</v>
       </c>
       <c r="O25" s="1">
-        <v>-7362.98</v>
+        <v>-4298.4799999999996</v>
       </c>
       <c r="P25" s="1">
-        <v>-19.77</v>
+        <v>-11.54</v>
       </c>
       <c r="Q25" s="1">
-        <v>29875.5</v>
+        <v>32940</v>
       </c>
       <c r="R25" s="1">
-        <v>29875.5</v>
-      </c>
-      <c r="S25" s="1">
-        <v>463.18</v>
-      </c>
-      <c r="T25" s="1">
-        <v>463.18</v>
-      </c>
+        <v>32940</v>
+      </c>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
       <c r="U25" s="1">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="V25" s="1">
         <v>0</v>
@@ -1994,49 +1982,45 @@
         <v>700</v>
       </c>
       <c r="G26" s="1">
-        <v>4300</v>
+        <v>4673</v>
       </c>
       <c r="H26" t="s">
         <v>2</v>
       </c>
       <c r="I26" s="1">
-        <v>188.44</v>
+        <v>-474.55</v>
       </c>
       <c r="J26" s="1">
-        <v>0.63</v>
+        <v>-1.43</v>
       </c>
       <c r="K26" s="1">
-        <v>5582.59</v>
+        <v>5547.95</v>
       </c>
       <c r="L26" s="1">
         <v>5657.95</v>
       </c>
       <c r="M26" s="1">
-        <v>-8978.1</v>
+        <v>-6124.68</v>
       </c>
       <c r="N26" s="1">
-        <v>-22.97</v>
+        <v>-15.77</v>
       </c>
       <c r="O26" s="1">
-        <v>-9505.6200000000008</v>
+        <v>-6894.62</v>
       </c>
       <c r="P26" s="1">
-        <v>-24</v>
+        <v>-17.399999999999999</v>
       </c>
       <c r="Q26" s="1">
-        <v>30100</v>
+        <v>32711</v>
       </c>
       <c r="R26" s="1">
-        <v>30100</v>
-      </c>
-      <c r="S26" s="1">
-        <v>242.42</v>
-      </c>
-      <c r="T26" s="1">
-        <v>242.42</v>
-      </c>
+        <v>32711</v>
+      </c>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
       <c r="U26" s="1">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="V26" s="1">
         <v>0</v>
@@ -2065,16 +2049,16 @@
         <v>2900</v>
       </c>
       <c r="G27" s="1">
-        <v>748</v>
+        <v>755.6</v>
       </c>
       <c r="H27" t="s">
         <v>2</v>
       </c>
       <c r="I27" s="1">
-        <v>28.16</v>
+        <v>-203.47</v>
       </c>
       <c r="J27" s="1">
-        <v>0.13</v>
+        <v>-0.92</v>
       </c>
       <c r="K27" s="1">
         <v>998</v>
@@ -2083,27 +2067,27 @@
         <v>998.9</v>
       </c>
       <c r="M27" s="1">
-        <v>-7250</v>
+        <v>-7029.6</v>
       </c>
       <c r="N27" s="1">
-        <v>-25.05</v>
+        <v>-24.28</v>
       </c>
       <c r="O27" s="1">
-        <v>-7276.05</v>
+        <v>-7055.65</v>
       </c>
       <c r="P27" s="1">
-        <v>-25.11</v>
+        <v>-24.35</v>
       </c>
       <c r="Q27" s="1">
-        <v>21692</v>
+        <v>21912.400000000001</v>
       </c>
       <c r="R27" s="1">
-        <v>21692</v>
+        <v>21912.400000000001</v>
       </c>
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
       <c r="U27" s="1">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="V27" s="1">
         <v>0</v>
@@ -2132,7 +2116,7 @@
         <v>252849</v>
       </c>
       <c r="G28" s="1">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H28" t="s">
         <v>2</v>
@@ -2141,7 +2125,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="1">
-        <v>-0.55000000000000004</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
         <v>40</v>
@@ -2150,27 +2134,27 @@
         <v>40.04</v>
       </c>
       <c r="M28" s="1">
-        <v>-10103.84</v>
+        <v>-20217.8</v>
       </c>
       <c r="N28" s="1">
-        <v>-9.99</v>
+        <v>-19.989999999999998</v>
       </c>
       <c r="O28" s="1">
-        <v>-10201.11</v>
+        <v>-20315.07</v>
       </c>
       <c r="P28" s="1">
-        <v>-10.07</v>
+        <v>-20.059999999999999</v>
       </c>
       <c r="Q28" s="1">
-        <v>91025.64</v>
+        <v>80911.679999999993</v>
       </c>
       <c r="R28" s="1">
-        <v>91025.64</v>
+        <v>80911.679999999993</v>
       </c>
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
       <c r="U28" s="1">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="V28" s="1">
         <v>0</v>
@@ -2266,16 +2250,16 @@
         <v>500</v>
       </c>
       <c r="G30" s="1">
-        <v>4553</v>
+        <v>4167</v>
       </c>
       <c r="H30" t="s">
         <v>2</v>
       </c>
       <c r="I30" s="1">
-        <v>301.02</v>
+        <v>-651.03</v>
       </c>
       <c r="J30" s="1">
-        <v>1.34</v>
+        <v>-3.03</v>
       </c>
       <c r="K30" s="1">
         <v>4481.99</v>
@@ -2284,27 +2268,27 @@
         <v>4486.0200000000004</v>
       </c>
       <c r="M30" s="1">
-        <v>355.06</v>
+        <v>-1574.93</v>
       </c>
       <c r="N30" s="1">
-        <v>1.58</v>
+        <v>-7.02</v>
       </c>
       <c r="O30" s="1">
-        <v>334.91</v>
+        <v>-1595.09</v>
       </c>
       <c r="P30" s="1">
-        <v>1.49</v>
+        <v>-7.11</v>
       </c>
       <c r="Q30" s="1">
-        <v>22765</v>
+        <v>20835</v>
       </c>
       <c r="R30" s="1">
-        <v>22765</v>
+        <v>20835</v>
       </c>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
       <c r="U30" s="1">
-        <v>1.1299999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="V30" s="1">
         <v>0</v>
@@ -2434,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="Q32" s="1">
-        <v>557156.42000000004</v>
+        <v>563426.4</v>
       </c>
       <c r="R32" t="s">
         <v>0</v>
@@ -2617,16 +2601,16 @@
         <v>30000</v>
       </c>
       <c r="G35" s="1">
-        <v>120.8</v>
+        <v>121.73</v>
       </c>
       <c r="H35" t="s">
         <v>2</v>
       </c>
       <c r="I35" s="1">
-        <v>-178.45</v>
+        <v>25.55</v>
       </c>
       <c r="J35" s="1">
-        <v>-0.49</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K35" s="1">
         <v>120.64</v>
@@ -2635,27 +2619,27 @@
         <v>120.76</v>
       </c>
       <c r="M35" s="1">
-        <v>48.11</v>
+        <v>327.11</v>
       </c>
       <c r="N35" s="1">
-        <v>0.13</v>
+        <v>0.9</v>
       </c>
       <c r="O35" s="1">
-        <v>11.23</v>
+        <v>290.23</v>
       </c>
       <c r="P35" s="1">
-        <v>0.03</v>
+        <v>0.8</v>
       </c>
       <c r="Q35" s="1">
-        <v>36240</v>
+        <v>36519</v>
       </c>
       <c r="R35" s="1">
-        <v>36240</v>
+        <v>36519</v>
       </c>
       <c r="S35" s="1"/>
       <c r="T35" s="1"/>
       <c r="U35" s="1">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V35" s="1">
         <v>0</v>
@@ -2684,16 +2668,16 @@
         <v>75688.77</v>
       </c>
       <c r="G36" s="1">
-        <v>89.72</v>
+        <v>89.74</v>
       </c>
       <c r="H36" t="s">
         <v>2</v>
       </c>
       <c r="I36" s="1">
-        <v>-6.79</v>
+        <v>6.79</v>
       </c>
       <c r="J36" s="1">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="K36" s="1">
         <v>74.53</v>
@@ -2702,22 +2686,22 @@
         <v>81.37</v>
       </c>
       <c r="M36" s="1">
-        <v>11501.05</v>
+        <v>11516.19</v>
       </c>
       <c r="N36" s="1">
-        <v>20.38</v>
+        <v>20.41</v>
       </c>
       <c r="O36" s="1">
-        <v>6320.04</v>
+        <v>6335.18</v>
       </c>
       <c r="P36" s="1">
-        <v>10.26</v>
+        <v>10.28</v>
       </c>
       <c r="Q36" s="1">
-        <v>67907.960000000006</v>
+        <v>67923.100000000006</v>
       </c>
       <c r="R36" s="1">
-        <v>67907.960000000006</v>
+        <v>67923.100000000006</v>
       </c>
       <c r="S36" s="1"/>
       <c r="T36" s="1"/>
@@ -2751,16 +2735,16 @@
         <v>50000</v>
       </c>
       <c r="G37" s="1">
-        <v>103</v>
+        <v>104.89</v>
       </c>
       <c r="H37" t="s">
         <v>2</v>
       </c>
       <c r="I37" s="1">
-        <v>0</v>
+        <v>94.23</v>
       </c>
       <c r="J37" s="1">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="K37" s="1">
         <v>99.28</v>
@@ -2769,27 +2753,27 @@
         <v>102.54</v>
       </c>
       <c r="M37" s="1">
-        <v>1858.69</v>
+        <v>2803.69</v>
       </c>
       <c r="N37" s="1">
-        <v>3.74</v>
+        <v>5.64</v>
       </c>
       <c r="O37" s="1">
-        <v>231.4</v>
+        <v>1176.4000000000001</v>
       </c>
       <c r="P37" s="1">
-        <v>0.45</v>
+        <v>2.29</v>
       </c>
       <c r="Q37" s="1">
-        <v>51500</v>
+        <v>52445</v>
       </c>
       <c r="R37" s="1">
-        <v>51500</v>
+        <v>52445</v>
       </c>
       <c r="S37" s="1"/>
       <c r="T37" s="1"/>
       <c r="U37" s="1">
-        <v>2.5499999999999998</v>
+        <v>2.59</v>
       </c>
       <c r="V37" s="1">
         <v>0</v>
@@ -2818,7 +2802,7 @@
         <v>25000</v>
       </c>
       <c r="G38" s="1">
-        <v>99.24</v>
+        <v>98.75</v>
       </c>
       <c r="H38" t="s">
         <v>2</v>
@@ -2836,27 +2820,27 @@
         <v>100.91</v>
       </c>
       <c r="M38" s="1">
-        <v>428.47</v>
+        <v>305.97000000000003</v>
       </c>
       <c r="N38" s="1">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="O38" s="1">
-        <v>-417.97</v>
+        <v>-540.47</v>
       </c>
       <c r="P38" s="1">
-        <v>-1.65</v>
+        <v>-2.14</v>
       </c>
       <c r="Q38" s="1">
-        <v>24810</v>
+        <v>24687.5</v>
       </c>
       <c r="R38" s="1">
-        <v>24810</v>
+        <v>24687.5</v>
       </c>
       <c r="S38" s="1"/>
       <c r="T38" s="1"/>
       <c r="U38" s="1">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="V38" s="1">
         <v>0</v>
@@ -2885,16 +2869,16 @@
         <v>80257.09</v>
       </c>
       <c r="G39" s="1">
-        <v>112.34</v>
+        <v>112.82</v>
       </c>
       <c r="H39" t="s">
         <v>2</v>
       </c>
       <c r="I39" s="1">
-        <v>90.07</v>
+        <v>117.56</v>
       </c>
       <c r="J39" s="1">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="K39" s="1">
         <v>94.06</v>
@@ -2903,27 +2887,27 @@
         <v>99.76</v>
       </c>
       <c r="M39" s="1">
-        <v>14668.02</v>
+        <v>15053.26</v>
       </c>
       <c r="N39" s="1">
-        <v>19.420000000000002</v>
+        <v>19.93</v>
       </c>
       <c r="O39" s="1">
-        <v>10099.459999999999</v>
+        <v>10484.700000000001</v>
       </c>
       <c r="P39" s="1">
-        <v>12.61</v>
+        <v>13.09</v>
       </c>
       <c r="Q39" s="1">
-        <v>90160.81</v>
+        <v>90546.05</v>
       </c>
       <c r="R39" s="1">
-        <v>90160.81</v>
+        <v>90546.05</v>
       </c>
       <c r="S39" s="1"/>
       <c r="T39" s="1"/>
       <c r="U39" s="1">
-        <v>4.46</v>
+        <v>4.47</v>
       </c>
       <c r="V39" s="1">
         <v>0</v>
@@ -2952,16 +2936,16 @@
         <v>23000</v>
       </c>
       <c r="G40" s="1">
-        <v>120.93</v>
+        <v>121.42</v>
       </c>
       <c r="H40" t="s">
         <v>2</v>
       </c>
       <c r="I40" s="1">
-        <v>0</v>
+        <v>16.75</v>
       </c>
       <c r="J40" s="1">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="K40" s="1">
         <v>120.19</v>
@@ -2970,22 +2954,22 @@
         <v>120.3</v>
       </c>
       <c r="M40" s="1">
-        <v>170.19</v>
+        <v>282.89</v>
       </c>
       <c r="N40" s="1">
-        <v>0.61</v>
+        <v>1.02</v>
       </c>
       <c r="O40" s="1">
-        <v>145.32</v>
+        <v>258.02</v>
       </c>
       <c r="P40" s="1">
-        <v>0.52</v>
+        <v>0.93</v>
       </c>
       <c r="Q40" s="1">
-        <v>27813.9</v>
+        <v>27926.6</v>
       </c>
       <c r="R40" s="1">
-        <v>27813.9</v>
+        <v>27926.6</v>
       </c>
       <c r="S40" s="1"/>
       <c r="T40" s="1"/>
@@ -3019,16 +3003,16 @@
         <v>100000</v>
       </c>
       <c r="G41" s="1">
-        <v>92.33</v>
+        <v>92.41</v>
       </c>
       <c r="H41" t="s">
         <v>2</v>
       </c>
       <c r="I41" s="1">
-        <v>27.69</v>
+        <v>-9.24</v>
       </c>
       <c r="J41" s="1">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="K41" s="1">
         <v>74.83</v>
@@ -3037,22 +3021,22 @@
         <v>82.14</v>
       </c>
       <c r="M41" s="1">
-        <v>17502.490000000002</v>
+        <v>17582.490000000002</v>
       </c>
       <c r="N41" s="1">
-        <v>23.39</v>
+        <v>23.49</v>
       </c>
       <c r="O41" s="1">
-        <v>10187.93</v>
+        <v>10267.93</v>
       </c>
       <c r="P41" s="1">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="Q41" s="1">
-        <v>92330</v>
+        <v>92410</v>
       </c>
       <c r="R41" s="1">
-        <v>92330</v>
+        <v>92410</v>
       </c>
       <c r="S41" s="1"/>
       <c r="T41" s="1"/>
@@ -3086,16 +3070,16 @@
         <v>45000</v>
       </c>
       <c r="G42" s="1">
-        <v>102</v>
+        <v>100.5</v>
       </c>
       <c r="H42" t="s">
         <v>2</v>
       </c>
       <c r="I42" s="1">
-        <v>1293.5899999999999</v>
+        <v>500.91</v>
       </c>
       <c r="J42" s="1">
-        <v>2.9</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="K42" s="1">
         <v>102.23</v>
@@ -3104,27 +3088,27 @@
         <v>102.33</v>
       </c>
       <c r="M42" s="1">
-        <v>-104.98</v>
+        <v>-779.98</v>
       </c>
       <c r="N42" s="1">
-        <v>-0.22</v>
+        <v>-1.69</v>
       </c>
       <c r="O42" s="1">
-        <v>-146.4</v>
+        <v>-821.4</v>
       </c>
       <c r="P42" s="1">
-        <v>-0.31</v>
+        <v>-1.78</v>
       </c>
       <c r="Q42" s="1">
-        <v>45900</v>
+        <v>45225</v>
       </c>
       <c r="R42" s="1">
-        <v>45900</v>
+        <v>45225</v>
       </c>
       <c r="S42" s="1"/>
       <c r="T42" s="1"/>
       <c r="U42" s="1">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="V42" s="1">
         <v>0</v>
@@ -3153,7 +3137,7 @@
         <v>30000</v>
       </c>
       <c r="G43" s="1">
-        <v>99</v>
+        <v>100.4</v>
       </c>
       <c r="H43" t="s">
         <v>2</v>
@@ -3171,27 +3155,27 @@
         <v>99.09</v>
       </c>
       <c r="M43" s="1">
-        <v>0</v>
+        <v>419.99</v>
       </c>
       <c r="N43" s="1">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O43" s="1">
-        <v>-26.73</v>
+        <v>393.27</v>
       </c>
       <c r="P43" s="1">
-        <v>-0.08</v>
+        <v>1.32</v>
       </c>
       <c r="Q43" s="1">
-        <v>29700</v>
+        <v>30120</v>
       </c>
       <c r="R43" s="1">
-        <v>29700</v>
+        <v>30120</v>
       </c>
       <c r="S43" s="1"/>
       <c r="T43" s="1"/>
       <c r="U43" s="1">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="V43" s="1">
         <v>0</v>
@@ -3220,16 +3204,16 @@
         <v>25133</v>
       </c>
       <c r="G44" s="1">
-        <v>100.61</v>
+        <v>100.92</v>
       </c>
       <c r="H44" t="s">
         <v>2</v>
       </c>
       <c r="I44" s="1">
-        <v>0</v>
+        <v>35.46</v>
       </c>
       <c r="J44" s="1">
-        <v>0</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="K44" s="1">
         <v>97.53</v>
@@ -3238,22 +3222,22 @@
         <v>99.56</v>
       </c>
       <c r="M44" s="1">
-        <v>774.54</v>
+        <v>852.46</v>
       </c>
       <c r="N44" s="1">
-        <v>3.15</v>
+        <v>3.47</v>
       </c>
       <c r="O44" s="1">
-        <v>264.01</v>
+        <v>341.92</v>
       </c>
       <c r="P44" s="1">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="Q44" s="1">
-        <v>25286.31</v>
+        <v>25364.22</v>
       </c>
       <c r="R44" s="1">
-        <v>25286.31</v>
+        <v>25364.22</v>
       </c>
       <c r="S44" s="1"/>
       <c r="T44" s="1"/>
@@ -3287,16 +3271,16 @@
         <v>40000</v>
       </c>
       <c r="G45" s="1">
-        <v>95.4</v>
+        <v>96.6</v>
       </c>
       <c r="H45" t="s">
         <v>2</v>
       </c>
       <c r="I45" s="1">
-        <v>0</v>
+        <v>161.61000000000001</v>
       </c>
       <c r="J45" s="1">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="K45" s="1">
         <v>84.49</v>
@@ -3305,27 +3289,27 @@
         <v>94.72</v>
       </c>
       <c r="M45" s="1">
-        <v>4363.63</v>
+        <v>4843.63</v>
       </c>
       <c r="N45" s="1">
-        <v>12.91</v>
+        <v>14.33</v>
       </c>
       <c r="O45" s="1">
-        <v>272.16000000000003</v>
+        <v>752.16</v>
       </c>
       <c r="P45" s="1">
-        <v>0.71</v>
+        <v>1.98</v>
       </c>
       <c r="Q45" s="1">
-        <v>38160</v>
+        <v>38640</v>
       </c>
       <c r="R45" s="1">
-        <v>38160</v>
+        <v>38640</v>
       </c>
       <c r="S45" s="1"/>
       <c r="T45" s="1"/>
       <c r="U45" s="1">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V45" s="1">
         <v>0</v>
@@ -3354,16 +3338,16 @@
         <v>41667.919999999998</v>
       </c>
       <c r="G46" s="1">
-        <v>109.77</v>
+        <v>110.2</v>
       </c>
       <c r="H46" t="s">
         <v>2</v>
       </c>
       <c r="I46" s="1">
-        <v>-9.15</v>
+        <v>4.59</v>
       </c>
       <c r="J46" s="1">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="K46" s="1">
         <v>107.93</v>
@@ -3372,27 +3356,27 @@
         <v>108.14</v>
       </c>
       <c r="M46" s="1">
-        <v>768.52</v>
+        <v>947.69</v>
       </c>
       <c r="N46" s="1">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="O46" s="1">
-        <v>680.34</v>
+        <v>859.51</v>
       </c>
       <c r="P46" s="1">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="Q46" s="1">
-        <v>45738.879999999997</v>
+        <v>45918.05</v>
       </c>
       <c r="R46" s="1">
-        <v>45738.879999999997</v>
+        <v>45918.05</v>
       </c>
       <c r="S46" s="1"/>
       <c r="T46" s="1"/>
       <c r="U46" s="1">
-        <v>2.2599999999999998</v>
+        <v>2.27</v>
       </c>
       <c r="V46" s="1">
         <v>0</v>
@@ -3421,16 +3405,16 @@
         <v>61602</v>
       </c>
       <c r="G47" s="1">
-        <v>96.54</v>
+        <v>96.6</v>
       </c>
       <c r="H47" t="s">
         <v>2</v>
       </c>
       <c r="I47" s="1">
-        <v>0</v>
+        <v>-137.18</v>
       </c>
       <c r="J47" s="1">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
       <c r="K47" s="1">
         <v>86.1</v>
@@ -3439,22 +3423,22 @@
         <v>88.3</v>
       </c>
       <c r="M47" s="1">
-        <v>6430.2</v>
+        <v>6467.16</v>
       </c>
       <c r="N47" s="1">
-        <v>12.12</v>
+        <v>12.19</v>
       </c>
       <c r="O47" s="1">
-        <v>5073.8</v>
+        <v>5110.76</v>
       </c>
       <c r="P47" s="1">
-        <v>9.32</v>
+        <v>9.39</v>
       </c>
       <c r="Q47" s="1">
-        <v>59470.57</v>
+        <v>59507.53</v>
       </c>
       <c r="R47" s="1">
-        <v>59470.57</v>
+        <v>59507.53</v>
       </c>
       <c r="S47" s="1"/>
       <c r="T47" s="1"/>
@@ -3488,16 +3472,16 @@
         <v>57435.9</v>
       </c>
       <c r="G48" s="1">
-        <v>119.33</v>
+        <v>119.55</v>
       </c>
       <c r="H48" t="s">
         <v>2</v>
       </c>
       <c r="I48" s="1">
-        <v>20.56</v>
+        <v>-6.87</v>
       </c>
       <c r="J48" s="1">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="K48" s="1">
         <v>106.92</v>
@@ -3506,22 +3490,22 @@
         <v>110.63</v>
       </c>
       <c r="M48" s="1">
-        <v>7127.5</v>
+        <v>7253.86</v>
       </c>
       <c r="N48" s="1">
-        <v>11.6</v>
+        <v>11.81</v>
       </c>
       <c r="O48" s="1">
-        <v>4994.57</v>
+        <v>5120.93</v>
       </c>
       <c r="P48" s="1">
-        <v>7.86</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="Q48" s="1">
-        <v>68538.259999999995</v>
+        <v>68664.62</v>
       </c>
       <c r="R48" s="1">
-        <v>68538.259999999995</v>
+        <v>68664.62</v>
       </c>
       <c r="S48" s="1"/>
       <c r="T48" s="1"/>
@@ -3555,16 +3539,16 @@
         <v>45000</v>
       </c>
       <c r="G49" s="1">
-        <v>104.2</v>
+        <v>104.46</v>
       </c>
       <c r="H49" t="s">
         <v>2</v>
       </c>
       <c r="I49" s="1">
-        <v>-23.46</v>
+        <v>4.7</v>
       </c>
       <c r="J49" s="1">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="K49" s="1">
         <v>101.08</v>
@@ -3573,22 +3557,22 @@
         <v>106.6</v>
       </c>
       <c r="M49" s="1">
-        <v>1404.98</v>
+        <v>1521.98</v>
       </c>
       <c r="N49" s="1">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="O49" s="1">
-        <v>-1078.1199999999999</v>
+        <v>-961.12</v>
       </c>
       <c r="P49" s="1">
-        <v>-2.2400000000000002</v>
+        <v>-2</v>
       </c>
       <c r="Q49" s="1">
-        <v>46890</v>
+        <v>47007</v>
       </c>
       <c r="R49" s="1">
-        <v>46890</v>
+        <v>47007</v>
       </c>
       <c r="S49" s="1"/>
       <c r="T49" s="1"/>
@@ -3622,16 +3606,16 @@
         <v>40000</v>
       </c>
       <c r="G50" s="1">
-        <v>118.95</v>
+        <v>119.2</v>
       </c>
       <c r="H50" t="s">
         <v>2</v>
       </c>
       <c r="I50" s="1">
-        <v>0</v>
+        <v>-14.31</v>
       </c>
       <c r="J50" s="1">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="K50" s="1">
         <v>109.11</v>
@@ -3640,27 +3624,27 @@
         <v>111.45</v>
       </c>
       <c r="M50" s="1">
-        <v>3937.39</v>
+        <v>4037.39</v>
       </c>
       <c r="N50" s="1">
-        <v>9.02</v>
+        <v>9.25</v>
       </c>
       <c r="O50" s="1">
-        <v>3001.07</v>
+        <v>3101.07</v>
       </c>
       <c r="P50" s="1">
-        <v>6.73</v>
+        <v>6.95</v>
       </c>
       <c r="Q50" s="1">
-        <v>47580</v>
+        <v>47680</v>
       </c>
       <c r="R50" s="1">
-        <v>47580</v>
+        <v>47680</v>
       </c>
       <c r="S50" s="1"/>
       <c r="T50" s="1"/>
       <c r="U50" s="1">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="V50" s="1">
         <v>0</v>
@@ -3689,16 +3673,16 @@
         <v>24000</v>
       </c>
       <c r="G51" s="1">
-        <v>121.39</v>
+        <v>121.8</v>
       </c>
       <c r="H51" t="s">
         <v>2</v>
       </c>
       <c r="I51" s="1">
-        <v>0</v>
+        <v>23.37</v>
       </c>
       <c r="J51" s="1">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="K51" s="1">
         <v>121</v>
@@ -3707,22 +3691,22 @@
         <v>121.13</v>
       </c>
       <c r="M51" s="1">
-        <v>93.59</v>
+        <v>191.99</v>
       </c>
       <c r="N51" s="1">
-        <v>0.32</v>
+        <v>0.66</v>
       </c>
       <c r="O51" s="1">
-        <v>63.01</v>
+        <v>161.41</v>
       </c>
       <c r="P51" s="1">
-        <v>0.21</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="Q51" s="1">
-        <v>29133.599999999999</v>
+        <v>29232</v>
       </c>
       <c r="R51" s="1">
-        <v>29133.599999999999</v>
+        <v>29232</v>
       </c>
       <c r="S51" s="1"/>
       <c r="T51" s="1"/>
@@ -3741,10 +3725,10 @@
         <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="C52" t="s">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="D52" t="s">
         <v>0</v>
@@ -3752,51 +3736,55 @@
       <c r="E52" t="s">
         <v>0</v>
       </c>
-      <c r="F52" s="1">
-        <v>20000</v>
-      </c>
-      <c r="G52" s="1">
-        <v>144.69999999999999</v>
+      <c r="F52" t="s">
+        <v>0</v>
+      </c>
+      <c r="G52" t="s">
+        <v>0</v>
       </c>
       <c r="H52" t="s">
-        <v>2</v>
-      </c>
-      <c r="I52" s="1">
-        <v>-218.69</v>
-      </c>
-      <c r="J52" s="1">
-        <v>-0.75</v>
-      </c>
-      <c r="K52" s="1">
-        <v>121.85</v>
-      </c>
-      <c r="L52" s="1">
-        <v>124.11</v>
-      </c>
-      <c r="M52" s="1">
-        <v>4569.97</v>
-      </c>
-      <c r="N52" s="1">
-        <v>18.75</v>
-      </c>
-      <c r="O52" s="1">
-        <v>4117.68</v>
-      </c>
-      <c r="P52" s="1">
-        <v>16.579999999999998</v>
-      </c>
-      <c r="Q52" s="1">
-        <v>28940</v>
-      </c>
-      <c r="R52" s="1">
-        <v>28940</v>
-      </c>
-      <c r="S52" s="1"/>
-      <c r="T52" s="1"/>
-      <c r="U52" s="1">
-        <v>1.43</v>
-      </c>
-      <c r="V52" s="1">
+        <v>0</v>
+      </c>
+      <c r="I52" t="s">
+        <v>0</v>
+      </c>
+      <c r="J52" t="s">
+        <v>0</v>
+      </c>
+      <c r="K52" t="s">
+        <v>0</v>
+      </c>
+      <c r="L52" t="s">
+        <v>0</v>
+      </c>
+      <c r="M52" t="s">
+        <v>0</v>
+      </c>
+      <c r="N52" t="s">
+        <v>0</v>
+      </c>
+      <c r="O52" t="s">
+        <v>0</v>
+      </c>
+      <c r="P52" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>0</v>
+      </c>
+      <c r="R52" t="s">
+        <v>0</v>
+      </c>
+      <c r="S52" t="s">
+        <v>0</v>
+      </c>
+      <c r="T52" t="s">
+        <v>0</v>
+      </c>
+      <c r="U52" t="s">
+        <v>0</v>
+      </c>
+      <c r="V52" t="s">
         <v>0</v>
       </c>
       <c r="W52" t="s">
@@ -3808,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="B53" t="s">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C53" t="s">
         <v>0</v>
@@ -3852,8 +3840,8 @@
       <c r="P53" t="s">
         <v>0</v>
       </c>
-      <c r="Q53" t="s">
-        <v>0</v>
+      <c r="Q53" s="1">
+        <v>829815.67</v>
       </c>
       <c r="R53" t="s">
         <v>0</v>
@@ -3879,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="B54" t="s">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="C54" t="s">
         <v>0</v>
@@ -3923,8 +3911,8 @@
       <c r="P54" t="s">
         <v>0</v>
       </c>
-      <c r="Q54" s="1">
-        <v>856100.29</v>
+      <c r="Q54" t="s">
+        <v>0</v>
       </c>
       <c r="R54" t="s">
         <v>0</v>
@@ -3950,7 +3938,7 @@
         <v>0</v>
       </c>
       <c r="B55" t="s">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="C55" t="s">
         <v>0</v>
@@ -4021,66 +4009,62 @@
         <v>0</v>
       </c>
       <c r="B56" t="s">
+        <v>97</v>
+      </c>
+      <c r="C56" t="s">
         <v>98</v>
       </c>
-      <c r="C56" t="s">
-        <v>0</v>
-      </c>
       <c r="D56" t="s">
         <v>0</v>
       </c>
       <c r="E56" t="s">
         <v>0</v>
       </c>
-      <c r="F56" t="s">
-        <v>0</v>
-      </c>
-      <c r="G56" t="s">
-        <v>0</v>
+      <c r="F56" s="1">
+        <v>41000</v>
+      </c>
+      <c r="G56" s="1">
+        <v>127.46</v>
       </c>
       <c r="H56" t="s">
-        <v>0</v>
-      </c>
-      <c r="I56" t="s">
-        <v>0</v>
-      </c>
-      <c r="J56" t="s">
-        <v>0</v>
-      </c>
-      <c r="K56" t="s">
-        <v>0</v>
-      </c>
-      <c r="L56" t="s">
-        <v>0</v>
-      </c>
-      <c r="M56" t="s">
-        <v>0</v>
-      </c>
-      <c r="N56" t="s">
-        <v>0</v>
-      </c>
-      <c r="O56" t="s">
-        <v>0</v>
-      </c>
-      <c r="P56" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="s">
-        <v>0</v>
-      </c>
-      <c r="R56" t="s">
-        <v>0</v>
-      </c>
-      <c r="S56" t="s">
-        <v>0</v>
-      </c>
-      <c r="T56" t="s">
-        <v>0</v>
-      </c>
-      <c r="U56" t="s">
-        <v>0</v>
-      </c>
-      <c r="V56" t="s">
+        <v>3</v>
+      </c>
+      <c r="I56" s="1">
+        <v>24.49</v>
+      </c>
+      <c r="J56" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="K56" s="1">
+        <v>120.19</v>
+      </c>
+      <c r="L56" s="1">
+        <v>125.17</v>
+      </c>
+      <c r="M56" s="1">
+        <v>8962.42</v>
+      </c>
+      <c r="N56" s="1">
+        <v>6.05</v>
+      </c>
+      <c r="O56" s="1">
+        <v>2819.29</v>
+      </c>
+      <c r="P56" s="1">
+        <v>1.82</v>
+      </c>
+      <c r="Q56" s="1">
+        <v>157037.09</v>
+      </c>
+      <c r="R56" s="1">
+        <v>52258.6</v>
+      </c>
+      <c r="S56" s="1"/>
+      <c r="T56" s="1"/>
+      <c r="U56" s="1">
+        <v>7.76</v>
+      </c>
+      <c r="V56" s="1">
         <v>0</v>
       </c>
       <c r="W56" t="s">
@@ -4104,48 +4088,48 @@
         <v>0</v>
       </c>
       <c r="F57" s="1">
-        <v>45000</v>
+        <v>144000</v>
       </c>
       <c r="G57" s="1">
-        <v>127.37</v>
+        <v>106.24</v>
       </c>
       <c r="H57" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I57" s="1">
-        <v>40.020000000000003</v>
+        <v>14.38</v>
       </c>
       <c r="J57" s="1">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="K57" s="1">
-        <v>120.19</v>
+        <v>105.16</v>
       </c>
       <c r="L57" s="1">
-        <v>125.11</v>
+        <v>105.53</v>
       </c>
       <c r="M57" s="1">
-        <v>9608.41</v>
+        <v>1549</v>
       </c>
       <c r="N57" s="1">
-        <v>5.97</v>
+        <v>1.02</v>
       </c>
       <c r="O57" s="1">
-        <v>3019.84</v>
+        <v>1022.4</v>
       </c>
       <c r="P57" s="1">
-        <v>1.8</v>
+        <v>0.67</v>
       </c>
       <c r="Q57" s="1">
-        <v>170344.64</v>
+        <v>152985.60000000001</v>
       </c>
       <c r="R57" s="1">
-        <v>57316.5</v>
+        <v>152985.60000000001</v>
       </c>
       <c r="S57" s="1"/>
       <c r="T57" s="1"/>
       <c r="U57" s="1">
-        <v>8.43</v>
+        <v>7.56</v>
       </c>
       <c r="V57" s="1">
         <v>0</v>
@@ -4171,48 +4155,48 @@
         <v>0</v>
       </c>
       <c r="F58" s="1">
-        <v>144000</v>
+        <v>30000</v>
       </c>
       <c r="G58" s="1">
-        <v>106.15</v>
+        <v>108.37</v>
       </c>
       <c r="H58" t="s">
         <v>2</v>
       </c>
       <c r="I58" s="1">
-        <v>0</v>
+        <v>5.98</v>
       </c>
       <c r="J58" s="1">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="K58" s="1">
-        <v>105.16</v>
+        <v>108.37</v>
       </c>
       <c r="L58" s="1">
-        <v>105.53</v>
+        <v>108.37</v>
       </c>
       <c r="M58" s="1">
-        <v>1419.4</v>
+        <v>0</v>
       </c>
       <c r="N58" s="1">
-        <v>0.93</v>
+        <v>0</v>
       </c>
       <c r="O58" s="1">
-        <v>892.8</v>
+        <v>0</v>
       </c>
       <c r="P58" s="1">
-        <v>0.57999999999999996</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="1">
-        <v>152856</v>
+        <v>32511</v>
       </c>
       <c r="R58" s="1">
-        <v>152856</v>
+        <v>32511</v>
       </c>
       <c r="S58" s="1"/>
       <c r="T58" s="1"/>
       <c r="U58" s="1">
-        <v>7.56</v>
+        <v>1.61</v>
       </c>
       <c r="V58" s="1">
         <v>0</v>
@@ -4342,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="Q60" s="1">
-        <v>323200.64000000001</v>
+        <v>342533.69</v>
       </c>
       <c r="R60" t="s">
         <v>0</v>
@@ -4525,16 +4509,16 @@
         <v>703</v>
       </c>
       <c r="G63" s="1">
-        <v>39820</v>
+        <v>40860</v>
       </c>
       <c r="H63" t="s">
         <v>2</v>
       </c>
       <c r="I63" s="1">
-        <v>3100.54</v>
+        <v>2251.46</v>
       </c>
       <c r="J63" s="1">
-        <v>1.1200000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="K63" s="1">
         <v>34092.879999999997</v>
@@ -4543,27 +4527,27 @@
         <v>34168.11</v>
       </c>
       <c r="M63" s="1">
-        <v>40261.65</v>
+        <v>47572.85</v>
       </c>
       <c r="N63" s="1">
-        <v>16.79</v>
+        <v>19.84</v>
       </c>
       <c r="O63" s="1">
-        <v>39732.81</v>
+        <v>47044.01</v>
       </c>
       <c r="P63" s="1">
-        <v>16.54</v>
+        <v>19.579999999999998</v>
       </c>
       <c r="Q63" s="1">
-        <v>279934.59999999998</v>
+        <v>287245.8</v>
       </c>
       <c r="R63" s="1">
-        <v>279934.59999999998</v>
+        <v>287245.8</v>
       </c>
       <c r="S63" s="1"/>
       <c r="T63" s="1"/>
       <c r="U63" s="1">
-        <v>13.85</v>
+        <v>14.19</v>
       </c>
       <c r="V63" s="1">
         <v>0</v>
@@ -4693,7 +4677,7 @@
         <v>0</v>
       </c>
       <c r="Q65" s="1">
-        <v>279934.59999999998</v>
+        <v>287245.8</v>
       </c>
       <c r="R65" t="s">
         <v>0</v>
@@ -4861,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="B68" t="s">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="C68" t="s">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D68" t="s">
         <v>0</v>
@@ -4872,51 +4856,55 @@
       <c r="E68" t="s">
         <v>0</v>
       </c>
-      <c r="F68" s="1">
-        <v>7148</v>
-      </c>
-      <c r="G68" s="1">
-        <v>56.5</v>
+      <c r="F68" t="s">
+        <v>0</v>
+      </c>
+      <c r="G68" t="s">
+        <v>0</v>
       </c>
       <c r="H68" t="s">
-        <v>2</v>
-      </c>
-      <c r="I68" s="1">
-        <v>0</v>
-      </c>
-      <c r="J68" s="1">
-        <v>0</v>
-      </c>
-      <c r="K68" s="1">
-        <v>56.1</v>
-      </c>
-      <c r="L68" s="1">
-        <v>56.15</v>
-      </c>
-      <c r="M68" s="1">
-        <v>28.59</v>
-      </c>
-      <c r="N68" s="1">
-        <v>0.71</v>
-      </c>
-      <c r="O68" s="1">
-        <v>24.99</v>
-      </c>
-      <c r="P68" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="Q68" s="1">
-        <v>4038.62</v>
-      </c>
-      <c r="R68" s="1">
-        <v>4038.62</v>
-      </c>
-      <c r="S68" s="1"/>
-      <c r="T68" s="1"/>
-      <c r="U68" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="V68" s="1">
+        <v>0</v>
+      </c>
+      <c r="I68" t="s">
+        <v>0</v>
+      </c>
+      <c r="J68" t="s">
+        <v>0</v>
+      </c>
+      <c r="K68" t="s">
+        <v>0</v>
+      </c>
+      <c r="L68" t="s">
+        <v>0</v>
+      </c>
+      <c r="M68" t="s">
+        <v>0</v>
+      </c>
+      <c r="N68" t="s">
+        <v>0</v>
+      </c>
+      <c r="O68" t="s">
+        <v>0</v>
+      </c>
+      <c r="P68" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>0</v>
+      </c>
+      <c r="R68" t="s">
+        <v>0</v>
+      </c>
+      <c r="S68" t="s">
+        <v>0</v>
+      </c>
+      <c r="T68" t="s">
+        <v>0</v>
+      </c>
+      <c r="U68" t="s">
+        <v>0</v>
+      </c>
+      <c r="V68" t="s">
         <v>0</v>
       </c>
       <c r="W68" t="s">
@@ -4928,7 +4916,7 @@
         <v>0</v>
       </c>
       <c r="B69" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C69" t="s">
         <v>0</v>
@@ -4999,66 +4987,62 @@
         <v>0</v>
       </c>
       <c r="B70" t="s">
+        <v>109</v>
+      </c>
+      <c r="C70" t="s">
+        <v>110</v>
+      </c>
+      <c r="D70" t="s">
         <v>111</v>
       </c>
-      <c r="C70" t="s">
-        <v>0</v>
-      </c>
-      <c r="D70" t="s">
-        <v>0</v>
-      </c>
       <c r="E70" t="s">
         <v>0</v>
       </c>
-      <c r="F70" t="s">
-        <v>0</v>
-      </c>
-      <c r="G70" t="s">
-        <v>0</v>
+      <c r="F70" s="1">
+        <v>700</v>
+      </c>
+      <c r="G70" s="1">
+        <v>0.33</v>
       </c>
       <c r="H70" t="s">
-        <v>0</v>
-      </c>
-      <c r="I70" t="s">
-        <v>0</v>
-      </c>
-      <c r="J70" t="s">
-        <v>0</v>
-      </c>
-      <c r="K70" t="s">
-        <v>0</v>
-      </c>
-      <c r="L70" t="s">
-        <v>0</v>
-      </c>
-      <c r="M70" t="s">
-        <v>0</v>
-      </c>
-      <c r="N70" t="s">
-        <v>0</v>
-      </c>
-      <c r="O70" t="s">
-        <v>0</v>
-      </c>
-      <c r="P70" t="s">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="I70" s="1">
+        <v>0</v>
+      </c>
+      <c r="J70" s="1">
+        <v>0</v>
+      </c>
+      <c r="K70" s="1">
+        <v>0.59</v>
+      </c>
+      <c r="L70" s="1">
+        <v>0.59</v>
+      </c>
+      <c r="M70" s="1">
+        <v>-555.74</v>
+      </c>
+      <c r="N70" s="1">
+        <v>-44.77</v>
+      </c>
+      <c r="O70" s="1">
+        <v>-564.15</v>
+      </c>
+      <c r="P70" s="1">
+        <v>-45.15</v>
       </c>
       <c r="Q70" s="1">
-        <v>4038.62</v>
-      </c>
-      <c r="R70" t="s">
-        <v>0</v>
-      </c>
-      <c r="S70" t="s">
-        <v>0</v>
-      </c>
-      <c r="T70" t="s">
-        <v>0</v>
-      </c>
-      <c r="U70" t="s">
-        <v>0</v>
-      </c>
-      <c r="V70" t="s">
+        <v>685.32</v>
+      </c>
+      <c r="R70" s="1">
+        <v>228.06</v>
+      </c>
+      <c r="S70" s="1"/>
+      <c r="T70" s="1"/>
+      <c r="U70" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="V70" s="1">
         <v>0</v>
       </c>
       <c r="W70" t="s">
@@ -5141,7 +5125,7 @@
         <v>0</v>
       </c>
       <c r="B72" t="s">
-        <v>112</v>
+        <v>59</v>
       </c>
       <c r="C72" t="s">
         <v>0</v>
@@ -5185,8 +5169,8 @@
       <c r="P72" t="s">
         <v>0</v>
       </c>
-      <c r="Q72" t="s">
-        <v>0</v>
+      <c r="Q72" s="1">
+        <v>685.32</v>
       </c>
       <c r="R72" t="s">
         <v>0</v>
@@ -5204,357 +5188,6 @@
         <v>0</v>
       </c>
       <c r="W72" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C73" t="s">
-        <v>0</v>
-      </c>
-      <c r="D73" t="s">
-        <v>0</v>
-      </c>
-      <c r="E73" t="s">
-        <v>0</v>
-      </c>
-      <c r="F73" t="s">
-        <v>0</v>
-      </c>
-      <c r="G73" t="s">
-        <v>0</v>
-      </c>
-      <c r="H73" t="s">
-        <v>0</v>
-      </c>
-      <c r="I73" t="s">
-        <v>0</v>
-      </c>
-      <c r="J73" t="s">
-        <v>0</v>
-      </c>
-      <c r="K73" t="s">
-        <v>0</v>
-      </c>
-      <c r="L73" t="s">
-        <v>0</v>
-      </c>
-      <c r="M73" t="s">
-        <v>0</v>
-      </c>
-      <c r="N73" t="s">
-        <v>0</v>
-      </c>
-      <c r="O73" t="s">
-        <v>0</v>
-      </c>
-      <c r="P73" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q73" t="s">
-        <v>0</v>
-      </c>
-      <c r="R73" t="s">
-        <v>0</v>
-      </c>
-      <c r="S73" t="s">
-        <v>0</v>
-      </c>
-      <c r="T73" t="s">
-        <v>0</v>
-      </c>
-      <c r="U73" t="s">
-        <v>0</v>
-      </c>
-      <c r="V73" t="s">
-        <v>0</v>
-      </c>
-      <c r="W73" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A74" t="s">
-        <v>0</v>
-      </c>
-      <c r="B74" t="s">
-        <v>26</v>
-      </c>
-      <c r="C74" t="s">
-        <v>0</v>
-      </c>
-      <c r="D74" t="s">
-        <v>0</v>
-      </c>
-      <c r="E74" t="s">
-        <v>0</v>
-      </c>
-      <c r="F74" t="s">
-        <v>0</v>
-      </c>
-      <c r="G74" t="s">
-        <v>0</v>
-      </c>
-      <c r="H74" t="s">
-        <v>0</v>
-      </c>
-      <c r="I74" t="s">
-        <v>0</v>
-      </c>
-      <c r="J74" t="s">
-        <v>0</v>
-      </c>
-      <c r="K74" t="s">
-        <v>0</v>
-      </c>
-      <c r="L74" t="s">
-        <v>0</v>
-      </c>
-      <c r="M74" t="s">
-        <v>0</v>
-      </c>
-      <c r="N74" t="s">
-        <v>0</v>
-      </c>
-      <c r="O74" t="s">
-        <v>0</v>
-      </c>
-      <c r="P74" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q74" t="s">
-        <v>0</v>
-      </c>
-      <c r="R74" t="s">
-        <v>0</v>
-      </c>
-      <c r="S74" t="s">
-        <v>0</v>
-      </c>
-      <c r="T74" t="s">
-        <v>0</v>
-      </c>
-      <c r="U74" t="s">
-        <v>0</v>
-      </c>
-      <c r="V74" t="s">
-        <v>0</v>
-      </c>
-      <c r="W74" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A75" t="s">
-        <v>0</v>
-      </c>
-      <c r="B75" t="s">
-        <v>113</v>
-      </c>
-      <c r="C75" t="s">
-        <v>114</v>
-      </c>
-      <c r="D75" t="s">
-        <v>115</v>
-      </c>
-      <c r="E75" t="s">
-        <v>0</v>
-      </c>
-      <c r="F75" s="1">
-        <v>700</v>
-      </c>
-      <c r="G75" s="1">
-        <v>0.33</v>
-      </c>
-      <c r="H75" t="s">
-        <v>3</v>
-      </c>
-      <c r="I75" s="1">
-        <v>-17.059999999999999</v>
-      </c>
-      <c r="J75" s="1">
-        <v>-2.41</v>
-      </c>
-      <c r="K75" s="1">
-        <v>0.59</v>
-      </c>
-      <c r="L75" s="1">
-        <v>0.59</v>
-      </c>
-      <c r="M75" s="1">
-        <v>-537.98</v>
-      </c>
-      <c r="N75" s="1">
-        <v>-43.83</v>
-      </c>
-      <c r="O75" s="1">
-        <v>-546.29999999999995</v>
-      </c>
-      <c r="P75" s="1">
-        <v>-44.2</v>
-      </c>
-      <c r="Q75" s="1">
-        <v>689.44</v>
-      </c>
-      <c r="R75" s="1">
-        <v>231.98</v>
-      </c>
-      <c r="S75" s="1"/>
-      <c r="T75" s="1"/>
-      <c r="U75" s="1">
-        <v>0.03</v>
-      </c>
-      <c r="V75" s="1">
-        <v>0</v>
-      </c>
-      <c r="W75" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A76" t="s">
-        <v>0</v>
-      </c>
-      <c r="B76" t="s">
-        <v>0</v>
-      </c>
-      <c r="C76" t="s">
-        <v>0</v>
-      </c>
-      <c r="D76" t="s">
-        <v>0</v>
-      </c>
-      <c r="E76" t="s">
-        <v>0</v>
-      </c>
-      <c r="F76" t="s">
-        <v>0</v>
-      </c>
-      <c r="G76" t="s">
-        <v>0</v>
-      </c>
-      <c r="H76" t="s">
-        <v>0</v>
-      </c>
-      <c r="I76" t="s">
-        <v>0</v>
-      </c>
-      <c r="J76" t="s">
-        <v>0</v>
-      </c>
-      <c r="K76" t="s">
-        <v>0</v>
-      </c>
-      <c r="L76" t="s">
-        <v>0</v>
-      </c>
-      <c r="M76" t="s">
-        <v>0</v>
-      </c>
-      <c r="N76" t="s">
-        <v>0</v>
-      </c>
-      <c r="O76" t="s">
-        <v>0</v>
-      </c>
-      <c r="P76" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q76" t="s">
-        <v>0</v>
-      </c>
-      <c r="R76" t="s">
-        <v>0</v>
-      </c>
-      <c r="S76" t="s">
-        <v>0</v>
-      </c>
-      <c r="T76" t="s">
-        <v>0</v>
-      </c>
-      <c r="U76" t="s">
-        <v>0</v>
-      </c>
-      <c r="V76" t="s">
-        <v>0</v>
-      </c>
-      <c r="W76" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A77" t="s">
-        <v>0</v>
-      </c>
-      <c r="B77" t="s">
-        <v>59</v>
-      </c>
-      <c r="C77" t="s">
-        <v>0</v>
-      </c>
-      <c r="D77" t="s">
-        <v>0</v>
-      </c>
-      <c r="E77" t="s">
-        <v>0</v>
-      </c>
-      <c r="F77" t="s">
-        <v>0</v>
-      </c>
-      <c r="G77" t="s">
-        <v>0</v>
-      </c>
-      <c r="H77" t="s">
-        <v>0</v>
-      </c>
-      <c r="I77" t="s">
-        <v>0</v>
-      </c>
-      <c r="J77" t="s">
-        <v>0</v>
-      </c>
-      <c r="K77" t="s">
-        <v>0</v>
-      </c>
-      <c r="L77" t="s">
-        <v>0</v>
-      </c>
-      <c r="M77" t="s">
-        <v>0</v>
-      </c>
-      <c r="N77" t="s">
-        <v>0</v>
-      </c>
-      <c r="O77" t="s">
-        <v>0</v>
-      </c>
-      <c r="P77" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q77" s="1">
-        <v>689.44</v>
-      </c>
-      <c r="R77" t="s">
-        <v>0</v>
-      </c>
-      <c r="S77" t="s">
-        <v>0</v>
-      </c>
-      <c r="T77" t="s">
-        <v>0</v>
-      </c>
-      <c r="U77" t="s">
-        <v>0</v>
-      </c>
-      <c r="V77" t="s">
-        <v>0</v>
-      </c>
-      <c r="W77" t="s">
         <v>0</v>
       </c>
     </row>
